--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80881FA0-F06D-43DF-BBA9-A24D39F20A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA60FAAD-B710-45A2-B8F2-AE32531C0C0D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="215">
   <si>
     <t>Project Name</t>
   </si>
@@ -601,6 +602,268 @@
   <si>
     <t xml:space="preserve">Mobile -461463
 </t>
+  </si>
+  <si>
+    <t>TS_FB_05</t>
+  </si>
+  <si>
+    <t>TC_FB_Nav_1</t>
+  </si>
+  <si>
+    <t>Verify Menu items and links</t>
+  </si>
+  <si>
+    <t>Login to Facebook &amp; Redirecting Menu items and links (Facebook Logo, Search,Home, Friends, Notifications, Messages )</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password 
+03. Click on login button
+04. Click on facebook logo
+05. Click on facebook search
+06. Click on facebook home
+07. Click on facebook Friends
+08. Click on facebook Notifications
+09. Click on facebook Messages</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Search "Rajarata Uni Lovers"</t>
+  </si>
+  <si>
+    <t>01. Reload to Homepage when click on logo
+02. Search Keyword
+03.Visit homepage, friends page, groups page, notification and messenger section</t>
+  </si>
+  <si>
+    <t>01. Reloading to Homepage when click on logo
+02. Searching Keyword
+03.Visiting  homepage, friends page, groups page, notification and messenger section</t>
+  </si>
+  <si>
+    <t>User should be able to see Facebook Home page, search keywords, see Home, Friends, Notifications, Messages sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigtion Bar </t>
+  </si>
+  <si>
+    <t>FaceBook Posting</t>
+  </si>
+  <si>
+    <t>TC_FB_post_1</t>
+  </si>
+  <si>
+    <t>User should be able to create a post</t>
+  </si>
+  <si>
+    <t>Create post</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Post - "Hi everyone, this is a Test Post, -KAVISHKA-"
+Location - Colombo
+Feeling - Happy
+Audience - Friends</t>
+  </si>
+  <si>
+    <t>Create post that including text, add location, feeling, tag friend, select audience and upload</t>
+  </si>
+  <si>
+    <t>CreatIing post</t>
+  </si>
+  <si>
+    <t>TS_FB_06</t>
+  </si>
+  <si>
+    <t>TC_FB_post_2</t>
+  </si>
+  <si>
+    <t>Create post by uploding photo with a caption, add location, activity, tag friend, select audience and upload</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Create post</t>
+  </si>
+  <si>
+    <t>User should be able to upload a photo and create a post</t>
+  </si>
+  <si>
+    <t>TC_FB_post_3</t>
+  </si>
+  <si>
+    <t>Edit Facebook post</t>
+  </si>
+  <si>
+    <t>User should be able to edit a post</t>
+  </si>
+  <si>
+    <t>Edit post</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Upload photo/video
+05. Create post</t>
+  </si>
+  <si>
+    <t>Upload a photo/video and Create post</t>
+  </si>
+  <si>
+    <t>Uploading a photo/video  and Create post</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Post - "Hi everyone, this is a Test Post, -KAVISHKA-"
+Photo
+Location - Kurunegala
+Activity - Listning to Youtube
+Audience - Friends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username - jigiwi7156@jofuso.com
+Password - Celkon
+Caption - "Successfully Edited"
+</t>
+  </si>
+  <si>
+    <t>TC_FB_post_4</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Visit Profile
+05. Edit post</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. React to post</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Reactions - Like, heart, wow, care, angry</t>
+  </si>
+  <si>
+    <t>React to post</t>
+  </si>
+  <si>
+    <t>Reacting to post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Facebook Post create and edit Fucntionality </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Facebook post reaction Fucntionality </t>
+  </si>
+  <si>
+    <t>React on Facebook posts</t>
+  </si>
+  <si>
+    <t>TC_FB_post_5</t>
+  </si>
+  <si>
+    <t>TC_FB_post_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Facebook comment Fucntionality </t>
+  </si>
+  <si>
+    <t>Write text comment on Facebook posts</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Write comment</t>
+  </si>
+  <si>
+    <t>User should be able to write a text comment on a post</t>
+  </si>
+  <si>
+    <t>Comment to post</t>
+  </si>
+  <si>
+    <t>Commenting to post</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Comment - "This is a test comment, From KAVISHKA"  + Emoji</t>
+  </si>
+  <si>
+    <t>Add photo comment on Facebook posts</t>
+  </si>
+  <si>
+    <t>User should be able to upload a photo and write a text comment on a post</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Comment - "This is a test comment, From KAVISHKA"  + Emoji
+Photo</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Write comment
+05. Upload a photo</t>
+  </si>
+  <si>
+    <t>TC_FB_post_7</t>
+  </si>
+  <si>
+    <t>Add sticker comment on Facebook posts</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Write comment
+05. Insert Sticker</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Comment - "This is a test comment, From KAVISHKA"  + Emoji
+Sticker</t>
+  </si>
+  <si>
+    <t>User should be able to insert a sticker and write a text comment on a post</t>
+  </si>
+  <si>
+    <t>TC_FB_post_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. React on comment
+</t>
+  </si>
+  <si>
+    <t>React on a comment of a Facebook post</t>
+  </si>
+  <si>
+    <t>User should be able to react on comments</t>
+  </si>
+  <si>
+    <t>User should be able to react on posts</t>
+  </si>
+  <si>
+    <t>React to comment</t>
+  </si>
+  <si>
+    <t>Reacting to comment</t>
   </si>
 </sst>
 </file>
@@ -635,7 +898,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -663,6 +926,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF7474"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C3FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -708,7 +983,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -765,23 +1040,624 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="92">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF6C3FF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1013,186 +1889,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1338,91 +2034,137 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}" name="Table4" displayName="Table4" ref="A8:N13" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}" name="Table4" displayName="Table4" ref="A8:N13" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
   <autoFilter ref="A8:N13" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{FA1520E5-151F-4C35-9564-490E6E227E63}" name="Test Scenario ID" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{4CD9CF72-D3D5-4E13-B21F-2628B71CA730}" name="Test Scenario Description" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{64C682F3-74F4-4B58-9AAA-079E2202EC63}" name="Test Case ID" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{F8711D9F-D3E9-4C0E-83A5-1112EACF3ECF}" name="Test Case Description" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{3C9E830E-1C51-4CB9-9B33-8A5AFEEE698E}" name="Test Steps" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{795BF8D4-2BAA-4AD4-842A-88C791483F7A}" name="Preconditions" dataDxfId="54"/>
-    <tableColumn id="14" xr3:uid="{21B04C03-953D-42FE-8068-4BF43AFF3291}" name="Test Data" dataDxfId="53"/>
-    <tableColumn id="15" xr3:uid="{9CF2DA71-3D28-4A14-A4CE-044972166E7C}" name="Post conditions" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{42C30692-F71E-4898-A159-20BE875D8033}" name="Expected Result" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{03D56321-2D40-4418-8D06-EED641A4F370}" name="Actual Result" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{C0EAC999-BB87-4D0C-9360-9BFF9AF67768}" name="Status" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{3B92054E-DFF9-4A75-AF0B-7B5080A92062}" name="Executed by" dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{E7860CF1-1E6C-471A-B8FB-6DB223239798}" name="Executed Date" dataDxfId="47"/>
-    <tableColumn id="11" xr3:uid="{D4382055-B4B2-40BA-B30A-2EE9840623E1}" name="Comments (Any)" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{FA1520E5-151F-4C35-9564-490E6E227E63}" name="Test Scenario ID" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{4CD9CF72-D3D5-4E13-B21F-2628B71CA730}" name="Test Scenario Description" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{64C682F3-74F4-4B58-9AAA-079E2202EC63}" name="Test Case ID" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{F8711D9F-D3E9-4C0E-83A5-1112EACF3ECF}" name="Test Case Description" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{3C9E830E-1C51-4CB9-9B33-8A5AFEEE698E}" name="Test Steps" dataDxfId="85"/>
+    <tableColumn id="13" xr3:uid="{795BF8D4-2BAA-4AD4-842A-88C791483F7A}" name="Preconditions" dataDxfId="84"/>
+    <tableColumn id="14" xr3:uid="{21B04C03-953D-42FE-8068-4BF43AFF3291}" name="Test Data" dataDxfId="83"/>
+    <tableColumn id="15" xr3:uid="{9CF2DA71-3D28-4A14-A4CE-044972166E7C}" name="Post conditions" dataDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{42C30692-F71E-4898-A159-20BE875D8033}" name="Expected Result" dataDxfId="81"/>
+    <tableColumn id="7" xr3:uid="{03D56321-2D40-4418-8D06-EED641A4F370}" name="Actual Result" dataDxfId="80"/>
+    <tableColumn id="8" xr3:uid="{C0EAC999-BB87-4D0C-9360-9BFF9AF67768}" name="Status" dataDxfId="79"/>
+    <tableColumn id="9" xr3:uid="{3B92054E-DFF9-4A75-AF0B-7B5080A92062}" name="Executed by" dataDxfId="78"/>
+    <tableColumn id="10" xr3:uid="{E7860CF1-1E6C-471A-B8FB-6DB223239798}" name="Executed Date" dataDxfId="77"/>
+    <tableColumn id="11" xr3:uid="{D4382055-B4B2-40BA-B30A-2EE9840623E1}" name="Comments (Any)" dataDxfId="76"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}" name="Table42" displayName="Table42" ref="A24:N32" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}" name="Table42" displayName="Table42" ref="A24:N32" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
   <autoFilter ref="A24:N32" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{B343AAFA-6457-4739-9100-101EF218F54D}" name="Test Scenario ID" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{E5529356-E16E-4EC4-9C43-4E830FC2E50F}" name="Test Scenario Description" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{2551A72A-8D4F-449F-B940-710504664FA5}" name="Test Case ID" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{00ECB93F-754B-43F5-9E43-F3D6BB21402C}" name="Test Case Description" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{66E4AAFF-0A66-44A2-A53B-7FABEAD85F8D}" name="Test Steps" dataDxfId="39"/>
-    <tableColumn id="13" xr3:uid="{662ABFF6-2773-475F-B091-BCDABF3FB4DE}" name="Preconditions" dataDxfId="38"/>
-    <tableColumn id="14" xr3:uid="{671E1D04-8126-4597-BD89-AC9A178AC6EA}" name="Test Data" dataDxfId="37"/>
-    <tableColumn id="15" xr3:uid="{90971945-FDC9-429A-8527-A13B23E811A8}" name="Post conditions" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{EF04FFC6-AA15-47C8-B4A9-828B2777CD1D}" name="Expected Result" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{4CA89147-B985-4D56-876B-62F63DC92C49}" name="Actual Result" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{BDA4C2F1-0AF2-488C-953C-82660F211B43}" name="Status" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{EF661887-7461-490A-8D26-42708C7DEF3D}" name="Executed by" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{BD8FCAC9-00C9-4F76-A5CA-C0CB2DE0CB76}" name="Executed Date" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{C33D96A1-29CA-4A83-BFA6-64CF06278883}" name="Comments (Any)" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{B343AAFA-6457-4739-9100-101EF218F54D}" name="Test Scenario ID" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{E5529356-E16E-4EC4-9C43-4E830FC2E50F}" name="Test Scenario Description" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{2551A72A-8D4F-449F-B940-710504664FA5}" name="Test Case ID" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{00ECB93F-754B-43F5-9E43-F3D6BB21402C}" name="Test Case Description" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{66E4AAFF-0A66-44A2-A53B-7FABEAD85F8D}" name="Test Steps" dataDxfId="69"/>
+    <tableColumn id="13" xr3:uid="{662ABFF6-2773-475F-B091-BCDABF3FB4DE}" name="Preconditions" dataDxfId="68"/>
+    <tableColumn id="14" xr3:uid="{671E1D04-8126-4597-BD89-AC9A178AC6EA}" name="Test Data" dataDxfId="67"/>
+    <tableColumn id="15" xr3:uid="{90971945-FDC9-429A-8527-A13B23E811A8}" name="Post conditions" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{EF04FFC6-AA15-47C8-B4A9-828B2777CD1D}" name="Expected Result" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{4CA89147-B985-4D56-876B-62F63DC92C49}" name="Actual Result" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{BDA4C2F1-0AF2-488C-953C-82660F211B43}" name="Status" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{EF661887-7461-490A-8D26-42708C7DEF3D}" name="Executed by" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{BD8FCAC9-00C9-4F76-A5CA-C0CB2DE0CB76}" name="Executed Date" dataDxfId="61"/>
+    <tableColumn id="11" xr3:uid="{C33D96A1-29CA-4A83-BFA6-64CF06278883}" name="Comments (Any)" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}" name="Table3" displayName="Table3" ref="B42:N44" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}" name="Table3" displayName="Table3" ref="B42:N44" totalsRowShown="0" headerRowDxfId="59" tableBorderDxfId="58">
   <autoFilter ref="B42:N44" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{1059CC3C-316E-4BE4-9F28-B883A79B86D2}" name="Test Scenario Description" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EA041670-F9F4-43FB-A857-C38D44666E25}" name="Test Case ID" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{9B2E537F-3535-451E-BB48-220B1F6FFB7F}" name="Test Case Description" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{4769C369-46C1-44B9-930F-E23A6BA66DD9}" name="Test Steps" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{298DD112-4C8B-46B3-A446-0E6D93CB1BC8}" name="Preconditions" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{37B46AC9-16E7-4ED1-8C0B-ADAE9CAAB714}" name="Test Data" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{8A9B609E-0F77-49DB-AE71-A0094C3164A7}" name="Post conditions" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{0CD618D3-C88B-4295-8ECC-CD62E718B8E9}" name="Expected Result" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{F2F61744-A610-47C1-8D18-258D214AD0AD}" name="Actual Result" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{BB7F01C1-4CCB-48BB-B1AF-EC76036F7A50}" name="Status" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{738EFE1E-9B5A-467D-B51A-FAE3C680984E}" name="Executed by" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{1CF50F8E-99F5-489F-9DDE-9E3702A3D89D}" name="Executed Date" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{9B03223D-6ED3-4549-9812-44F9B7FB9F5E}" name="Comments (Any)" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{1059CC3C-316E-4BE4-9F28-B883A79B86D2}" name="Test Scenario Description" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{EA041670-F9F4-43FB-A857-C38D44666E25}" name="Test Case ID" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{9B2E537F-3535-451E-BB48-220B1F6FFB7F}" name="Test Case Description" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{4769C369-46C1-44B9-930F-E23A6BA66DD9}" name="Test Steps" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{298DD112-4C8B-46B3-A446-0E6D93CB1BC8}" name="Preconditions" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{37B46AC9-16E7-4ED1-8C0B-ADAE9CAAB714}" name="Test Data" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{8A9B609E-0F77-49DB-AE71-A0094C3164A7}" name="Post conditions" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{0CD618D3-C88B-4295-8ECC-CD62E718B8E9}" name="Expected Result" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{F2F61744-A610-47C1-8D18-258D214AD0AD}" name="Actual Result" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{BB7F01C1-4CCB-48BB-B1AF-EC76036F7A50}" name="Status" dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{738EFE1E-9B5A-467D-B51A-FAE3C680984E}" name="Executed by" dataDxfId="47"/>
+    <tableColumn id="12" xr3:uid="{1CF50F8E-99F5-489F-9DDE-9E3702A3D89D}" name="Executed Date" dataDxfId="46"/>
+    <tableColumn id="13" xr3:uid="{9B03223D-6ED3-4549-9812-44F9B7FB9F5E}" name="Comments (Any)" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}" name="Table5" displayName="Table5" ref="A54:N58" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}" name="Table5" displayName="Table5" ref="A54:N58" totalsRowShown="0" headerRowDxfId="44" tableBorderDxfId="43">
   <autoFilter ref="A54:N58" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{314B3457-1047-4B97-8690-0FC0C7E63A1B}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{8959A1D5-A8D6-4050-B431-3851687F3ACC}" name="Test Scenario Description" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{A67188D0-2718-49A7-9C98-559566B5BE34}" name="Test Case ID" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{183B190A-4A91-4704-A29A-7C10A864D50D}" name="Test Case Description" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{7A4E1888-CA65-4F52-B8DF-9B408E40F16C}" name="Test Steps" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{6D584D05-96FA-4797-9ECD-0ED9575C801B}" name="Preconditions" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{66F6BE7C-A5F9-4754-814D-8B481CF9EFEA}" name="Test Data" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{AB5CBC21-875A-440D-9540-043ECA26AB57}" name="Post conditions" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{CBB06D44-CDEA-4E08-88B7-B4D1ECE1DE4B}" name="Expected Result" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{C8ABBDB4-2419-49CC-A91E-AB7491F28F90}" name="Actual Result" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{020B1BAD-98DF-459D-BEF2-5D317249BC9D}" name="Status" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{227321DB-D0BA-4E7D-AD16-B96E11598F32}" name="Executed by" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{9ACAB240-5794-4560-B26C-28738972BD58}" name="Executed Date" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{8943EAAB-FDBC-4C27-B51B-36476E6099B6}" name="Comments (Any)" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{8959A1D5-A8D6-4050-B431-3851687F3ACC}" name="Test Scenario Description" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{A67188D0-2718-49A7-9C98-559566B5BE34}" name="Test Case ID" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{183B190A-4A91-4704-A29A-7C10A864D50D}" name="Test Case Description" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{7A4E1888-CA65-4F52-B8DF-9B408E40F16C}" name="Test Steps" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{6D584D05-96FA-4797-9ECD-0ED9575C801B}" name="Preconditions" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{66F6BE7C-A5F9-4754-814D-8B481CF9EFEA}" name="Test Data" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{AB5CBC21-875A-440D-9540-043ECA26AB57}" name="Post conditions" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{CBB06D44-CDEA-4E08-88B7-B4D1ECE1DE4B}" name="Expected Result" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{C8ABBDB4-2419-49CC-A91E-AB7491F28F90}" name="Actual Result" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{020B1BAD-98DF-459D-BEF2-5D317249BC9D}" name="Status" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{227321DB-D0BA-4E7D-AD16-B96E11598F32}" name="Executed by" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{9ACAB240-5794-4560-B26C-28738972BD58}" name="Executed Date" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{8943EAAB-FDBC-4C27-B51B-36476E6099B6}" name="Comments (Any)" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}" name="Table59" displayName="Table59" ref="A68:N69" totalsRowShown="0" headerRowDxfId="29" tableBorderDxfId="28">
+  <autoFilter ref="A68:N69" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{8EA9A8A1-5263-4BA6-B939-0576AB70C56B}" name="Test Scenario ID"/>
+    <tableColumn id="2" xr3:uid="{A09BFAB6-F331-4553-89F5-F645B197E6E4}" name="Test Scenario Description" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{95CD5178-70C6-4029-953F-2BF330D539E9}" name="Test Case ID" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{F7B88AC7-FFC4-4BD9-ABF2-1F7387637638}" name="Test Case Description" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{EBAB9F15-3FB9-4ADA-BBE0-1B9863E0F75A}" name="Test Steps" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{317B7FB8-1C15-459D-84BE-5FF22CB5F1DA}" name="Preconditions" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{FE69F33E-245E-4967-9DA5-61661D9E9AE2}" name="Test Data" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{A638ACA4-6A84-474A-8B20-92270C496B28}" name="Post conditions" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{4C22FB79-3826-4059-B9D1-787B48B379DD}" name="Expected Result" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{6447313D-A350-4AE5-91A9-DFB9ECA1C3EF}" name="Actual Result" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{4342DDD7-CFD6-4F93-AF81-A9D957048D98}" name="Status" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{B8008DF3-60E3-493D-87C9-A6021F446EB7}" name="Executed by" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{FB1CC5CA-CB21-45DD-862E-9141FA956663}" name="Executed Date" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{E2201D2A-882B-4DDA-85CA-BEB8666A1674}" name="Comments (Any)" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}" name="Table57" displayName="Table57" ref="A79:N87" totalsRowShown="0" headerRowDxfId="14" tableBorderDxfId="13">
+  <autoFilter ref="A79:N87" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{9A85158C-C3D9-4D9C-BD2A-2B5772389099}" name="Test Scenario ID"/>
+    <tableColumn id="2" xr3:uid="{A94E9212-F76E-449A-8CA9-E193336BF565}" name="Test Scenario Description" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{6D6E821B-EFBF-487E-8EFD-65D718C427E4}" name="Test Case ID" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{747E0385-7511-4710-A360-A2B66EB42855}" name="Test Case Description" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{CC938E19-F87F-4452-919D-47E93CE148EA}" name="Test Steps" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{23D4BF6C-278D-4CB9-BE6F-689F8B058419}" name="Preconditions" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{023C0CBB-5E8E-4ED6-9B54-3D1CE6D1B758}" name="Test Data" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{BD6AE1D4-4907-417E-B61B-B9C56948AD74}" name="Post conditions" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{741D0EFD-8150-4F05-9134-06D25AB4E88F}" name="Expected Result" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{5E7DDCC4-7CA4-4051-B45C-1E497FA1C0ED}" name="Actual Result" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{B95FDC82-5F4D-4127-AB26-A07A18E3C44E}" name="Status" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{FDB1997D-3FD6-4316-9D6E-1E110EFC7217}" name="Executed by" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{1A04F9EA-D5D7-4856-AD37-257EEC2F87F0}" name="Executed Date" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{814E0251-0743-4E7B-A915-F8A9CC4917BE}" name="Comments (Any)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1725,7 +2467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -1835,7 +2577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
@@ -1879,7 +2621,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
@@ -2535,43 +3277,43 @@
       <c r="A42" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="23" t="s">
+      <c r="F42" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="23" t="s">
+      <c r="G42" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H42" s="23" t="s">
+      <c r="H42" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="I42" s="23" t="s">
+      <c r="I42" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="J42" s="23" t="s">
+      <c r="J42" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="K42" s="23" t="s">
+      <c r="K42" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="L42" s="23" t="s">
+      <c r="L42" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="M42" s="23" t="s">
+      <c r="M42" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="N42" s="23" t="s">
+      <c r="N42" s="22" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2706,46 +3448,46 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="24" t="s">
+      <c r="A54" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D54" s="25" t="s">
+      <c r="D54" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="25" t="s">
+      <c r="E54" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="F54" s="25" t="s">
+      <c r="F54" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="G54" s="25" t="s">
+      <c r="G54" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="H54" s="25" t="s">
+      <c r="H54" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="I54" s="25" t="s">
+      <c r="I54" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="J54" s="25" t="s">
+      <c r="J54" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="K54" s="25" t="s">
+      <c r="K54" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="L54" s="25" t="s">
+      <c r="L54" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="M54" s="25" t="s">
+      <c r="M54" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="N54" s="25" t="s">
+      <c r="N54" s="24" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2880,7 +3622,7 @@
       </c>
     </row>
     <row r="58" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="6" t="s">
         <v>125</v>
       </c>
       <c r="B58" s="14" t="s">
@@ -2920,15 +3662,579 @@
         <v>45643</v>
       </c>
       <c r="N58" s="14"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="1">
+        <v>45646</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="1">
+        <v>45646</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H68" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="J68" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="K68" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="L68" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="M68" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="N68" s="26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="169.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H69" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="I69" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="J69" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="K69" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L69" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M69" s="19">
+        <v>45646</v>
+      </c>
+      <c r="N69" s="14"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B73" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="1">
+        <v>45647</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" s="1">
+        <v>45646</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H79" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I79" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="J79" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="K79" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="L79" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="M79" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="N79" s="30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="180.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H80" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="I80" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K80" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L80" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M80" s="19">
+        <v>45647</v>
+      </c>
+      <c r="N80" s="14"/>
+    </row>
+    <row r="81" spans="1:14" ht="173.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="H81" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="I81" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="J81" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="K81" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L81" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M81" s="19">
+        <v>45648</v>
+      </c>
+      <c r="N81" s="14"/>
+    </row>
+    <row r="82" spans="1:14" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="H82" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="K82" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L82" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M82" s="19">
+        <v>45648</v>
+      </c>
+      <c r="N82" s="14"/>
+    </row>
+    <row r="83" spans="1:14" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E83" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="I83" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="K83" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L83" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M83" s="19">
+        <v>45650</v>
+      </c>
+      <c r="N83" s="14"/>
+    </row>
+    <row r="84" spans="1:14" ht="111.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="H84" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="I84" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="J84" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="K84" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L84" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M84" s="19">
+        <v>45650</v>
+      </c>
+      <c r="N84" s="14"/>
+    </row>
+    <row r="85" spans="1:14" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="H85" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="I85" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="J85" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="K85" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L85" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M85" s="19">
+        <v>45650</v>
+      </c>
+      <c r="N85" s="14"/>
+    </row>
+    <row r="86" spans="1:14" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="H86" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="I86" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="K86" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L86" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M86" s="19">
+        <v>45650</v>
+      </c>
+      <c r="N86" s="14"/>
+    </row>
+    <row r="87" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A87" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="E87" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="H87" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="I87" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="J87" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="K87" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L87" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M87" s="19">
+        <v>45650</v>
+      </c>
+      <c r="N87" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="4">
+  <tableParts count="6">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA60FAAD-B710-45A2-B8F2-AE32531C0C0D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6062BA37-B9DA-4A38-9549-0FA22DE3BEFB}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="216">
   <si>
     <t>Project Name</t>
   </si>
@@ -844,26 +843,29 @@
     <t>TC_FB_post_8</t>
   </si>
   <si>
+    <t>User should be able to react on posts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Facebook Post share Fucntionality </t>
+  </si>
+  <si>
+    <t>Share a post on Facebook</t>
+  </si>
+  <si>
     <t xml:space="preserve">01. Enter a valid username 
 02. Enter a valid password
 03. Click on Login Button
-04. React on comment
+04. Share a post
 </t>
   </si>
   <si>
-    <t>React on a comment of a Facebook post</t>
-  </si>
-  <si>
-    <t>User should be able to react on comments</t>
-  </si>
-  <si>
-    <t>User should be able to react on posts</t>
-  </si>
-  <si>
-    <t>React to comment</t>
-  </si>
-  <si>
-    <t>Reacting to comment</t>
+    <t>User should be able to share posts</t>
+  </si>
+  <si>
+    <t>Share posts</t>
+  </si>
+  <si>
+    <t>Sharing posts</t>
   </si>
 </sst>
 </file>
@@ -4038,7 +4040,7 @@
         <v>184</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I83" s="14" t="s">
         <v>185</v>
@@ -4188,31 +4190,31 @@
         <v>167</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>208</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F87" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G87" s="14" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K87" s="18" t="s">
         <v>96</v>
@@ -4221,7 +4223,7 @@
         <v>32</v>
       </c>
       <c r="M87" s="19">
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="N87" s="14"/>
     </row>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6062BA37-B9DA-4A38-9549-0FA22DE3BEFB}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D8B755-CD8D-49FD-8D6C-E9A98EB9C8E6}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="234">
   <si>
     <t>Project Name</t>
   </si>
@@ -867,12 +867,70 @@
   <si>
     <t>Sharing posts</t>
   </si>
+  <si>
+    <t>FaceBook Messaging</t>
+  </si>
+  <si>
+    <t>TS_FB_07</t>
+  </si>
+  <si>
+    <t>Verify that the user can send an emoji, GIF, or sticker</t>
+  </si>
+  <si>
+    <t>Verify that the user can send multiple messages in a conversation.</t>
+  </si>
+  <si>
+    <t>Verify that the user can send an image file via chat.</t>
+  </si>
+  <si>
+    <t>Verify that the user can send audio messages.</t>
+  </si>
+  <si>
+    <t>Verify that the user can send a file (PDF, DOC, etc.) via chat.</t>
+  </si>
+  <si>
+    <t>TC_FB_Msg_1</t>
+  </si>
+  <si>
+    <t>TC_FB_Msg_2</t>
+  </si>
+  <si>
+    <t>TC_FB_Msg_3</t>
+  </si>
+  <si>
+    <t>TC_FB_Msg_4</t>
+  </si>
+  <si>
+    <t>TC_FB_Msg_5</t>
+  </si>
+  <si>
+    <t>TC_FB_Msg_6</t>
+  </si>
+  <si>
+    <t>TC_FB_Msg_7</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Visit messages
+05. Send message</t>
+  </si>
+  <si>
+    <t>send a text message to a recipient.</t>
+  </si>
+  <si>
+    <t>Verify that the user can send a text message to a recipient.</t>
+  </si>
+  <si>
+    <t>User should be able to send a text message to a recipient.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -899,8 +957,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -940,6 +1013,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -985,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1065,11 +1144,478 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="92">
+  <dxfs count="108">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -2036,139 +2582,162 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}" name="Table4" displayName="Table4" ref="A8:N13" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}" name="Table4" displayName="Table4" ref="A8:N13" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
   <autoFilter ref="A8:N13" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{FA1520E5-151F-4C35-9564-490E6E227E63}" name="Test Scenario ID" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{4CD9CF72-D3D5-4E13-B21F-2628B71CA730}" name="Test Scenario Description" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{64C682F3-74F4-4B58-9AAA-079E2202EC63}" name="Test Case ID" dataDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{F8711D9F-D3E9-4C0E-83A5-1112EACF3ECF}" name="Test Case Description" dataDxfId="86"/>
-    <tableColumn id="5" xr3:uid="{3C9E830E-1C51-4CB9-9B33-8A5AFEEE698E}" name="Test Steps" dataDxfId="85"/>
-    <tableColumn id="13" xr3:uid="{795BF8D4-2BAA-4AD4-842A-88C791483F7A}" name="Preconditions" dataDxfId="84"/>
-    <tableColumn id="14" xr3:uid="{21B04C03-953D-42FE-8068-4BF43AFF3291}" name="Test Data" dataDxfId="83"/>
-    <tableColumn id="15" xr3:uid="{9CF2DA71-3D28-4A14-A4CE-044972166E7C}" name="Post conditions" dataDxfId="82"/>
-    <tableColumn id="6" xr3:uid="{42C30692-F71E-4898-A159-20BE875D8033}" name="Expected Result" dataDxfId="81"/>
-    <tableColumn id="7" xr3:uid="{03D56321-2D40-4418-8D06-EED641A4F370}" name="Actual Result" dataDxfId="80"/>
-    <tableColumn id="8" xr3:uid="{C0EAC999-BB87-4D0C-9360-9BFF9AF67768}" name="Status" dataDxfId="79"/>
-    <tableColumn id="9" xr3:uid="{3B92054E-DFF9-4A75-AF0B-7B5080A92062}" name="Executed by" dataDxfId="78"/>
-    <tableColumn id="10" xr3:uid="{E7860CF1-1E6C-471A-B8FB-6DB223239798}" name="Executed Date" dataDxfId="77"/>
-    <tableColumn id="11" xr3:uid="{D4382055-B4B2-40BA-B30A-2EE9840623E1}" name="Comments (Any)" dataDxfId="76"/>
+    <tableColumn id="1" xr3:uid="{FA1520E5-151F-4C35-9564-490E6E227E63}" name="Test Scenario ID" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{4CD9CF72-D3D5-4E13-B21F-2628B71CA730}" name="Test Scenario Description" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{64C682F3-74F4-4B58-9AAA-079E2202EC63}" name="Test Case ID" dataDxfId="103"/>
+    <tableColumn id="4" xr3:uid="{F8711D9F-D3E9-4C0E-83A5-1112EACF3ECF}" name="Test Case Description" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{3C9E830E-1C51-4CB9-9B33-8A5AFEEE698E}" name="Test Steps" dataDxfId="101"/>
+    <tableColumn id="13" xr3:uid="{795BF8D4-2BAA-4AD4-842A-88C791483F7A}" name="Preconditions" dataDxfId="100"/>
+    <tableColumn id="14" xr3:uid="{21B04C03-953D-42FE-8068-4BF43AFF3291}" name="Test Data" dataDxfId="99"/>
+    <tableColumn id="15" xr3:uid="{9CF2DA71-3D28-4A14-A4CE-044972166E7C}" name="Post conditions" dataDxfId="98"/>
+    <tableColumn id="6" xr3:uid="{42C30692-F71E-4898-A159-20BE875D8033}" name="Expected Result" dataDxfId="97"/>
+    <tableColumn id="7" xr3:uid="{03D56321-2D40-4418-8D06-EED641A4F370}" name="Actual Result" dataDxfId="96"/>
+    <tableColumn id="8" xr3:uid="{C0EAC999-BB87-4D0C-9360-9BFF9AF67768}" name="Status" dataDxfId="95"/>
+    <tableColumn id="9" xr3:uid="{3B92054E-DFF9-4A75-AF0B-7B5080A92062}" name="Executed by" dataDxfId="94"/>
+    <tableColumn id="10" xr3:uid="{E7860CF1-1E6C-471A-B8FB-6DB223239798}" name="Executed Date" dataDxfId="93"/>
+    <tableColumn id="11" xr3:uid="{D4382055-B4B2-40BA-B30A-2EE9840623E1}" name="Comments (Any)" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}" name="Table42" displayName="Table42" ref="A24:N32" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}" name="Table42" displayName="Table42" ref="A24:N32" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
   <autoFilter ref="A24:N32" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{B343AAFA-6457-4739-9100-101EF218F54D}" name="Test Scenario ID" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{E5529356-E16E-4EC4-9C43-4E830FC2E50F}" name="Test Scenario Description" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{2551A72A-8D4F-449F-B940-710504664FA5}" name="Test Case ID" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{00ECB93F-754B-43F5-9E43-F3D6BB21402C}" name="Test Case Description" dataDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{66E4AAFF-0A66-44A2-A53B-7FABEAD85F8D}" name="Test Steps" dataDxfId="69"/>
-    <tableColumn id="13" xr3:uid="{662ABFF6-2773-475F-B091-BCDABF3FB4DE}" name="Preconditions" dataDxfId="68"/>
-    <tableColumn id="14" xr3:uid="{671E1D04-8126-4597-BD89-AC9A178AC6EA}" name="Test Data" dataDxfId="67"/>
-    <tableColumn id="15" xr3:uid="{90971945-FDC9-429A-8527-A13B23E811A8}" name="Post conditions" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{EF04FFC6-AA15-47C8-B4A9-828B2777CD1D}" name="Expected Result" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{4CA89147-B985-4D56-876B-62F63DC92C49}" name="Actual Result" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{BDA4C2F1-0AF2-488C-953C-82660F211B43}" name="Status" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{EF661887-7461-490A-8D26-42708C7DEF3D}" name="Executed by" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{BD8FCAC9-00C9-4F76-A5CA-C0CB2DE0CB76}" name="Executed Date" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{C33D96A1-29CA-4A83-BFA6-64CF06278883}" name="Comments (Any)" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{B343AAFA-6457-4739-9100-101EF218F54D}" name="Test Scenario ID" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{E5529356-E16E-4EC4-9C43-4E830FC2E50F}" name="Test Scenario Description" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{2551A72A-8D4F-449F-B940-710504664FA5}" name="Test Case ID" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{00ECB93F-754B-43F5-9E43-F3D6BB21402C}" name="Test Case Description" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{66E4AAFF-0A66-44A2-A53B-7FABEAD85F8D}" name="Test Steps" dataDxfId="85"/>
+    <tableColumn id="13" xr3:uid="{662ABFF6-2773-475F-B091-BCDABF3FB4DE}" name="Preconditions" dataDxfId="84"/>
+    <tableColumn id="14" xr3:uid="{671E1D04-8126-4597-BD89-AC9A178AC6EA}" name="Test Data" dataDxfId="83"/>
+    <tableColumn id="15" xr3:uid="{90971945-FDC9-429A-8527-A13B23E811A8}" name="Post conditions" dataDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{EF04FFC6-AA15-47C8-B4A9-828B2777CD1D}" name="Expected Result" dataDxfId="81"/>
+    <tableColumn id="7" xr3:uid="{4CA89147-B985-4D56-876B-62F63DC92C49}" name="Actual Result" dataDxfId="80"/>
+    <tableColumn id="8" xr3:uid="{BDA4C2F1-0AF2-488C-953C-82660F211B43}" name="Status" dataDxfId="79"/>
+    <tableColumn id="9" xr3:uid="{EF661887-7461-490A-8D26-42708C7DEF3D}" name="Executed by" dataDxfId="78"/>
+    <tableColumn id="10" xr3:uid="{BD8FCAC9-00C9-4F76-A5CA-C0CB2DE0CB76}" name="Executed Date" dataDxfId="77"/>
+    <tableColumn id="11" xr3:uid="{C33D96A1-29CA-4A83-BFA6-64CF06278883}" name="Comments (Any)" dataDxfId="76"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}" name="Table3" displayName="Table3" ref="B42:N44" totalsRowShown="0" headerRowDxfId="59" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}" name="Table3" displayName="Table3" ref="B42:N44" totalsRowShown="0" headerRowDxfId="75" tableBorderDxfId="74">
   <autoFilter ref="B42:N44" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{1059CC3C-316E-4BE4-9F28-B883A79B86D2}" name="Test Scenario Description" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{EA041670-F9F4-43FB-A857-C38D44666E25}" name="Test Case ID" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{9B2E537F-3535-451E-BB48-220B1F6FFB7F}" name="Test Case Description" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{4769C369-46C1-44B9-930F-E23A6BA66DD9}" name="Test Steps" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{298DD112-4C8B-46B3-A446-0E6D93CB1BC8}" name="Preconditions" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{37B46AC9-16E7-4ED1-8C0B-ADAE9CAAB714}" name="Test Data" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{8A9B609E-0F77-49DB-AE71-A0094C3164A7}" name="Post conditions" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{0CD618D3-C88B-4295-8ECC-CD62E718B8E9}" name="Expected Result" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{F2F61744-A610-47C1-8D18-258D214AD0AD}" name="Actual Result" dataDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{BB7F01C1-4CCB-48BB-B1AF-EC76036F7A50}" name="Status" dataDxfId="48"/>
-    <tableColumn id="11" xr3:uid="{738EFE1E-9B5A-467D-B51A-FAE3C680984E}" name="Executed by" dataDxfId="47"/>
-    <tableColumn id="12" xr3:uid="{1CF50F8E-99F5-489F-9DDE-9E3702A3D89D}" name="Executed Date" dataDxfId="46"/>
-    <tableColumn id="13" xr3:uid="{9B03223D-6ED3-4549-9812-44F9B7FB9F5E}" name="Comments (Any)" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{1059CC3C-316E-4BE4-9F28-B883A79B86D2}" name="Test Scenario Description" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{EA041670-F9F4-43FB-A857-C38D44666E25}" name="Test Case ID" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{9B2E537F-3535-451E-BB48-220B1F6FFB7F}" name="Test Case Description" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{4769C369-46C1-44B9-930F-E23A6BA66DD9}" name="Test Steps" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{298DD112-4C8B-46B3-A446-0E6D93CB1BC8}" name="Preconditions" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{37B46AC9-16E7-4ED1-8C0B-ADAE9CAAB714}" name="Test Data" dataDxfId="68"/>
+    <tableColumn id="7" xr3:uid="{8A9B609E-0F77-49DB-AE71-A0094C3164A7}" name="Post conditions" dataDxfId="67"/>
+    <tableColumn id="8" xr3:uid="{0CD618D3-C88B-4295-8ECC-CD62E718B8E9}" name="Expected Result" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{F2F61744-A610-47C1-8D18-258D214AD0AD}" name="Actual Result" dataDxfId="65"/>
+    <tableColumn id="10" xr3:uid="{BB7F01C1-4CCB-48BB-B1AF-EC76036F7A50}" name="Status" dataDxfId="64"/>
+    <tableColumn id="11" xr3:uid="{738EFE1E-9B5A-467D-B51A-FAE3C680984E}" name="Executed by" dataDxfId="63"/>
+    <tableColumn id="12" xr3:uid="{1CF50F8E-99F5-489F-9DDE-9E3702A3D89D}" name="Executed Date" dataDxfId="62"/>
+    <tableColumn id="13" xr3:uid="{9B03223D-6ED3-4549-9812-44F9B7FB9F5E}" name="Comments (Any)" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}" name="Table5" displayName="Table5" ref="A54:N58" totalsRowShown="0" headerRowDxfId="44" tableBorderDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}" name="Table5" displayName="Table5" ref="A54:N58" totalsRowShown="0" headerRowDxfId="60" tableBorderDxfId="59">
   <autoFilter ref="A54:N58" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{314B3457-1047-4B97-8690-0FC0C7E63A1B}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{8959A1D5-A8D6-4050-B431-3851687F3ACC}" name="Test Scenario Description" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{A67188D0-2718-49A7-9C98-559566B5BE34}" name="Test Case ID" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{183B190A-4A91-4704-A29A-7C10A864D50D}" name="Test Case Description" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{7A4E1888-CA65-4F52-B8DF-9B408E40F16C}" name="Test Steps" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{6D584D05-96FA-4797-9ECD-0ED9575C801B}" name="Preconditions" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{66F6BE7C-A5F9-4754-814D-8B481CF9EFEA}" name="Test Data" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{AB5CBC21-875A-440D-9540-043ECA26AB57}" name="Post conditions" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{CBB06D44-CDEA-4E08-88B7-B4D1ECE1DE4B}" name="Expected Result" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{C8ABBDB4-2419-49CC-A91E-AB7491F28F90}" name="Actual Result" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{020B1BAD-98DF-459D-BEF2-5D317249BC9D}" name="Status" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{227321DB-D0BA-4E7D-AD16-B96E11598F32}" name="Executed by" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{9ACAB240-5794-4560-B26C-28738972BD58}" name="Executed Date" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{8943EAAB-FDBC-4C27-B51B-36476E6099B6}" name="Comments (Any)" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{8959A1D5-A8D6-4050-B431-3851687F3ACC}" name="Test Scenario Description" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{A67188D0-2718-49A7-9C98-559566B5BE34}" name="Test Case ID" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{183B190A-4A91-4704-A29A-7C10A864D50D}" name="Test Case Description" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{7A4E1888-CA65-4F52-B8DF-9B408E40F16C}" name="Test Steps" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{6D584D05-96FA-4797-9ECD-0ED9575C801B}" name="Preconditions" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{66F6BE7C-A5F9-4754-814D-8B481CF9EFEA}" name="Test Data" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{AB5CBC21-875A-440D-9540-043ECA26AB57}" name="Post conditions" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{CBB06D44-CDEA-4E08-88B7-B4D1ECE1DE4B}" name="Expected Result" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{C8ABBDB4-2419-49CC-A91E-AB7491F28F90}" name="Actual Result" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{020B1BAD-98DF-459D-BEF2-5D317249BC9D}" name="Status" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{227321DB-D0BA-4E7D-AD16-B96E11598F32}" name="Executed by" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{9ACAB240-5794-4560-B26C-28738972BD58}" name="Executed Date" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{8943EAAB-FDBC-4C27-B51B-36476E6099B6}" name="Comments (Any)" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}" name="Table59" displayName="Table59" ref="A68:N69" totalsRowShown="0" headerRowDxfId="29" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}" name="Table59" displayName="Table59" ref="A68:N69" totalsRowShown="0" headerRowDxfId="45" tableBorderDxfId="44">
   <autoFilter ref="A68:N69" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{8EA9A8A1-5263-4BA6-B939-0576AB70C56B}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{A09BFAB6-F331-4553-89F5-F645B197E6E4}" name="Test Scenario Description" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{95CD5178-70C6-4029-953F-2BF330D539E9}" name="Test Case ID" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{F7B88AC7-FFC4-4BD9-ABF2-1F7387637638}" name="Test Case Description" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{EBAB9F15-3FB9-4ADA-BBE0-1B9863E0F75A}" name="Test Steps" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{317B7FB8-1C15-459D-84BE-5FF22CB5F1DA}" name="Preconditions" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{FE69F33E-245E-4967-9DA5-61661D9E9AE2}" name="Test Data" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{A638ACA4-6A84-474A-8B20-92270C496B28}" name="Post conditions" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{4C22FB79-3826-4059-B9D1-787B48B379DD}" name="Expected Result" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{6447313D-A350-4AE5-91A9-DFB9ECA1C3EF}" name="Actual Result" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{4342DDD7-CFD6-4F93-AF81-A9D957048D98}" name="Status" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{B8008DF3-60E3-493D-87C9-A6021F446EB7}" name="Executed by" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{FB1CC5CA-CB21-45DD-862E-9141FA956663}" name="Executed Date" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{E2201D2A-882B-4DDA-85CA-BEB8666A1674}" name="Comments (Any)" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{A09BFAB6-F331-4553-89F5-F645B197E6E4}" name="Test Scenario Description" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{95CD5178-70C6-4029-953F-2BF330D539E9}" name="Test Case ID" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{F7B88AC7-FFC4-4BD9-ABF2-1F7387637638}" name="Test Case Description" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{EBAB9F15-3FB9-4ADA-BBE0-1B9863E0F75A}" name="Test Steps" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{317B7FB8-1C15-459D-84BE-5FF22CB5F1DA}" name="Preconditions" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{FE69F33E-245E-4967-9DA5-61661D9E9AE2}" name="Test Data" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{A638ACA4-6A84-474A-8B20-92270C496B28}" name="Post conditions" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{4C22FB79-3826-4059-B9D1-787B48B379DD}" name="Expected Result" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{6447313D-A350-4AE5-91A9-DFB9ECA1C3EF}" name="Actual Result" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{4342DDD7-CFD6-4F93-AF81-A9D957048D98}" name="Status" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{B8008DF3-60E3-493D-87C9-A6021F446EB7}" name="Executed by" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{FB1CC5CA-CB21-45DD-862E-9141FA956663}" name="Executed Date" dataDxfId="32"/>
+    <tableColumn id="14" xr3:uid="{E2201D2A-882B-4DDA-85CA-BEB8666A1674}" name="Comments (Any)" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}" name="Table57" displayName="Table57" ref="A79:N87" totalsRowShown="0" headerRowDxfId="14" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}" name="Table57" displayName="Table57" ref="A79:N87" totalsRowShown="0" headerRowDxfId="30" tableBorderDxfId="29">
   <autoFilter ref="A79:N87" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{9A85158C-C3D9-4D9C-BD2A-2B5772389099}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{A94E9212-F76E-449A-8CA9-E193336BF565}" name="Test Scenario Description" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{6D6E821B-EFBF-487E-8EFD-65D718C427E4}" name="Test Case ID" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{747E0385-7511-4710-A360-A2B66EB42855}" name="Test Case Description" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{CC938E19-F87F-4452-919D-47E93CE148EA}" name="Test Steps" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{23D4BF6C-278D-4CB9-BE6F-689F8B058419}" name="Preconditions" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{023C0CBB-5E8E-4ED6-9B54-3D1CE6D1B758}" name="Test Data" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{BD6AE1D4-4907-417E-B61B-B9C56948AD74}" name="Post conditions" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{741D0EFD-8150-4F05-9134-06D25AB4E88F}" name="Expected Result" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{5E7DDCC4-7CA4-4051-B45C-1E497FA1C0ED}" name="Actual Result" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{B95FDC82-5F4D-4127-AB26-A07A18E3C44E}" name="Status" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{FDB1997D-3FD6-4316-9D6E-1E110EFC7217}" name="Executed by" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{1A04F9EA-D5D7-4856-AD37-257EEC2F87F0}" name="Executed Date" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{814E0251-0743-4E7B-A915-F8A9CC4917BE}" name="Comments (Any)" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A94E9212-F76E-449A-8CA9-E193336BF565}" name="Test Scenario Description" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{6D6E821B-EFBF-487E-8EFD-65D718C427E4}" name="Test Case ID" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{747E0385-7511-4710-A360-A2B66EB42855}" name="Test Case Description" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{CC938E19-F87F-4452-919D-47E93CE148EA}" name="Test Steps" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{23D4BF6C-278D-4CB9-BE6F-689F8B058419}" name="Preconditions" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{023C0CBB-5E8E-4ED6-9B54-3D1CE6D1B758}" name="Test Data" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{BD6AE1D4-4907-417E-B61B-B9C56948AD74}" name="Post conditions" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{741D0EFD-8150-4F05-9134-06D25AB4E88F}" name="Expected Result" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{5E7DDCC4-7CA4-4051-B45C-1E497FA1C0ED}" name="Actual Result" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{B95FDC82-5F4D-4127-AB26-A07A18E3C44E}" name="Status" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{FDB1997D-3FD6-4316-9D6E-1E110EFC7217}" name="Executed by" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{1A04F9EA-D5D7-4856-AD37-257EEC2F87F0}" name="Executed Date" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{814E0251-0743-4E7B-A915-F8A9CC4917BE}" name="Comments (Any)" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N104" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="15">
+  <autoFilter ref="A97:N104" xr:uid="{579CEE6F-2BFF-4BA8-84B5-54FD3924CFE7}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{70CA3D9E-8ECA-4D8C-AB69-1087AC4F07B8}" name="Test Scenario ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{319399B1-33A1-4C16-AD15-4363C57C2DA0}" name="Test Scenario Description" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{BD9516DE-EFB6-45B5-90B8-97A92312EC6D}" name="Test Case ID" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{FA9382F4-41E9-425B-BE0D-0DFE248B76CC}" name="Test Case Description" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{E3B91FC0-33C0-42D3-884C-9898C818FB01}" name="Test Steps" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{826EF341-BA7F-42B6-ADD0-D1151A286FCB}" name="Preconditions" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{68A72ABC-F634-48C8-8145-DE769068807E}" name="Test Data" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{529801B7-1A06-40F1-8299-170161616A53}" name="Post conditions" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{68642ED6-B92A-489D-BF1E-5AD52EB0EDFB}" name="Expected Result" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{78C6ECC1-D57A-42EE-B74C-F356E5738487}" name="Actual Result" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{1D2F2D20-1615-4FE4-9961-49B9DA08014C}" name="Status" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{FBC3F02B-40C3-4F05-9308-70B55D3F01FA}" name="Executed by" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{805737BF-EFB1-41B6-AA4F-0C9913761E9A}" name="Executed Date" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{D471A4CD-F57D-448F-A88B-C9A1BC646C2E}" name="Comments (Any)" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2469,21 +3038,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" customWidth="1"/>
     <col min="5" max="5" width="29.6640625" customWidth="1"/>
     <col min="6" max="6" width="16.5546875" customWidth="1"/>
     <col min="7" max="7" width="21.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" customWidth="1"/>
     <col min="9" max="10" width="17.21875" customWidth="1"/>
     <col min="11" max="11" width="10.88671875" customWidth="1"/>
     <col min="12" max="12" width="19.5546875" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" customWidth="1"/>
     <col min="14" max="14" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4227,16 +4796,391 @@
       </c>
       <c r="N87" s="14"/>
     </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A90" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A91" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B91" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="1">
+        <v>45651</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A94" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="1">
+        <v>45651</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B97" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F97" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="H97" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="I97" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="J97" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="K97" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="L97" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="M97" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="N97" s="38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="C98" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="D98" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="E98" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="F98" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="H98" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="I98" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="J98" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="K98" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L98" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M98" s="36">
+        <v>45647</v>
+      </c>
+      <c r="N98" s="31"/>
+    </row>
+    <row r="99" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A99" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B99" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C99" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="D99" s="31"/>
+      <c r="E99" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="F99" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="H99" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="I99" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="J99" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="K99" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L99" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M99" s="36">
+        <v>45648</v>
+      </c>
+      <c r="N99" s="31"/>
+    </row>
+    <row r="100" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A100" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B100" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="C100" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="F100" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G100" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="H100" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I100" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J100" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="K100" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L100" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M100" s="36">
+        <v>45648</v>
+      </c>
+      <c r="N100" s="31"/>
+    </row>
+    <row r="101" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A101" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B101" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="C101" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="D101" s="31"/>
+      <c r="E101" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="F101" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="H101" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I101" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J101" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="K101" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L101" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M101" s="36">
+        <v>45649</v>
+      </c>
+      <c r="N101" s="31"/>
+    </row>
+    <row r="102" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A102" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B102" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="C102" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="D102" s="31"/>
+      <c r="E102" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="F102" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G102" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="H102" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I102" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J102" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="K102" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L102" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M102" s="36">
+        <v>45650</v>
+      </c>
+      <c r="N102" s="31"/>
+    </row>
+    <row r="103" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A103" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B103" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C103" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D103" s="31"/>
+      <c r="E103" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="F103" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="H103" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I103" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J103" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="K103" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L103" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M103" s="36">
+        <v>45651</v>
+      </c>
+      <c r="N103" s="31"/>
+    </row>
+    <row r="104" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A104" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B104" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="C104" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="D104" s="31"/>
+      <c r="E104" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="F104" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="H104" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I104" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J104" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="K104" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L104" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M104" s="36">
+        <v>45652</v>
+      </c>
+      <c r="N104" s="31"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="6">
+  <tableParts count="7">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D8B755-CD8D-49FD-8D6C-E9A98EB9C8E6}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97A24F8-3A4A-4E39-BB0B-99327EE17A61}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="239">
   <si>
     <t>Project Name</t>
   </si>
@@ -874,9 +874,6 @@
     <t>TS_FB_07</t>
   </si>
   <si>
-    <t>Verify that the user can send an emoji, GIF, or sticker</t>
-  </si>
-  <si>
     <t>Verify that the user can send multiple messages in a conversation.</t>
   </si>
   <si>
@@ -924,6 +921,40 @@
   </si>
   <si>
     <t>User should be able to send a text message to a recipient.</t>
+  </si>
+  <si>
+    <t>Verify that the user can send an emoji or sticker</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Visit messages
+05. Type text message
+06. Click on send button</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Visit messages
+05. Select emoji and sticker
+06. Click on send button</t>
+  </si>
+  <si>
+    <t>send a sticker or emoji to a recipient.</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Message - "This is a test message from KAVISHKA"</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Message - "This is a test message from KAVISHKA"
+Emoji
+Sticker</t>
   </si>
 </sst>
 </file>
@@ -1173,6 +1204,426 @@
   <dxfs count="108">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -1195,426 +1646,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2719,23 +2750,23 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N104" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N104" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="A97:N104" xr:uid="{579CEE6F-2BFF-4BA8-84B5-54FD3924CFE7}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{70CA3D9E-8ECA-4D8C-AB69-1087AC4F07B8}" name="Test Scenario ID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{319399B1-33A1-4C16-AD15-4363C57C2DA0}" name="Test Scenario Description" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{BD9516DE-EFB6-45B5-90B8-97A92312EC6D}" name="Test Case ID" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{FA9382F4-41E9-425B-BE0D-0DFE248B76CC}" name="Test Case Description" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{E3B91FC0-33C0-42D3-884C-9898C818FB01}" name="Test Steps" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{826EF341-BA7F-42B6-ADD0-D1151A286FCB}" name="Preconditions" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{68A72ABC-F634-48C8-8145-DE769068807E}" name="Test Data" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{529801B7-1A06-40F1-8299-170161616A53}" name="Post conditions" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{68642ED6-B92A-489D-BF1E-5AD52EB0EDFB}" name="Expected Result" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{78C6ECC1-D57A-42EE-B74C-F356E5738487}" name="Actual Result" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{1D2F2D20-1615-4FE4-9961-49B9DA08014C}" name="Status" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{FBC3F02B-40C3-4F05-9308-70B55D3F01FA}" name="Executed by" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{805737BF-EFB1-41B6-AA4F-0C9913761E9A}" name="Executed Date" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{D471A4CD-F57D-448F-A88B-C9A1BC646C2E}" name="Comments (Any)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{70CA3D9E-8ECA-4D8C-AB69-1087AC4F07B8}" name="Test Scenario ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{319399B1-33A1-4C16-AD15-4363C57C2DA0}" name="Test Scenario Description" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{BD9516DE-EFB6-45B5-90B8-97A92312EC6D}" name="Test Case ID" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{FA9382F4-41E9-425B-BE0D-0DFE248B76CC}" name="Test Case Description" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{E3B91FC0-33C0-42D3-884C-9898C818FB01}" name="Test Steps" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{826EF341-BA7F-42B6-ADD0-D1151A286FCB}" name="Preconditions" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{68A72ABC-F634-48C8-8145-DE769068807E}" name="Test Data" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{529801B7-1A06-40F1-8299-170161616A53}" name="Post conditions" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{68642ED6-B92A-489D-BF1E-5AD52EB0EDFB}" name="Expected Result" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{78C6ECC1-D57A-42EE-B74C-F356E5738487}" name="Actual Result" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{1D2F2D20-1615-4FE4-9961-49B9DA08014C}" name="Status" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{FBC3F02B-40C3-4F05-9308-70B55D3F01FA}" name="Executed by" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{805737BF-EFB1-41B6-AA4F-0C9913761E9A}" name="Executed Date" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{D471A4CD-F57D-448F-A88B-C9A1BC646C2E}" name="Comments (Any)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4888,36 +4919,36 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A98" s="35" t="s">
         <v>217</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D98" s="31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F98" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G98" s="31" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="H98" s="34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I98" s="31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J98" s="31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K98" s="35" t="s">
         <v>96</v>
@@ -4926,29 +4957,31 @@
         <v>32</v>
       </c>
       <c r="M98" s="36">
-        <v>45647</v>
+        <v>45655</v>
       </c>
       <c r="N98" s="31"/>
     </row>
-    <row r="99" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="35" t="s">
         <v>217</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="C99" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="D99" s="31"/>
+        <v>223</v>
+      </c>
+      <c r="D99" s="31" t="s">
+        <v>236</v>
+      </c>
       <c r="E99" s="31" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F99" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G99" s="31" t="s">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="H99" s="34" t="s">
         <v>171</v>
@@ -4966,23 +4999,23 @@
         <v>32</v>
       </c>
       <c r="M99" s="36">
-        <v>45648</v>
+        <v>45656</v>
       </c>
       <c r="N99" s="31"/>
     </row>
-    <row r="100" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="35" t="s">
         <v>217</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C100" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D100" s="31"/>
       <c r="E100" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F100" s="33" t="s">
         <v>33</v>
@@ -5015,14 +5048,14 @@
         <v>217</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C101" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D101" s="31"/>
       <c r="E101" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F101" s="33" t="s">
         <v>33</v>
@@ -5055,14 +5088,14 @@
         <v>217</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C102" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D102" s="31"/>
       <c r="E102" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F102" s="33" t="s">
         <v>33</v>
@@ -5095,14 +5128,14 @@
         <v>217</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C103" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D103" s="31"/>
       <c r="E103" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F103" s="33" t="s">
         <v>33</v>
@@ -5135,14 +5168,14 @@
         <v>217</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C104" s="32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D104" s="31"/>
       <c r="E104" s="31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F104" s="33" t="s">
         <v>33</v>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97A24F8-3A4A-4E39-BB0B-99327EE17A61}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEAA648-709D-4992-9B58-A6EF5DD81CBE}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="255">
   <si>
     <t>Project Name</t>
   </si>
@@ -883,9 +883,6 @@
     <t>Verify that the user can send audio messages.</t>
   </si>
   <si>
-    <t>Verify that the user can send a file (PDF, DOC, etc.) via chat.</t>
-  </si>
-  <si>
     <t>TC_FB_Msg_1</t>
   </si>
   <si>
@@ -899,19 +896,6 @@
   </si>
   <si>
     <t>TC_FB_Msg_5</t>
-  </si>
-  <si>
-    <t>TC_FB_Msg_6</t>
-  </si>
-  <si>
-    <t>TC_FB_Msg_7</t>
-  </si>
-  <si>
-    <t>01. Enter a valid username 
-02. Enter a valid password
-03. Click on Login Button
-04. Visit messages
-05. Send message</t>
   </si>
   <si>
     <t>send a text message to a recipient.</t>
@@ -934,27 +918,115 @@
 06. Click on send button</t>
   </si>
   <si>
+    <t>send a sticker or emoji to a recipient.</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Message - "This is a test message from KAVISHKA"</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Message - "This is a test message from KAVISHKA"
+Emoji
+Sticker</t>
+  </si>
+  <si>
+    <t>send multiple messages in a conversation.</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Visit messages
+05. Type multiple text messages
+06. Click on send button</t>
+  </si>
+  <si>
+    <t>User should be able to send multiple messages in a conversation</t>
+  </si>
+  <si>
+    <t>User should be able to send an emoji or sticker to a recipient.</t>
+  </si>
+  <si>
+    <t>send an emoji or sticker to a recipient.</t>
+  </si>
+  <si>
+    <t>sending an emoji or sticker to a recipient.</t>
+  </si>
+  <si>
+    <t>send multiple messages  to a recipient in a conversation.</t>
+  </si>
+  <si>
+    <t>sending multiple messages  to a recipient in a conversation.</t>
+  </si>
+  <si>
+    <t>send an image file to a recipient.</t>
+  </si>
+  <si>
+    <t>User should be able to send an image file in a conversation</t>
+  </si>
+  <si>
+    <t>sending an image file to a recipient.</t>
+  </si>
+  <si>
+    <t>send a audio message to a recipient.</t>
+  </si>
+  <si>
+    <t>User should be able to send a audio message in a conversation</t>
+  </si>
+  <si>
+    <t>send a audio message  to a recipient.</t>
+  </si>
+  <si>
+    <t>sending a audio message  to a recipient.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username - jigiwi7156@jofuso.com
+Password - Celkon
+Message - "This is a test message from KAVISHKA"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username - jigiwi7156@jofuso.com
+Password - Celkon
+Message - "This is a test message from KAVISHKA"
+Photo
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username - jigiwi7156@jofuso.com
+Password - Celkon
+Message - "This is a test message from KAVISHKA"
+Audio
+</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Visit messages
+05. Click on upload image
+06. Choose a image
+07. Send message</t>
+  </si>
+  <si>
     <t>01. Enter a valid username 
 02. Enter a valid password
 03. Click on Login Button
 04. Visit messages
 05. Select emoji and sticker
-06. Click on send button</t>
-  </si>
-  <si>
-    <t>send a sticker or emoji to a recipient.</t>
-  </si>
-  <si>
-    <t>Username - jigiwi7156@jofuso.com
-Password - Celkon
-Message - "This is a test message from KAVISHKA"</t>
-  </si>
-  <si>
-    <t>Username - jigiwi7156@jofuso.com
-Password - Celkon
-Message - "This is a test message from KAVISHKA"
-Emoji
-Sticker</t>
+06. Choose a sticker
+07. Click on send button</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Visit messages
+05. Click on upload audio
+06. Send message</t>
   </si>
 </sst>
 </file>
@@ -2750,8 +2822,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N104" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14">
-  <autoFilter ref="A97:N104" xr:uid="{579CEE6F-2BFF-4BA8-84B5-54FD3924CFE7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N102" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14">
+  <autoFilter ref="A97:N102" xr:uid="{579CEE6F-2BFF-4BA8-84B5-54FD3924CFE7}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{70CA3D9E-8ECA-4D8C-AB69-1087AC4F07B8}" name="Test Scenario ID" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{319399B1-33A1-4C16-AD15-4363C57C2DA0}" name="Test Scenario Description" dataDxfId="12"/>
@@ -3069,7 +3141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -4872,7 +4944,7 @@
         <v>5</v>
       </c>
       <c r="B95" s="1">
-        <v>45651</v>
+        <v>45293</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
@@ -4919,36 +4991,36 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="35" t="s">
         <v>217</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D98" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="E98" s="31" t="s">
         <v>230</v>
-      </c>
-      <c r="E98" s="31" t="s">
-        <v>234</v>
       </c>
       <c r="F98" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G98" s="31" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H98" s="34" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I98" s="31" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J98" s="31" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="K98" s="35" t="s">
         <v>96</v>
@@ -4966,31 +5038,31 @@
         <v>217</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C99" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D99" s="31" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="F99" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G99" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="H99" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="I99" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="H99" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="I99" s="31" t="s">
-        <v>177</v>
-      </c>
       <c r="J99" s="31" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="K99" s="35" t="s">
         <v>96</v>
@@ -5003,7 +5075,7 @@
       </c>
       <c r="N99" s="31"/>
     </row>
-    <row r="100" spans="1:14" ht="114" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="35" t="s">
         <v>217</v>
       </c>
@@ -5011,26 +5083,28 @@
         <v>218</v>
       </c>
       <c r="C100" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="D100" s="31"/>
+        <v>223</v>
+      </c>
+      <c r="D100" s="31" t="s">
+        <v>234</v>
+      </c>
       <c r="E100" s="31" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F100" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G100" s="31" t="s">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="H100" s="34" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="I100" s="31" t="s">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="J100" s="31" t="s">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="K100" s="35" t="s">
         <v>96</v>
@@ -5039,11 +5113,11 @@
         <v>32</v>
       </c>
       <c r="M100" s="36">
-        <v>45648</v>
+        <v>45659</v>
       </c>
       <c r="N100" s="31"/>
     </row>
-    <row r="101" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="35" t="s">
         <v>217</v>
       </c>
@@ -5051,26 +5125,28 @@
         <v>219</v>
       </c>
       <c r="C101" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D101" s="31"/>
+        <v>224</v>
+      </c>
+      <c r="D101" s="31" t="s">
+        <v>242</v>
+      </c>
       <c r="E101" s="31" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F101" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G101" s="31" t="s">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="H101" s="34" t="s">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="I101" s="31" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="J101" s="31" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="K101" s="35" t="s">
         <v>96</v>
@@ -5079,38 +5155,40 @@
         <v>32</v>
       </c>
       <c r="M101" s="36">
-        <v>45649</v>
+        <v>45659</v>
       </c>
       <c r="N101" s="31"/>
     </row>
-    <row r="102" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="35" t="s">
         <v>217</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C102" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="D102" s="31"/>
+        <v>225</v>
+      </c>
+      <c r="D102" s="31" t="s">
+        <v>245</v>
+      </c>
       <c r="E102" s="31" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="F102" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G102" s="31" t="s">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="H102" s="34" t="s">
-        <v>174</v>
+        <v>246</v>
       </c>
       <c r="I102" s="31" t="s">
-        <v>175</v>
+        <v>247</v>
       </c>
       <c r="J102" s="31" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="K102" s="35" t="s">
         <v>96</v>
@@ -5119,90 +5197,11 @@
         <v>32</v>
       </c>
       <c r="M102" s="36">
-        <v>45650</v>
+        <v>45659</v>
       </c>
       <c r="N102" s="31"/>
     </row>
-    <row r="103" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A103" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="B103" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="C103" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="D103" s="31"/>
-      <c r="E103" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="F103" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="G103" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="H103" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="I103" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="J103" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="K103" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="L103" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="M103" s="36">
-        <v>45651</v>
-      </c>
-      <c r="N103" s="31"/>
-    </row>
-    <row r="104" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A104" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="B104" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="C104" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="D104" s="31"/>
-      <c r="E104" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="F104" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="G104" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="H104" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="I104" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="J104" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="K104" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="L104" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="M104" s="36">
-        <v>45652</v>
-      </c>
-      <c r="N104" s="31"/>
-    </row>
+    <row r="103" spans="1:14" ht="103.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEAA648-709D-4992-9B58-A6EF5DD81CBE}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1E31E1-8F56-4352-B12F-5D0CE27B66A3}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="296">
   <si>
     <t>Project Name</t>
   </si>
@@ -1027,6 +1027,173 @@
 04. Visit messages
 05. Click on upload audio
 06. Send message</t>
+  </si>
+  <si>
+    <t>FaceBook Friends</t>
+  </si>
+  <si>
+    <t>TS_FB_08</t>
+  </si>
+  <si>
+    <t>TC_FB_Friends_1</t>
+  </si>
+  <si>
+    <t>Verify Send Friend Request</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04.Search for a user by name in the search bar.
+05.Click on the user's profile from the search results.
+06.Locate and click the "Add Friend" button on the user's profile page.
+07.Verify that the button text changes to "Friend Request Sent.</t>
+  </si>
+  <si>
+    <t>The friend request is sent successfully, and the button text should change to "Friend Request Sent."</t>
+  </si>
+  <si>
+    <t>User should be able to send a friend request .</t>
+  </si>
+  <si>
+    <t>TC_FB_Friends_2</t>
+  </si>
+  <si>
+    <t>TC_FB_Friends_3</t>
+  </si>
+  <si>
+    <t>TC_FB_Friends_4</t>
+  </si>
+  <si>
+    <t>TC_FB_Friends_5</t>
+  </si>
+  <si>
+    <t>Verify Accept Friend Request</t>
+  </si>
+  <si>
+    <t>User successfully accept the friend request, and the status should change to "Friends."</t>
+  </si>
+  <si>
+    <t>User should be able to accept the friend request.</t>
+  </si>
+  <si>
+    <t>Ensure that a user can successfully send a friend request to another user.</t>
+  </si>
+  <si>
+    <t>Ensure that a user can accept a friend request from another user.</t>
+  </si>
+  <si>
+    <t>Verify Unfriend Functionality</t>
+  </si>
+  <si>
+    <t>Ensure that a user can remove a friend from their friend list.</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Find a friend you wish to unfriend.
+05.Click on the "Friends" button next to their name.
+06.Select "Unfriend" from the dropdown.
+07.Verify that the "Add Friend" button now appears next to their name instead of "Friends."</t>
+  </si>
+  <si>
+    <t>The user successfully unfriended and the button should change back to "Add Friend."</t>
+  </si>
+  <si>
+    <t>User should be successfully unfriended.</t>
+  </si>
+  <si>
+    <t>Verify that the user can View Friend Suggestions</t>
+  </si>
+  <si>
+    <t>Ensure that the friend suggestions section is visible and displays recommendations to user.</t>
+  </si>
+  <si>
+    <t>A list of friend suggestions should appear, showing people the user might know.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be able to  View Friend Suggestions </t>
+  </si>
+  <si>
+    <t>TC_FB_Friends_6</t>
+  </si>
+  <si>
+    <t>Ensure that the  the user's friends list is visible and accessible.</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Navigate to the "Friends" section.
+05.Click on the "Suggestions" section</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Navigate to the "Friends" section.
+05.Click on the "All Friends" section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The friends list should be displayed with the names and profile pictures of friends.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can View Friends List
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be able to View Friends List
+</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+jegoh94617@konican.com
+celkon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username - jigiwi7156@jofuso.com
+Password - Celkon
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04.Send a friend request to another user (User B).
+05.Login to User B's Facebook account.
+06.Navigate to the "Friend Requests" section.
+07.Click "Confirm" on the pending request from User A.
+08. Visit to User A's Profile
+08.Verify that the "Respond" button is replaced with "Friends."
+</t>
+  </si>
+  <si>
+    <t>Verify Remove Friend Request</t>
+  </si>
+  <si>
+    <t>Ensure that a user can Remove a pending friend request.</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04.Send a friend request to another user (User B).
+05.Login to User B's Facebook account.
+06.Navigate to the "Friend Requests" section.
+07.Click "Delete" or "Remove" on the request from User A.
+08.Verify that the friend request is removed and no longer appears in the "Friend Requests" section.</t>
+  </si>
+  <si>
+    <t>User should be able to Remove a pending friend request.</t>
+  </si>
+  <si>
+    <t>The friend request should be Removed, and no connection should be made between the two users..</t>
+  </si>
+  <si>
+    <t>The friend request is Removed, and no connection should be made between the two users..</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1243,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1125,6 +1292,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72DC0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1167,7 +1340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1269,11 +1442,460 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="108">
+  <dxfs count="124">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC72DC0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2673,6 +3295,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC72DC0"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2685,160 +3312,183 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}" name="Table4" displayName="Table4" ref="A8:N13" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}" name="Table4" displayName="Table4" ref="A8:N13" totalsRowShown="0" headerRowDxfId="123" dataDxfId="122">
   <autoFilter ref="A8:N13" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{FA1520E5-151F-4C35-9564-490E6E227E63}" name="Test Scenario ID" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{4CD9CF72-D3D5-4E13-B21F-2628B71CA730}" name="Test Scenario Description" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{64C682F3-74F4-4B58-9AAA-079E2202EC63}" name="Test Case ID" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{F8711D9F-D3E9-4C0E-83A5-1112EACF3ECF}" name="Test Case Description" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{3C9E830E-1C51-4CB9-9B33-8A5AFEEE698E}" name="Test Steps" dataDxfId="101"/>
-    <tableColumn id="13" xr3:uid="{795BF8D4-2BAA-4AD4-842A-88C791483F7A}" name="Preconditions" dataDxfId="100"/>
-    <tableColumn id="14" xr3:uid="{21B04C03-953D-42FE-8068-4BF43AFF3291}" name="Test Data" dataDxfId="99"/>
-    <tableColumn id="15" xr3:uid="{9CF2DA71-3D28-4A14-A4CE-044972166E7C}" name="Post conditions" dataDxfId="98"/>
-    <tableColumn id="6" xr3:uid="{42C30692-F71E-4898-A159-20BE875D8033}" name="Expected Result" dataDxfId="97"/>
-    <tableColumn id="7" xr3:uid="{03D56321-2D40-4418-8D06-EED641A4F370}" name="Actual Result" dataDxfId="96"/>
-    <tableColumn id="8" xr3:uid="{C0EAC999-BB87-4D0C-9360-9BFF9AF67768}" name="Status" dataDxfId="95"/>
-    <tableColumn id="9" xr3:uid="{3B92054E-DFF9-4A75-AF0B-7B5080A92062}" name="Executed by" dataDxfId="94"/>
-    <tableColumn id="10" xr3:uid="{E7860CF1-1E6C-471A-B8FB-6DB223239798}" name="Executed Date" dataDxfId="93"/>
-    <tableColumn id="11" xr3:uid="{D4382055-B4B2-40BA-B30A-2EE9840623E1}" name="Comments (Any)" dataDxfId="92"/>
+    <tableColumn id="1" xr3:uid="{FA1520E5-151F-4C35-9564-490E6E227E63}" name="Test Scenario ID" dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{4CD9CF72-D3D5-4E13-B21F-2628B71CA730}" name="Test Scenario Description" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{64C682F3-74F4-4B58-9AAA-079E2202EC63}" name="Test Case ID" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{F8711D9F-D3E9-4C0E-83A5-1112EACF3ECF}" name="Test Case Description" dataDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{3C9E830E-1C51-4CB9-9B33-8A5AFEEE698E}" name="Test Steps" dataDxfId="117"/>
+    <tableColumn id="13" xr3:uid="{795BF8D4-2BAA-4AD4-842A-88C791483F7A}" name="Preconditions" dataDxfId="116"/>
+    <tableColumn id="14" xr3:uid="{21B04C03-953D-42FE-8068-4BF43AFF3291}" name="Test Data" dataDxfId="115"/>
+    <tableColumn id="15" xr3:uid="{9CF2DA71-3D28-4A14-A4CE-044972166E7C}" name="Post conditions" dataDxfId="114"/>
+    <tableColumn id="6" xr3:uid="{42C30692-F71E-4898-A159-20BE875D8033}" name="Expected Result" dataDxfId="113"/>
+    <tableColumn id="7" xr3:uid="{03D56321-2D40-4418-8D06-EED641A4F370}" name="Actual Result" dataDxfId="112"/>
+    <tableColumn id="8" xr3:uid="{C0EAC999-BB87-4D0C-9360-9BFF9AF67768}" name="Status" dataDxfId="111"/>
+    <tableColumn id="9" xr3:uid="{3B92054E-DFF9-4A75-AF0B-7B5080A92062}" name="Executed by" dataDxfId="110"/>
+    <tableColumn id="10" xr3:uid="{E7860CF1-1E6C-471A-B8FB-6DB223239798}" name="Executed Date" dataDxfId="109"/>
+    <tableColumn id="11" xr3:uid="{D4382055-B4B2-40BA-B30A-2EE9840623E1}" name="Comments (Any)" dataDxfId="108"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}" name="Table42" displayName="Table42" ref="A24:N32" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}" name="Table42" displayName="Table42" ref="A24:N32" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
   <autoFilter ref="A24:N32" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{B343AAFA-6457-4739-9100-101EF218F54D}" name="Test Scenario ID" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{E5529356-E16E-4EC4-9C43-4E830FC2E50F}" name="Test Scenario Description" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{2551A72A-8D4F-449F-B940-710504664FA5}" name="Test Case ID" dataDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{00ECB93F-754B-43F5-9E43-F3D6BB21402C}" name="Test Case Description" dataDxfId="86"/>
-    <tableColumn id="5" xr3:uid="{66E4AAFF-0A66-44A2-A53B-7FABEAD85F8D}" name="Test Steps" dataDxfId="85"/>
-    <tableColumn id="13" xr3:uid="{662ABFF6-2773-475F-B091-BCDABF3FB4DE}" name="Preconditions" dataDxfId="84"/>
-    <tableColumn id="14" xr3:uid="{671E1D04-8126-4597-BD89-AC9A178AC6EA}" name="Test Data" dataDxfId="83"/>
-    <tableColumn id="15" xr3:uid="{90971945-FDC9-429A-8527-A13B23E811A8}" name="Post conditions" dataDxfId="82"/>
-    <tableColumn id="6" xr3:uid="{EF04FFC6-AA15-47C8-B4A9-828B2777CD1D}" name="Expected Result" dataDxfId="81"/>
-    <tableColumn id="7" xr3:uid="{4CA89147-B985-4D56-876B-62F63DC92C49}" name="Actual Result" dataDxfId="80"/>
-    <tableColumn id="8" xr3:uid="{BDA4C2F1-0AF2-488C-953C-82660F211B43}" name="Status" dataDxfId="79"/>
-    <tableColumn id="9" xr3:uid="{EF661887-7461-490A-8D26-42708C7DEF3D}" name="Executed by" dataDxfId="78"/>
-    <tableColumn id="10" xr3:uid="{BD8FCAC9-00C9-4F76-A5CA-C0CB2DE0CB76}" name="Executed Date" dataDxfId="77"/>
-    <tableColumn id="11" xr3:uid="{C33D96A1-29CA-4A83-BFA6-64CF06278883}" name="Comments (Any)" dataDxfId="76"/>
+    <tableColumn id="1" xr3:uid="{B343AAFA-6457-4739-9100-101EF218F54D}" name="Test Scenario ID" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{E5529356-E16E-4EC4-9C43-4E830FC2E50F}" name="Test Scenario Description" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{2551A72A-8D4F-449F-B940-710504664FA5}" name="Test Case ID" dataDxfId="103"/>
+    <tableColumn id="4" xr3:uid="{00ECB93F-754B-43F5-9E43-F3D6BB21402C}" name="Test Case Description" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{66E4AAFF-0A66-44A2-A53B-7FABEAD85F8D}" name="Test Steps" dataDxfId="101"/>
+    <tableColumn id="13" xr3:uid="{662ABFF6-2773-475F-B091-BCDABF3FB4DE}" name="Preconditions" dataDxfId="100"/>
+    <tableColumn id="14" xr3:uid="{671E1D04-8126-4597-BD89-AC9A178AC6EA}" name="Test Data" dataDxfId="99"/>
+    <tableColumn id="15" xr3:uid="{90971945-FDC9-429A-8527-A13B23E811A8}" name="Post conditions" dataDxfId="98"/>
+    <tableColumn id="6" xr3:uid="{EF04FFC6-AA15-47C8-B4A9-828B2777CD1D}" name="Expected Result" dataDxfId="97"/>
+    <tableColumn id="7" xr3:uid="{4CA89147-B985-4D56-876B-62F63DC92C49}" name="Actual Result" dataDxfId="96"/>
+    <tableColumn id="8" xr3:uid="{BDA4C2F1-0AF2-488C-953C-82660F211B43}" name="Status" dataDxfId="95"/>
+    <tableColumn id="9" xr3:uid="{EF661887-7461-490A-8D26-42708C7DEF3D}" name="Executed by" dataDxfId="94"/>
+    <tableColumn id="10" xr3:uid="{BD8FCAC9-00C9-4F76-A5CA-C0CB2DE0CB76}" name="Executed Date" dataDxfId="93"/>
+    <tableColumn id="11" xr3:uid="{C33D96A1-29CA-4A83-BFA6-64CF06278883}" name="Comments (Any)" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}" name="Table3" displayName="Table3" ref="B42:N44" totalsRowShown="0" headerRowDxfId="75" tableBorderDxfId="74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}" name="Table3" displayName="Table3" ref="B42:N44" totalsRowShown="0" headerRowDxfId="91" tableBorderDxfId="90">
   <autoFilter ref="B42:N44" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{1059CC3C-316E-4BE4-9F28-B883A79B86D2}" name="Test Scenario Description" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{EA041670-F9F4-43FB-A857-C38D44666E25}" name="Test Case ID" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{9B2E537F-3535-451E-BB48-220B1F6FFB7F}" name="Test Case Description" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{4769C369-46C1-44B9-930F-E23A6BA66DD9}" name="Test Steps" dataDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{298DD112-4C8B-46B3-A446-0E6D93CB1BC8}" name="Preconditions" dataDxfId="69"/>
-    <tableColumn id="6" xr3:uid="{37B46AC9-16E7-4ED1-8C0B-ADAE9CAAB714}" name="Test Data" dataDxfId="68"/>
-    <tableColumn id="7" xr3:uid="{8A9B609E-0F77-49DB-AE71-A0094C3164A7}" name="Post conditions" dataDxfId="67"/>
-    <tableColumn id="8" xr3:uid="{0CD618D3-C88B-4295-8ECC-CD62E718B8E9}" name="Expected Result" dataDxfId="66"/>
-    <tableColumn id="9" xr3:uid="{F2F61744-A610-47C1-8D18-258D214AD0AD}" name="Actual Result" dataDxfId="65"/>
-    <tableColumn id="10" xr3:uid="{BB7F01C1-4CCB-48BB-B1AF-EC76036F7A50}" name="Status" dataDxfId="64"/>
-    <tableColumn id="11" xr3:uid="{738EFE1E-9B5A-467D-B51A-FAE3C680984E}" name="Executed by" dataDxfId="63"/>
-    <tableColumn id="12" xr3:uid="{1CF50F8E-99F5-489F-9DDE-9E3702A3D89D}" name="Executed Date" dataDxfId="62"/>
-    <tableColumn id="13" xr3:uid="{9B03223D-6ED3-4549-9812-44F9B7FB9F5E}" name="Comments (Any)" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{1059CC3C-316E-4BE4-9F28-B883A79B86D2}" name="Test Scenario Description" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{EA041670-F9F4-43FB-A857-C38D44666E25}" name="Test Case ID" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{9B2E537F-3535-451E-BB48-220B1F6FFB7F}" name="Test Case Description" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{4769C369-46C1-44B9-930F-E23A6BA66DD9}" name="Test Steps" dataDxfId="86"/>
+    <tableColumn id="5" xr3:uid="{298DD112-4C8B-46B3-A446-0E6D93CB1BC8}" name="Preconditions" dataDxfId="85"/>
+    <tableColumn id="6" xr3:uid="{37B46AC9-16E7-4ED1-8C0B-ADAE9CAAB714}" name="Test Data" dataDxfId="84"/>
+    <tableColumn id="7" xr3:uid="{8A9B609E-0F77-49DB-AE71-A0094C3164A7}" name="Post conditions" dataDxfId="83"/>
+    <tableColumn id="8" xr3:uid="{0CD618D3-C88B-4295-8ECC-CD62E718B8E9}" name="Expected Result" dataDxfId="82"/>
+    <tableColumn id="9" xr3:uid="{F2F61744-A610-47C1-8D18-258D214AD0AD}" name="Actual Result" dataDxfId="81"/>
+    <tableColumn id="10" xr3:uid="{BB7F01C1-4CCB-48BB-B1AF-EC76036F7A50}" name="Status" dataDxfId="80"/>
+    <tableColumn id="11" xr3:uid="{738EFE1E-9B5A-467D-B51A-FAE3C680984E}" name="Executed by" dataDxfId="79"/>
+    <tableColumn id="12" xr3:uid="{1CF50F8E-99F5-489F-9DDE-9E3702A3D89D}" name="Executed Date" dataDxfId="78"/>
+    <tableColumn id="13" xr3:uid="{9B03223D-6ED3-4549-9812-44F9B7FB9F5E}" name="Comments (Any)" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}" name="Table5" displayName="Table5" ref="A54:N58" totalsRowShown="0" headerRowDxfId="60" tableBorderDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}" name="Table5" displayName="Table5" ref="A54:N58" totalsRowShown="0" headerRowDxfId="76" tableBorderDxfId="75">
   <autoFilter ref="A54:N58" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{314B3457-1047-4B97-8690-0FC0C7E63A1B}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{8959A1D5-A8D6-4050-B431-3851687F3ACC}" name="Test Scenario Description" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{A67188D0-2718-49A7-9C98-559566B5BE34}" name="Test Case ID" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{183B190A-4A91-4704-A29A-7C10A864D50D}" name="Test Case Description" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{7A4E1888-CA65-4F52-B8DF-9B408E40F16C}" name="Test Steps" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{6D584D05-96FA-4797-9ECD-0ED9575C801B}" name="Preconditions" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{66F6BE7C-A5F9-4754-814D-8B481CF9EFEA}" name="Test Data" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{AB5CBC21-875A-440D-9540-043ECA26AB57}" name="Post conditions" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{CBB06D44-CDEA-4E08-88B7-B4D1ECE1DE4B}" name="Expected Result" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{C8ABBDB4-2419-49CC-A91E-AB7491F28F90}" name="Actual Result" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{020B1BAD-98DF-459D-BEF2-5D317249BC9D}" name="Status" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{227321DB-D0BA-4E7D-AD16-B96E11598F32}" name="Executed by" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{9ACAB240-5794-4560-B26C-28738972BD58}" name="Executed Date" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{8943EAAB-FDBC-4C27-B51B-36476E6099B6}" name="Comments (Any)" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{8959A1D5-A8D6-4050-B431-3851687F3ACC}" name="Test Scenario Description" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{A67188D0-2718-49A7-9C98-559566B5BE34}" name="Test Case ID" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{183B190A-4A91-4704-A29A-7C10A864D50D}" name="Test Case Description" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{7A4E1888-CA65-4F52-B8DF-9B408E40F16C}" name="Test Steps" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{6D584D05-96FA-4797-9ECD-0ED9575C801B}" name="Preconditions" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{66F6BE7C-A5F9-4754-814D-8B481CF9EFEA}" name="Test Data" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{AB5CBC21-875A-440D-9540-043ECA26AB57}" name="Post conditions" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{CBB06D44-CDEA-4E08-88B7-B4D1ECE1DE4B}" name="Expected Result" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{C8ABBDB4-2419-49CC-A91E-AB7491F28F90}" name="Actual Result" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{020B1BAD-98DF-459D-BEF2-5D317249BC9D}" name="Status" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{227321DB-D0BA-4E7D-AD16-B96E11598F32}" name="Executed by" dataDxfId="64"/>
+    <tableColumn id="13" xr3:uid="{9ACAB240-5794-4560-B26C-28738972BD58}" name="Executed Date" dataDxfId="63"/>
+    <tableColumn id="14" xr3:uid="{8943EAAB-FDBC-4C27-B51B-36476E6099B6}" name="Comments (Any)" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}" name="Table59" displayName="Table59" ref="A68:N69" totalsRowShown="0" headerRowDxfId="45" tableBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}" name="Table59" displayName="Table59" ref="A68:N69" totalsRowShown="0" headerRowDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A68:N69" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{8EA9A8A1-5263-4BA6-B939-0576AB70C56B}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{A09BFAB6-F331-4553-89F5-F645B197E6E4}" name="Test Scenario Description" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{95CD5178-70C6-4029-953F-2BF330D539E9}" name="Test Case ID" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{F7B88AC7-FFC4-4BD9-ABF2-1F7387637638}" name="Test Case Description" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{EBAB9F15-3FB9-4ADA-BBE0-1B9863E0F75A}" name="Test Steps" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{317B7FB8-1C15-459D-84BE-5FF22CB5F1DA}" name="Preconditions" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{FE69F33E-245E-4967-9DA5-61661D9E9AE2}" name="Test Data" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{A638ACA4-6A84-474A-8B20-92270C496B28}" name="Post conditions" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{4C22FB79-3826-4059-B9D1-787B48B379DD}" name="Expected Result" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{6447313D-A350-4AE5-91A9-DFB9ECA1C3EF}" name="Actual Result" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{4342DDD7-CFD6-4F93-AF81-A9D957048D98}" name="Status" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{B8008DF3-60E3-493D-87C9-A6021F446EB7}" name="Executed by" dataDxfId="33"/>
-    <tableColumn id="13" xr3:uid="{FB1CC5CA-CB21-45DD-862E-9141FA956663}" name="Executed Date" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{E2201D2A-882B-4DDA-85CA-BEB8666A1674}" name="Comments (Any)" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{A09BFAB6-F331-4553-89F5-F645B197E6E4}" name="Test Scenario Description" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{95CD5178-70C6-4029-953F-2BF330D539E9}" name="Test Case ID" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{F7B88AC7-FFC4-4BD9-ABF2-1F7387637638}" name="Test Case Description" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{EBAB9F15-3FB9-4ADA-BBE0-1B9863E0F75A}" name="Test Steps" dataDxfId="56"/>
+    <tableColumn id="6" xr3:uid="{317B7FB8-1C15-459D-84BE-5FF22CB5F1DA}" name="Preconditions" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{FE69F33E-245E-4967-9DA5-61661D9E9AE2}" name="Test Data" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{A638ACA4-6A84-474A-8B20-92270C496B28}" name="Post conditions" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{4C22FB79-3826-4059-B9D1-787B48B379DD}" name="Expected Result" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{6447313D-A350-4AE5-91A9-DFB9ECA1C3EF}" name="Actual Result" dataDxfId="51"/>
+    <tableColumn id="11" xr3:uid="{4342DDD7-CFD6-4F93-AF81-A9D957048D98}" name="Status" dataDxfId="50"/>
+    <tableColumn id="12" xr3:uid="{B8008DF3-60E3-493D-87C9-A6021F446EB7}" name="Executed by" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{FB1CC5CA-CB21-45DD-862E-9141FA956663}" name="Executed Date" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{E2201D2A-882B-4DDA-85CA-BEB8666A1674}" name="Comments (Any)" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}" name="Table57" displayName="Table57" ref="A79:N87" totalsRowShown="0" headerRowDxfId="30" tableBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}" name="Table57" displayName="Table57" ref="A79:N87" totalsRowShown="0" headerRowDxfId="46" tableBorderDxfId="45">
   <autoFilter ref="A79:N87" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{9A85158C-C3D9-4D9C-BD2A-2B5772389099}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{A94E9212-F76E-449A-8CA9-E193336BF565}" name="Test Scenario Description" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{6D6E821B-EFBF-487E-8EFD-65D718C427E4}" name="Test Case ID" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{747E0385-7511-4710-A360-A2B66EB42855}" name="Test Case Description" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{CC938E19-F87F-4452-919D-47E93CE148EA}" name="Test Steps" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{23D4BF6C-278D-4CB9-BE6F-689F8B058419}" name="Preconditions" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{023C0CBB-5E8E-4ED6-9B54-3D1CE6D1B758}" name="Test Data" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{BD6AE1D4-4907-417E-B61B-B9C56948AD74}" name="Post conditions" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{741D0EFD-8150-4F05-9134-06D25AB4E88F}" name="Expected Result" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{5E7DDCC4-7CA4-4051-B45C-1E497FA1C0ED}" name="Actual Result" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{B95FDC82-5F4D-4127-AB26-A07A18E3C44E}" name="Status" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{FDB1997D-3FD6-4316-9D6E-1E110EFC7217}" name="Executed by" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{1A04F9EA-D5D7-4856-AD37-257EEC2F87F0}" name="Executed Date" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{814E0251-0743-4E7B-A915-F8A9CC4917BE}" name="Comments (Any)" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{A94E9212-F76E-449A-8CA9-E193336BF565}" name="Test Scenario Description" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{6D6E821B-EFBF-487E-8EFD-65D718C427E4}" name="Test Case ID" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{747E0385-7511-4710-A360-A2B66EB42855}" name="Test Case Description" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{CC938E19-F87F-4452-919D-47E93CE148EA}" name="Test Steps" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{23D4BF6C-278D-4CB9-BE6F-689F8B058419}" name="Preconditions" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{023C0CBB-5E8E-4ED6-9B54-3D1CE6D1B758}" name="Test Data" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{BD6AE1D4-4907-417E-B61B-B9C56948AD74}" name="Post conditions" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{741D0EFD-8150-4F05-9134-06D25AB4E88F}" name="Expected Result" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{5E7DDCC4-7CA4-4051-B45C-1E497FA1C0ED}" name="Actual Result" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{B95FDC82-5F4D-4127-AB26-A07A18E3C44E}" name="Status" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{FDB1997D-3FD6-4316-9D6E-1E110EFC7217}" name="Executed by" dataDxfId="34"/>
+    <tableColumn id="13" xr3:uid="{1A04F9EA-D5D7-4856-AD37-257EEC2F87F0}" name="Executed Date" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{814E0251-0743-4E7B-A915-F8A9CC4917BE}" name="Comments (Any)" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N102" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N102" totalsRowShown="0" headerRowDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A97:N102" xr:uid="{579CEE6F-2BFF-4BA8-84B5-54FD3924CFE7}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{70CA3D9E-8ECA-4D8C-AB69-1087AC4F07B8}" name="Test Scenario ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{319399B1-33A1-4C16-AD15-4363C57C2DA0}" name="Test Scenario Description" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{BD9516DE-EFB6-45B5-90B8-97A92312EC6D}" name="Test Case ID" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{FA9382F4-41E9-425B-BE0D-0DFE248B76CC}" name="Test Case Description" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{E3B91FC0-33C0-42D3-884C-9898C818FB01}" name="Test Steps" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{826EF341-BA7F-42B6-ADD0-D1151A286FCB}" name="Preconditions" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{68A72ABC-F634-48C8-8145-DE769068807E}" name="Test Data" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{529801B7-1A06-40F1-8299-170161616A53}" name="Post conditions" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{68642ED6-B92A-489D-BF1E-5AD52EB0EDFB}" name="Expected Result" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{78C6ECC1-D57A-42EE-B74C-F356E5738487}" name="Actual Result" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{1D2F2D20-1615-4FE4-9961-49B9DA08014C}" name="Status" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{FBC3F02B-40C3-4F05-9308-70B55D3F01FA}" name="Executed by" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{805737BF-EFB1-41B6-AA4F-0C9913761E9A}" name="Executed Date" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{D471A4CD-F57D-448F-A88B-C9A1BC646C2E}" name="Comments (Any)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{70CA3D9E-8ECA-4D8C-AB69-1087AC4F07B8}" name="Test Scenario ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{319399B1-33A1-4C16-AD15-4363C57C2DA0}" name="Test Scenario Description" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{BD9516DE-EFB6-45B5-90B8-97A92312EC6D}" name="Test Case ID" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{FA9382F4-41E9-425B-BE0D-0DFE248B76CC}" name="Test Case Description" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{E3B91FC0-33C0-42D3-884C-9898C818FB01}" name="Test Steps" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{826EF341-BA7F-42B6-ADD0-D1151A286FCB}" name="Preconditions" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{68A72ABC-F634-48C8-8145-DE769068807E}" name="Test Data" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{529801B7-1A06-40F1-8299-170161616A53}" name="Post conditions" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{68642ED6-B92A-489D-BF1E-5AD52EB0EDFB}" name="Expected Result" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{78C6ECC1-D57A-42EE-B74C-F356E5738487}" name="Actual Result" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{1D2F2D20-1615-4FE4-9961-49B9DA08014C}" name="Status" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{FBC3F02B-40C3-4F05-9308-70B55D3F01FA}" name="Executed by" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{805737BF-EFB1-41B6-AA4F-0C9913761E9A}" name="Executed Date" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{D471A4CD-F57D-448F-A88B-C9A1BC646C2E}" name="Comments (Any)" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D35822AE-00B1-4788-BA43-280FABFC6C81}" name="Table210" displayName="Table210" ref="A112:N118" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="15">
+  <autoFilter ref="A112:N118" xr:uid="{7A236607-3E62-47E8-B96A-B11C3E40CEF1}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{C31DD80F-756C-4177-BDB3-6D4F8DD72099}" name="Test Scenario ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{533B9560-B1D5-4D20-9000-392A140C7C1E}" name="Test Scenario Description" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{3860407E-E155-4A09-91CE-190A0F20369B}" name="Test Case ID" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{48A16583-BCC4-4F31-BCE0-E7AE733006F9}" name="Test Case Description" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{671A089D-3410-4E9A-8E3E-EC71871AEC97}" name="Test Steps" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{E00EF447-DC92-469B-A840-74344E24A09D}" name="Preconditions" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{1260BFA0-63A4-46F7-A460-DD1BD8BF23F7}" name="Test Data" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{FA3365D1-CF54-4DE9-9880-A45BC574C6F8}" name="Post conditions" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{1F65AB25-4AB4-4C5A-AC1F-0CCB12972211}" name="Expected Result" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{DC82F03F-B715-406F-B0DE-D61DE98B3D49}" name="Actual Result" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{AE4CADFA-E0BD-4AEA-8322-C3CBB09140D9}" name="Status" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{36B04482-0528-4C73-AE34-4082ECC4D745}" name="Executed by" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{75B47AD3-20BD-43FB-B060-39CABA76AAC3}" name="Executed Date" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{36789A90-4167-4477-A969-ABB8212BBD61}" name="Comments (Any)" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3141,7 +3791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -5201,11 +5851,354 @@
       </c>
       <c r="N102" s="31"/>
     </row>
-    <row r="103" spans="1:14" ht="103.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A105" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A106" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="B106" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A107" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B107" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A108" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="1">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A109" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B109" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A110" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B110" s="1">
+        <v>45293</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A112" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F112" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G112" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="H112" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="I112" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="J112" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K112" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="L112" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="M112" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="N112" s="40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="179.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="C113" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="D113" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="E113" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="F113" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G113" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="H113" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="I113" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="J113" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="K113" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L113" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M113" s="36">
+        <v>45299</v>
+      </c>
+      <c r="N113" s="31"/>
+    </row>
+    <row r="114" spans="1:14" ht="245.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B114" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="C114" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="D114" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="E114" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="F114" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G114" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="H114" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="I114" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="J114" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="K114" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L114" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M114" s="36">
+        <v>45299</v>
+      </c>
+      <c r="N114" s="31"/>
+    </row>
+    <row r="115" spans="1:14" ht="223.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="C115" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="D115" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="E115" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="F115" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G115" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="H115" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="I115" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="J115" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="K115" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L115" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M115" s="36">
+        <v>45299</v>
+      </c>
+      <c r="N115" s="31"/>
+    </row>
+    <row r="116" spans="1:14" ht="183" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B116" s="31" t="s">
+        <v>271</v>
+      </c>
+      <c r="C116" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="D116" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="E116" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="F116" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G116" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="H116" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="I116" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="J116" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="K116" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L116" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M116" s="36">
+        <v>45659</v>
+      </c>
+      <c r="N116" s="31"/>
+    </row>
+    <row r="117" spans="1:14" ht="145.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B117" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="C117" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D117" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="E117" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F117" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G117" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="H117" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="I117" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="J117" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="K117" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L117" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M117" s="36">
+        <v>45659</v>
+      </c>
+      <c r="N117" s="31"/>
+    </row>
+    <row r="118" spans="1:14" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B118" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C118" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="D118" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="E118" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F118" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="H118" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="I118" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="J118" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="K118" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L118" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M118" s="36">
+        <v>45660</v>
+      </c>
+      <c r="N118" s="31"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="7">
+  <tableParts count="8">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -5213,6 +6206,7 @@
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1E31E1-8F56-4352-B12F-5D0CE27B66A3}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46135811-0729-480B-8C0D-A5257850A974}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="304">
   <si>
     <t>Project Name</t>
   </si>
@@ -1086,18 +1086,6 @@
     <t>Verify Unfriend Functionality</t>
   </si>
   <si>
-    <t>Ensure that a user can remove a friend from their friend list.</t>
-  </si>
-  <si>
-    <t>01. Enter a valid username 
-02. Enter a valid password
-03. Click on Login Button
-04. Find a friend you wish to unfriend.
-05.Click on the "Friends" button next to their name.
-06.Select "Unfriend" from the dropdown.
-07.Verify that the "Add Friend" button now appears next to their name instead of "Friends."</t>
-  </si>
-  <si>
     <t>The user successfully unfriended and the button should change back to "Add Friend."</t>
   </si>
   <si>
@@ -1108,9 +1096,6 @@
   </si>
   <si>
     <t>Ensure that the friend suggestions section is visible and displays recommendations to user.</t>
-  </si>
-  <si>
-    <t>A list of friend suggestions should appear, showing people the user might know.</t>
   </si>
   <si>
     <t xml:space="preserve">User should be able to  View Friend Suggestions </t>
@@ -1134,10 +1119,6 @@
 03. Click on Login Button
 04. Navigate to the "Friends" section.
 05.Click on the "All Friends" section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The friends list should be displayed with the names and profile pictures of friends.
-</t>
   </si>
   <si>
     <t xml:space="preserve">Verify that the user can View Friends List
@@ -1194,6 +1175,57 @@
   </si>
   <si>
     <t>The friend request is Removed, and no connection should be made between the two users..</t>
+  </si>
+  <si>
+    <t>Ensure that a user can unfriend an another user from their friend list.</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04.Find friend who wish to unfriend
+05.Click on the "Friends" button next to their name.
+06.Select "Unfriend" from the dropdown.
+07.Verify that the "Add Friend" button now appears next to their name instead of "Friends."</t>
+  </si>
+  <si>
+    <t>TC_FB_Friends_7</t>
+  </si>
+  <si>
+    <t>Verify Unfollow Functionality</t>
+  </si>
+  <si>
+    <t>Ensure that a user can unfollow an another user from their friend list.</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04.Find friend who wish to unfriend
+05.Click on the "Friends" button next to their name.
+06.Select "Unfollow" from the dropdown.
+07.Verify that the "Unfollow" button now appears next to their name instead of "Follow."</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon</t>
+  </si>
+  <si>
+    <t>User should be successfully unfollowed.</t>
+  </si>
+  <si>
+    <t>The user successfully unfollowed and the button should change back to "Follow."</t>
+  </si>
+  <si>
+    <t>A list of friend suggestions appear, showing people the user might know.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The friends list will display with the names and profile pictures of friends.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The friends list is displaying with the names and profile pictures of friends.
+</t>
   </si>
 </sst>
 </file>
@@ -1453,6 +1485,426 @@
   <dxfs count="124">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -1475,426 +1927,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3472,23 +3504,23 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D35822AE-00B1-4788-BA43-280FABFC6C81}" name="Table210" displayName="Table210" ref="A112:N118" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="15">
-  <autoFilter ref="A112:N118" xr:uid="{7A236607-3E62-47E8-B96A-B11C3E40CEF1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D35822AE-00B1-4788-BA43-280FABFC6C81}" name="Table210" displayName="Table210" ref="A112:N119" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14">
+  <autoFilter ref="A112:N119" xr:uid="{7A236607-3E62-47E8-B96A-B11C3E40CEF1}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{C31DD80F-756C-4177-BDB3-6D4F8DD72099}" name="Test Scenario ID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{533B9560-B1D5-4D20-9000-392A140C7C1E}" name="Test Scenario Description" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{3860407E-E155-4A09-91CE-190A0F20369B}" name="Test Case ID" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{48A16583-BCC4-4F31-BCE0-E7AE733006F9}" name="Test Case Description" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{671A089D-3410-4E9A-8E3E-EC71871AEC97}" name="Test Steps" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{E00EF447-DC92-469B-A840-74344E24A09D}" name="Preconditions" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{1260BFA0-63A4-46F7-A460-DD1BD8BF23F7}" name="Test Data" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{FA3365D1-CF54-4DE9-9880-A45BC574C6F8}" name="Post conditions" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{1F65AB25-4AB4-4C5A-AC1F-0CCB12972211}" name="Expected Result" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{DC82F03F-B715-406F-B0DE-D61DE98B3D49}" name="Actual Result" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{AE4CADFA-E0BD-4AEA-8322-C3CBB09140D9}" name="Status" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{36B04482-0528-4C73-AE34-4082ECC4D745}" name="Executed by" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{75B47AD3-20BD-43FB-B060-39CABA76AAC3}" name="Executed Date" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{36789A90-4167-4477-A969-ABB8212BBD61}" name="Comments (Any)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C31DD80F-756C-4177-BDB3-6D4F8DD72099}" name="Test Scenario ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{533B9560-B1D5-4D20-9000-392A140C7C1E}" name="Test Scenario Description" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{3860407E-E155-4A09-91CE-190A0F20369B}" name="Test Case ID" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{48A16583-BCC4-4F31-BCE0-E7AE733006F9}" name="Test Case Description" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{671A089D-3410-4E9A-8E3E-EC71871AEC97}" name="Test Steps" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{E00EF447-DC92-469B-A840-74344E24A09D}" name="Preconditions" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{1260BFA0-63A4-46F7-A460-DD1BD8BF23F7}" name="Test Data" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{FA3365D1-CF54-4DE9-9880-A45BC574C6F8}" name="Post conditions" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{1F65AB25-4AB4-4C5A-AC1F-0CCB12972211}" name="Expected Result" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{DC82F03F-B715-406F-B0DE-D61DE98B3D49}" name="Actual Result" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{AE4CADFA-E0BD-4AEA-8322-C3CBB09140D9}" name="Status" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{36B04482-0528-4C73-AE34-4082ECC4D745}" name="Executed by" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{75B47AD3-20BD-43FB-B060-39CABA76AAC3}" name="Executed Date" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{36789A90-4167-4477-A969-ABB8212BBD61}" name="Comments (Any)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3791,7 +3823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -5896,7 +5928,7 @@
         <v>5</v>
       </c>
       <c r="B110" s="1">
-        <v>45293</v>
+        <v>45300</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
@@ -5943,7 +5975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="179.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" ht="192" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="35" t="s">
         <v>256</v>
       </c>
@@ -5963,7 +5995,7 @@
         <v>33</v>
       </c>
       <c r="G113" s="31" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="H113" s="34" t="s">
         <v>261</v>
@@ -5985,7 +6017,7 @@
       </c>
       <c r="N113" s="31"/>
     </row>
-    <row r="114" spans="1:14" ht="245.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" ht="210.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="35" t="s">
         <v>256</v>
       </c>
@@ -5999,13 +6031,13 @@
         <v>270</v>
       </c>
       <c r="E114" s="31" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F114" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G114" s="31" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="H114" s="34" t="s">
         <v>268</v>
@@ -6032,31 +6064,31 @@
         <v>256</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C115" s="32" t="s">
         <v>263</v>
       </c>
       <c r="D115" s="31" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F115" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G115" s="31" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="H115" s="34" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I115" s="31" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="J115" s="31" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K115" s="35" t="s">
         <v>96</v>
@@ -6074,31 +6106,31 @@
         <v>256</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C116" s="32" t="s">
         <v>264</v>
       </c>
       <c r="D116" s="31" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="F116" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G116" s="31" t="s">
-        <v>250</v>
+        <v>298</v>
       </c>
       <c r="H116" s="34" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="I116" s="31" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="J116" s="31" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="K116" s="35" t="s">
         <v>96</v>
@@ -6107,40 +6139,40 @@
         <v>32</v>
       </c>
       <c r="M116" s="36">
-        <v>45659</v>
+        <v>45666</v>
       </c>
       <c r="N116" s="31"/>
     </row>
-    <row r="117" spans="1:14" ht="145.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" ht="196.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="35" t="s">
         <v>256</v>
       </c>
       <c r="B117" s="31" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C117" s="32" t="s">
         <v>265</v>
       </c>
       <c r="D117" s="31" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="E117" s="31" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="F117" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G117" s="31" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="H117" s="34" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I117" s="31" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="J117" s="31" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="K117" s="35" t="s">
         <v>96</v>
@@ -6149,7 +6181,7 @@
         <v>32</v>
       </c>
       <c r="M117" s="36">
-        <v>45659</v>
+        <v>45666</v>
       </c>
       <c r="N117" s="31"/>
     </row>
@@ -6158,31 +6190,31 @@
         <v>256</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C118" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D118" s="31" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E118" s="31" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F118" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G118" s="31" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="H118" s="34" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I118" s="31" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="J118" s="31" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="K118" s="35" t="s">
         <v>96</v>
@@ -6191,9 +6223,51 @@
         <v>32</v>
       </c>
       <c r="M118" s="36">
-        <v>45660</v>
+        <v>45666</v>
       </c>
       <c r="N118" s="31"/>
+    </row>
+    <row r="119" spans="1:14" ht="117" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B119" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="C119" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="D119" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="E119" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="F119" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G119" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="H119" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="I119" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="J119" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="K119" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L119" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M119" s="36">
+        <v>45666</v>
+      </c>
+      <c r="N119" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46135811-0729-480B-8C0D-A5257850A974}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA35776-3DC1-4C76-B17D-6F48865DCDEA}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="334">
   <si>
     <t>Project Name</t>
   </si>
@@ -1226,6 +1226,118 @@
   <si>
     <t xml:space="preserve">The friends list is displaying with the names and profile pictures of friends.
 </t>
+  </si>
+  <si>
+    <t>TS_FB_09</t>
+  </si>
+  <si>
+    <t>FaceBook Mrketplace</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_1</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_2</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_3</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_4</t>
+  </si>
+  <si>
+    <t>Verify searching for an item with valid keywords</t>
+  </si>
+  <si>
+    <t>Verify access to Marketplace after login</t>
+  </si>
+  <si>
+    <t>Login to Access Marketplace</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.</t>
+  </si>
+  <si>
+    <t>User successfully logs in and is redirected to the Marketplace page</t>
+  </si>
+  <si>
+    <t>User should be able to access Marketplace after login</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.
+05. Enter a search keyword in the search bar.
+06. Press Enter.</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword - Iphone 13</t>
+  </si>
+  <si>
+    <t>Relevant results matching the keyword are displayed</t>
+  </si>
+  <si>
+    <t>Relevant results matching the keyword are displaying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be able to a searching for an item </t>
+  </si>
+  <si>
+    <t>searching for an item with valid keywords</t>
+  </si>
+  <si>
+    <t>Verify search with no matching keywords</t>
+  </si>
+  <si>
+    <t>searching for an item no matching keywords</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.
+05. Enter a random or meaningless string  in the search bar.
+06. Press Enter.</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword - asdsadsadas</t>
+  </si>
+  <si>
+    <t>A message like "No results found" is displayed</t>
+  </si>
+  <si>
+    <t>A message like "No results found" is displaying</t>
+  </si>
+  <si>
+    <t>Verify applying filters</t>
+  </si>
+  <si>
+    <t>Apply filters like Location, Price Range, Condition Date listed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.
+05. nter a search keyword in the search bar.
+06. Apply filters </t>
+  </si>
+  <si>
+    <t>Results update according to the selected filters</t>
+  </si>
+  <si>
+    <t>Results updating according to the selected filters</t>
+  </si>
+  <si>
+    <t>User should be able to applying filters</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1387,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1330,6 +1442,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1372,7 +1490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1478,11 +1596,223 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="124">
+  <dxfs count="139">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3329,6 +3659,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCCC00"/>
       <color rgb="FFC72DC0"/>
     </mruColors>
   </colors>
@@ -3344,185 +3675,208 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}" name="Table4" displayName="Table4" ref="A8:N13" totalsRowShown="0" headerRowDxfId="123" dataDxfId="122">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}" name="Table4" displayName="Table4" ref="A8:N13" totalsRowShown="0" headerRowDxfId="138" dataDxfId="137">
   <autoFilter ref="A8:N13" xr:uid="{B9F8EB46-DB7B-47C8-95C7-454F508025A7}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{FA1520E5-151F-4C35-9564-490E6E227E63}" name="Test Scenario ID" dataDxfId="121"/>
-    <tableColumn id="2" xr3:uid="{4CD9CF72-D3D5-4E13-B21F-2628B71CA730}" name="Test Scenario Description" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{64C682F3-74F4-4B58-9AAA-079E2202EC63}" name="Test Case ID" dataDxfId="119"/>
-    <tableColumn id="4" xr3:uid="{F8711D9F-D3E9-4C0E-83A5-1112EACF3ECF}" name="Test Case Description" dataDxfId="118"/>
-    <tableColumn id="5" xr3:uid="{3C9E830E-1C51-4CB9-9B33-8A5AFEEE698E}" name="Test Steps" dataDxfId="117"/>
-    <tableColumn id="13" xr3:uid="{795BF8D4-2BAA-4AD4-842A-88C791483F7A}" name="Preconditions" dataDxfId="116"/>
-    <tableColumn id="14" xr3:uid="{21B04C03-953D-42FE-8068-4BF43AFF3291}" name="Test Data" dataDxfId="115"/>
-    <tableColumn id="15" xr3:uid="{9CF2DA71-3D28-4A14-A4CE-044972166E7C}" name="Post conditions" dataDxfId="114"/>
-    <tableColumn id="6" xr3:uid="{42C30692-F71E-4898-A159-20BE875D8033}" name="Expected Result" dataDxfId="113"/>
-    <tableColumn id="7" xr3:uid="{03D56321-2D40-4418-8D06-EED641A4F370}" name="Actual Result" dataDxfId="112"/>
-    <tableColumn id="8" xr3:uid="{C0EAC999-BB87-4D0C-9360-9BFF9AF67768}" name="Status" dataDxfId="111"/>
-    <tableColumn id="9" xr3:uid="{3B92054E-DFF9-4A75-AF0B-7B5080A92062}" name="Executed by" dataDxfId="110"/>
-    <tableColumn id="10" xr3:uid="{E7860CF1-1E6C-471A-B8FB-6DB223239798}" name="Executed Date" dataDxfId="109"/>
-    <tableColumn id="11" xr3:uid="{D4382055-B4B2-40BA-B30A-2EE9840623E1}" name="Comments (Any)" dataDxfId="108"/>
+    <tableColumn id="1" xr3:uid="{FA1520E5-151F-4C35-9564-490E6E227E63}" name="Test Scenario ID" dataDxfId="136"/>
+    <tableColumn id="2" xr3:uid="{4CD9CF72-D3D5-4E13-B21F-2628B71CA730}" name="Test Scenario Description" dataDxfId="135"/>
+    <tableColumn id="3" xr3:uid="{64C682F3-74F4-4B58-9AAA-079E2202EC63}" name="Test Case ID" dataDxfId="134"/>
+    <tableColumn id="4" xr3:uid="{F8711D9F-D3E9-4C0E-83A5-1112EACF3ECF}" name="Test Case Description" dataDxfId="133"/>
+    <tableColumn id="5" xr3:uid="{3C9E830E-1C51-4CB9-9B33-8A5AFEEE698E}" name="Test Steps" dataDxfId="132"/>
+    <tableColumn id="13" xr3:uid="{795BF8D4-2BAA-4AD4-842A-88C791483F7A}" name="Preconditions" dataDxfId="131"/>
+    <tableColumn id="14" xr3:uid="{21B04C03-953D-42FE-8068-4BF43AFF3291}" name="Test Data" dataDxfId="130"/>
+    <tableColumn id="15" xr3:uid="{9CF2DA71-3D28-4A14-A4CE-044972166E7C}" name="Post conditions" dataDxfId="129"/>
+    <tableColumn id="6" xr3:uid="{42C30692-F71E-4898-A159-20BE875D8033}" name="Expected Result" dataDxfId="128"/>
+    <tableColumn id="7" xr3:uid="{03D56321-2D40-4418-8D06-EED641A4F370}" name="Actual Result" dataDxfId="127"/>
+    <tableColumn id="8" xr3:uid="{C0EAC999-BB87-4D0C-9360-9BFF9AF67768}" name="Status" dataDxfId="126"/>
+    <tableColumn id="9" xr3:uid="{3B92054E-DFF9-4A75-AF0B-7B5080A92062}" name="Executed by" dataDxfId="125"/>
+    <tableColumn id="10" xr3:uid="{E7860CF1-1E6C-471A-B8FB-6DB223239798}" name="Executed Date" dataDxfId="124"/>
+    <tableColumn id="11" xr3:uid="{D4382055-B4B2-40BA-B30A-2EE9840623E1}" name="Comments (Any)" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}" name="Table42" displayName="Table42" ref="A24:N32" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}" name="Table42" displayName="Table42" ref="A24:N32" totalsRowShown="0" headerRowDxfId="122" dataDxfId="121">
   <autoFilter ref="A24:N32" xr:uid="{B1155A5B-1493-4085-854F-C5DA20AD28C9}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{B343AAFA-6457-4739-9100-101EF218F54D}" name="Test Scenario ID" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{E5529356-E16E-4EC4-9C43-4E830FC2E50F}" name="Test Scenario Description" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{2551A72A-8D4F-449F-B940-710504664FA5}" name="Test Case ID" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{00ECB93F-754B-43F5-9E43-F3D6BB21402C}" name="Test Case Description" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{66E4AAFF-0A66-44A2-A53B-7FABEAD85F8D}" name="Test Steps" dataDxfId="101"/>
-    <tableColumn id="13" xr3:uid="{662ABFF6-2773-475F-B091-BCDABF3FB4DE}" name="Preconditions" dataDxfId="100"/>
-    <tableColumn id="14" xr3:uid="{671E1D04-8126-4597-BD89-AC9A178AC6EA}" name="Test Data" dataDxfId="99"/>
-    <tableColumn id="15" xr3:uid="{90971945-FDC9-429A-8527-A13B23E811A8}" name="Post conditions" dataDxfId="98"/>
-    <tableColumn id="6" xr3:uid="{EF04FFC6-AA15-47C8-B4A9-828B2777CD1D}" name="Expected Result" dataDxfId="97"/>
-    <tableColumn id="7" xr3:uid="{4CA89147-B985-4D56-876B-62F63DC92C49}" name="Actual Result" dataDxfId="96"/>
-    <tableColumn id="8" xr3:uid="{BDA4C2F1-0AF2-488C-953C-82660F211B43}" name="Status" dataDxfId="95"/>
-    <tableColumn id="9" xr3:uid="{EF661887-7461-490A-8D26-42708C7DEF3D}" name="Executed by" dataDxfId="94"/>
-    <tableColumn id="10" xr3:uid="{BD8FCAC9-00C9-4F76-A5CA-C0CB2DE0CB76}" name="Executed Date" dataDxfId="93"/>
-    <tableColumn id="11" xr3:uid="{C33D96A1-29CA-4A83-BFA6-64CF06278883}" name="Comments (Any)" dataDxfId="92"/>
+    <tableColumn id="1" xr3:uid="{B343AAFA-6457-4739-9100-101EF218F54D}" name="Test Scenario ID" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{E5529356-E16E-4EC4-9C43-4E830FC2E50F}" name="Test Scenario Description" dataDxfId="119"/>
+    <tableColumn id="3" xr3:uid="{2551A72A-8D4F-449F-B940-710504664FA5}" name="Test Case ID" dataDxfId="118"/>
+    <tableColumn id="4" xr3:uid="{00ECB93F-754B-43F5-9E43-F3D6BB21402C}" name="Test Case Description" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{66E4AAFF-0A66-44A2-A53B-7FABEAD85F8D}" name="Test Steps" dataDxfId="116"/>
+    <tableColumn id="13" xr3:uid="{662ABFF6-2773-475F-B091-BCDABF3FB4DE}" name="Preconditions" dataDxfId="115"/>
+    <tableColumn id="14" xr3:uid="{671E1D04-8126-4597-BD89-AC9A178AC6EA}" name="Test Data" dataDxfId="114"/>
+    <tableColumn id="15" xr3:uid="{90971945-FDC9-429A-8527-A13B23E811A8}" name="Post conditions" dataDxfId="113"/>
+    <tableColumn id="6" xr3:uid="{EF04FFC6-AA15-47C8-B4A9-828B2777CD1D}" name="Expected Result" dataDxfId="112"/>
+    <tableColumn id="7" xr3:uid="{4CA89147-B985-4D56-876B-62F63DC92C49}" name="Actual Result" dataDxfId="111"/>
+    <tableColumn id="8" xr3:uid="{BDA4C2F1-0AF2-488C-953C-82660F211B43}" name="Status" dataDxfId="110"/>
+    <tableColumn id="9" xr3:uid="{EF661887-7461-490A-8D26-42708C7DEF3D}" name="Executed by" dataDxfId="109"/>
+    <tableColumn id="10" xr3:uid="{BD8FCAC9-00C9-4F76-A5CA-C0CB2DE0CB76}" name="Executed Date" dataDxfId="108"/>
+    <tableColumn id="11" xr3:uid="{C33D96A1-29CA-4A83-BFA6-64CF06278883}" name="Comments (Any)" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}" name="Table3" displayName="Table3" ref="B42:N44" totalsRowShown="0" headerRowDxfId="91" tableBorderDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}" name="Table3" displayName="Table3" ref="B42:N44" totalsRowShown="0" headerRowDxfId="106" tableBorderDxfId="105">
   <autoFilter ref="B42:N44" xr:uid="{F9A2252F-3062-4FB1-BC86-9676251CE7EE}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{1059CC3C-316E-4BE4-9F28-B883A79B86D2}" name="Test Scenario Description" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{EA041670-F9F4-43FB-A857-C38D44666E25}" name="Test Case ID" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{9B2E537F-3535-451E-BB48-220B1F6FFB7F}" name="Test Case Description" dataDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{4769C369-46C1-44B9-930F-E23A6BA66DD9}" name="Test Steps" dataDxfId="86"/>
-    <tableColumn id="5" xr3:uid="{298DD112-4C8B-46B3-A446-0E6D93CB1BC8}" name="Preconditions" dataDxfId="85"/>
-    <tableColumn id="6" xr3:uid="{37B46AC9-16E7-4ED1-8C0B-ADAE9CAAB714}" name="Test Data" dataDxfId="84"/>
-    <tableColumn id="7" xr3:uid="{8A9B609E-0F77-49DB-AE71-A0094C3164A7}" name="Post conditions" dataDxfId="83"/>
-    <tableColumn id="8" xr3:uid="{0CD618D3-C88B-4295-8ECC-CD62E718B8E9}" name="Expected Result" dataDxfId="82"/>
-    <tableColumn id="9" xr3:uid="{F2F61744-A610-47C1-8D18-258D214AD0AD}" name="Actual Result" dataDxfId="81"/>
-    <tableColumn id="10" xr3:uid="{BB7F01C1-4CCB-48BB-B1AF-EC76036F7A50}" name="Status" dataDxfId="80"/>
-    <tableColumn id="11" xr3:uid="{738EFE1E-9B5A-467D-B51A-FAE3C680984E}" name="Executed by" dataDxfId="79"/>
-    <tableColumn id="12" xr3:uid="{1CF50F8E-99F5-489F-9DDE-9E3702A3D89D}" name="Executed Date" dataDxfId="78"/>
-    <tableColumn id="13" xr3:uid="{9B03223D-6ED3-4549-9812-44F9B7FB9F5E}" name="Comments (Any)" dataDxfId="77"/>
+    <tableColumn id="1" xr3:uid="{1059CC3C-316E-4BE4-9F28-B883A79B86D2}" name="Test Scenario Description" dataDxfId="104"/>
+    <tableColumn id="2" xr3:uid="{EA041670-F9F4-43FB-A857-C38D44666E25}" name="Test Case ID" dataDxfId="103"/>
+    <tableColumn id="3" xr3:uid="{9B2E537F-3535-451E-BB48-220B1F6FFB7F}" name="Test Case Description" dataDxfId="102"/>
+    <tableColumn id="4" xr3:uid="{4769C369-46C1-44B9-930F-E23A6BA66DD9}" name="Test Steps" dataDxfId="101"/>
+    <tableColumn id="5" xr3:uid="{298DD112-4C8B-46B3-A446-0E6D93CB1BC8}" name="Preconditions" dataDxfId="100"/>
+    <tableColumn id="6" xr3:uid="{37B46AC9-16E7-4ED1-8C0B-ADAE9CAAB714}" name="Test Data" dataDxfId="99"/>
+    <tableColumn id="7" xr3:uid="{8A9B609E-0F77-49DB-AE71-A0094C3164A7}" name="Post conditions" dataDxfId="98"/>
+    <tableColumn id="8" xr3:uid="{0CD618D3-C88B-4295-8ECC-CD62E718B8E9}" name="Expected Result" dataDxfId="97"/>
+    <tableColumn id="9" xr3:uid="{F2F61744-A610-47C1-8D18-258D214AD0AD}" name="Actual Result" dataDxfId="96"/>
+    <tableColumn id="10" xr3:uid="{BB7F01C1-4CCB-48BB-B1AF-EC76036F7A50}" name="Status" dataDxfId="95"/>
+    <tableColumn id="11" xr3:uid="{738EFE1E-9B5A-467D-B51A-FAE3C680984E}" name="Executed by" dataDxfId="94"/>
+    <tableColumn id="12" xr3:uid="{1CF50F8E-99F5-489F-9DDE-9E3702A3D89D}" name="Executed Date" dataDxfId="93"/>
+    <tableColumn id="13" xr3:uid="{9B03223D-6ED3-4549-9812-44F9B7FB9F5E}" name="Comments (Any)" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}" name="Table5" displayName="Table5" ref="A54:N58" totalsRowShown="0" headerRowDxfId="76" tableBorderDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}" name="Table5" displayName="Table5" ref="A54:N58" totalsRowShown="0" headerRowDxfId="91" tableBorderDxfId="90">
   <autoFilter ref="A54:N58" xr:uid="{6C06EC2A-C8FF-468C-AEAD-9712933D5407}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{314B3457-1047-4B97-8690-0FC0C7E63A1B}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{8959A1D5-A8D6-4050-B431-3851687F3ACC}" name="Test Scenario Description" dataDxfId="74"/>
-    <tableColumn id="3" xr3:uid="{A67188D0-2718-49A7-9C98-559566B5BE34}" name="Test Case ID" dataDxfId="73"/>
-    <tableColumn id="4" xr3:uid="{183B190A-4A91-4704-A29A-7C10A864D50D}" name="Test Case Description" dataDxfId="72"/>
-    <tableColumn id="5" xr3:uid="{7A4E1888-CA65-4F52-B8DF-9B408E40F16C}" name="Test Steps" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{6D584D05-96FA-4797-9ECD-0ED9575C801B}" name="Preconditions" dataDxfId="70"/>
-    <tableColumn id="7" xr3:uid="{66F6BE7C-A5F9-4754-814D-8B481CF9EFEA}" name="Test Data" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{AB5CBC21-875A-440D-9540-043ECA26AB57}" name="Post conditions" dataDxfId="68"/>
-    <tableColumn id="9" xr3:uid="{CBB06D44-CDEA-4E08-88B7-B4D1ECE1DE4B}" name="Expected Result" dataDxfId="67"/>
-    <tableColumn id="10" xr3:uid="{C8ABBDB4-2419-49CC-A91E-AB7491F28F90}" name="Actual Result" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{020B1BAD-98DF-459D-BEF2-5D317249BC9D}" name="Status" dataDxfId="65"/>
-    <tableColumn id="12" xr3:uid="{227321DB-D0BA-4E7D-AD16-B96E11598F32}" name="Executed by" dataDxfId="64"/>
-    <tableColumn id="13" xr3:uid="{9ACAB240-5794-4560-B26C-28738972BD58}" name="Executed Date" dataDxfId="63"/>
-    <tableColumn id="14" xr3:uid="{8943EAAB-FDBC-4C27-B51B-36476E6099B6}" name="Comments (Any)" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{8959A1D5-A8D6-4050-B431-3851687F3ACC}" name="Test Scenario Description" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{A67188D0-2718-49A7-9C98-559566B5BE34}" name="Test Case ID" dataDxfId="88"/>
+    <tableColumn id="4" xr3:uid="{183B190A-4A91-4704-A29A-7C10A864D50D}" name="Test Case Description" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{7A4E1888-CA65-4F52-B8DF-9B408E40F16C}" name="Test Steps" dataDxfId="86"/>
+    <tableColumn id="6" xr3:uid="{6D584D05-96FA-4797-9ECD-0ED9575C801B}" name="Preconditions" dataDxfId="85"/>
+    <tableColumn id="7" xr3:uid="{66F6BE7C-A5F9-4754-814D-8B481CF9EFEA}" name="Test Data" dataDxfId="84"/>
+    <tableColumn id="8" xr3:uid="{AB5CBC21-875A-440D-9540-043ECA26AB57}" name="Post conditions" dataDxfId="83"/>
+    <tableColumn id="9" xr3:uid="{CBB06D44-CDEA-4E08-88B7-B4D1ECE1DE4B}" name="Expected Result" dataDxfId="82"/>
+    <tableColumn id="10" xr3:uid="{C8ABBDB4-2419-49CC-A91E-AB7491F28F90}" name="Actual Result" dataDxfId="81"/>
+    <tableColumn id="11" xr3:uid="{020B1BAD-98DF-459D-BEF2-5D317249BC9D}" name="Status" dataDxfId="80"/>
+    <tableColumn id="12" xr3:uid="{227321DB-D0BA-4E7D-AD16-B96E11598F32}" name="Executed by" dataDxfId="79"/>
+    <tableColumn id="13" xr3:uid="{9ACAB240-5794-4560-B26C-28738972BD58}" name="Executed Date" dataDxfId="78"/>
+    <tableColumn id="14" xr3:uid="{8943EAAB-FDBC-4C27-B51B-36476E6099B6}" name="Comments (Any)" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}" name="Table59" displayName="Table59" ref="A68:N69" totalsRowShown="0" headerRowDxfId="61" tableBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}" name="Table59" displayName="Table59" ref="A68:N69" totalsRowShown="0" headerRowDxfId="76" tableBorderDxfId="75">
   <autoFilter ref="A68:N69" xr:uid="{6BBF9A88-4606-41ED-A0B0-9AA9F6074A2E}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{8EA9A8A1-5263-4BA6-B939-0576AB70C56B}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{A09BFAB6-F331-4553-89F5-F645B197E6E4}" name="Test Scenario Description" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{95CD5178-70C6-4029-953F-2BF330D539E9}" name="Test Case ID" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{F7B88AC7-FFC4-4BD9-ABF2-1F7387637638}" name="Test Case Description" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{EBAB9F15-3FB9-4ADA-BBE0-1B9863E0F75A}" name="Test Steps" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{317B7FB8-1C15-459D-84BE-5FF22CB5F1DA}" name="Preconditions" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{FE69F33E-245E-4967-9DA5-61661D9E9AE2}" name="Test Data" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{A638ACA4-6A84-474A-8B20-92270C496B28}" name="Post conditions" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{4C22FB79-3826-4059-B9D1-787B48B379DD}" name="Expected Result" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{6447313D-A350-4AE5-91A9-DFB9ECA1C3EF}" name="Actual Result" dataDxfId="51"/>
-    <tableColumn id="11" xr3:uid="{4342DDD7-CFD6-4F93-AF81-A9D957048D98}" name="Status" dataDxfId="50"/>
-    <tableColumn id="12" xr3:uid="{B8008DF3-60E3-493D-87C9-A6021F446EB7}" name="Executed by" dataDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{FB1CC5CA-CB21-45DD-862E-9141FA956663}" name="Executed Date" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{E2201D2A-882B-4DDA-85CA-BEB8666A1674}" name="Comments (Any)" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{A09BFAB6-F331-4553-89F5-F645B197E6E4}" name="Test Scenario Description" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{95CD5178-70C6-4029-953F-2BF330D539E9}" name="Test Case ID" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{F7B88AC7-FFC4-4BD9-ABF2-1F7387637638}" name="Test Case Description" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{EBAB9F15-3FB9-4ADA-BBE0-1B9863E0F75A}" name="Test Steps" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{317B7FB8-1C15-459D-84BE-5FF22CB5F1DA}" name="Preconditions" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{FE69F33E-245E-4967-9DA5-61661D9E9AE2}" name="Test Data" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{A638ACA4-6A84-474A-8B20-92270C496B28}" name="Post conditions" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{4C22FB79-3826-4059-B9D1-787B48B379DD}" name="Expected Result" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{6447313D-A350-4AE5-91A9-DFB9ECA1C3EF}" name="Actual Result" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{4342DDD7-CFD6-4F93-AF81-A9D957048D98}" name="Status" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{B8008DF3-60E3-493D-87C9-A6021F446EB7}" name="Executed by" dataDxfId="64"/>
+    <tableColumn id="13" xr3:uid="{FB1CC5CA-CB21-45DD-862E-9141FA956663}" name="Executed Date" dataDxfId="63"/>
+    <tableColumn id="14" xr3:uid="{E2201D2A-882B-4DDA-85CA-BEB8666A1674}" name="Comments (Any)" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}" name="Table57" displayName="Table57" ref="A79:N87" totalsRowShown="0" headerRowDxfId="46" tableBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}" name="Table57" displayName="Table57" ref="A79:N87" totalsRowShown="0" headerRowDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A79:N87" xr:uid="{B797A0D3-A995-4547-BA8E-134D25CB2273}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{9A85158C-C3D9-4D9C-BD2A-2B5772389099}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{A94E9212-F76E-449A-8CA9-E193336BF565}" name="Test Scenario Description" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{6D6E821B-EFBF-487E-8EFD-65D718C427E4}" name="Test Case ID" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{747E0385-7511-4710-A360-A2B66EB42855}" name="Test Case Description" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{CC938E19-F87F-4452-919D-47E93CE148EA}" name="Test Steps" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{23D4BF6C-278D-4CB9-BE6F-689F8B058419}" name="Preconditions" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{023C0CBB-5E8E-4ED6-9B54-3D1CE6D1B758}" name="Test Data" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{BD6AE1D4-4907-417E-B61B-B9C56948AD74}" name="Post conditions" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{741D0EFD-8150-4F05-9134-06D25AB4E88F}" name="Expected Result" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{5E7DDCC4-7CA4-4051-B45C-1E497FA1C0ED}" name="Actual Result" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{B95FDC82-5F4D-4127-AB26-A07A18E3C44E}" name="Status" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{FDB1997D-3FD6-4316-9D6E-1E110EFC7217}" name="Executed by" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{1A04F9EA-D5D7-4856-AD37-257EEC2F87F0}" name="Executed Date" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{814E0251-0743-4E7B-A915-F8A9CC4917BE}" name="Comments (Any)" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{A94E9212-F76E-449A-8CA9-E193336BF565}" name="Test Scenario Description" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{6D6E821B-EFBF-487E-8EFD-65D718C427E4}" name="Test Case ID" dataDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{747E0385-7511-4710-A360-A2B66EB42855}" name="Test Case Description" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{CC938E19-F87F-4452-919D-47E93CE148EA}" name="Test Steps" dataDxfId="56"/>
+    <tableColumn id="6" xr3:uid="{23D4BF6C-278D-4CB9-BE6F-689F8B058419}" name="Preconditions" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{023C0CBB-5E8E-4ED6-9B54-3D1CE6D1B758}" name="Test Data" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{BD6AE1D4-4907-417E-B61B-B9C56948AD74}" name="Post conditions" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{741D0EFD-8150-4F05-9134-06D25AB4E88F}" name="Expected Result" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{5E7DDCC4-7CA4-4051-B45C-1E497FA1C0ED}" name="Actual Result" dataDxfId="51"/>
+    <tableColumn id="11" xr3:uid="{B95FDC82-5F4D-4127-AB26-A07A18E3C44E}" name="Status" dataDxfId="50"/>
+    <tableColumn id="12" xr3:uid="{FDB1997D-3FD6-4316-9D6E-1E110EFC7217}" name="Executed by" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{1A04F9EA-D5D7-4856-AD37-257EEC2F87F0}" name="Executed Date" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{814E0251-0743-4E7B-A915-F8A9CC4917BE}" name="Comments (Any)" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N102" totalsRowShown="0" headerRowDxfId="31" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1B39BF24-2AEB-4D01-99C3-8E795AF4F0B2}" name="Table2" displayName="Table2" ref="A97:N102" totalsRowShown="0" headerRowDxfId="46" tableBorderDxfId="45">
   <autoFilter ref="A97:N102" xr:uid="{579CEE6F-2BFF-4BA8-84B5-54FD3924CFE7}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{70CA3D9E-8ECA-4D8C-AB69-1087AC4F07B8}" name="Test Scenario ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{319399B1-33A1-4C16-AD15-4363C57C2DA0}" name="Test Scenario Description" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{BD9516DE-EFB6-45B5-90B8-97A92312EC6D}" name="Test Case ID" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{FA9382F4-41E9-425B-BE0D-0DFE248B76CC}" name="Test Case Description" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{E3B91FC0-33C0-42D3-884C-9898C818FB01}" name="Test Steps" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{826EF341-BA7F-42B6-ADD0-D1151A286FCB}" name="Preconditions" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{68A72ABC-F634-48C8-8145-DE769068807E}" name="Test Data" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{529801B7-1A06-40F1-8299-170161616A53}" name="Post conditions" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{68642ED6-B92A-489D-BF1E-5AD52EB0EDFB}" name="Expected Result" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{78C6ECC1-D57A-42EE-B74C-F356E5738487}" name="Actual Result" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{1D2F2D20-1615-4FE4-9961-49B9DA08014C}" name="Status" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{FBC3F02B-40C3-4F05-9308-70B55D3F01FA}" name="Executed by" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{805737BF-EFB1-41B6-AA4F-0C9913761E9A}" name="Executed Date" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{D471A4CD-F57D-448F-A88B-C9A1BC646C2E}" name="Comments (Any)" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{70CA3D9E-8ECA-4D8C-AB69-1087AC4F07B8}" name="Test Scenario ID" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{319399B1-33A1-4C16-AD15-4363C57C2DA0}" name="Test Scenario Description" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{BD9516DE-EFB6-45B5-90B8-97A92312EC6D}" name="Test Case ID" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{FA9382F4-41E9-425B-BE0D-0DFE248B76CC}" name="Test Case Description" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{E3B91FC0-33C0-42D3-884C-9898C818FB01}" name="Test Steps" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{826EF341-BA7F-42B6-ADD0-D1151A286FCB}" name="Preconditions" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{68A72ABC-F634-48C8-8145-DE769068807E}" name="Test Data" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{529801B7-1A06-40F1-8299-170161616A53}" name="Post conditions" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{68642ED6-B92A-489D-BF1E-5AD52EB0EDFB}" name="Expected Result" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{78C6ECC1-D57A-42EE-B74C-F356E5738487}" name="Actual Result" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{1D2F2D20-1615-4FE4-9961-49B9DA08014C}" name="Status" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{FBC3F02B-40C3-4F05-9308-70B55D3F01FA}" name="Executed by" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{805737BF-EFB1-41B6-AA4F-0C9913761E9A}" name="Executed Date" dataDxfId="32"/>
+    <tableColumn id="14" xr3:uid="{D471A4CD-F57D-448F-A88B-C9A1BC646C2E}" name="Comments (Any)" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D35822AE-00B1-4788-BA43-280FABFC6C81}" name="Table210" displayName="Table210" ref="A112:N119" totalsRowShown="0" headerRowDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D35822AE-00B1-4788-BA43-280FABFC6C81}" name="Table210" displayName="Table210" ref="A112:N119" totalsRowShown="0" headerRowDxfId="30" tableBorderDxfId="29">
   <autoFilter ref="A112:N119" xr:uid="{7A236607-3E62-47E8-B96A-B11C3E40CEF1}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{C31DD80F-756C-4177-BDB3-6D4F8DD72099}" name="Test Scenario ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{533B9560-B1D5-4D20-9000-392A140C7C1E}" name="Test Scenario Description" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{3860407E-E155-4A09-91CE-190A0F20369B}" name="Test Case ID" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{48A16583-BCC4-4F31-BCE0-E7AE733006F9}" name="Test Case Description" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{671A089D-3410-4E9A-8E3E-EC71871AEC97}" name="Test Steps" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{E00EF447-DC92-469B-A840-74344E24A09D}" name="Preconditions" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{1260BFA0-63A4-46F7-A460-DD1BD8BF23F7}" name="Test Data" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{FA3365D1-CF54-4DE9-9880-A45BC574C6F8}" name="Post conditions" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{1F65AB25-4AB4-4C5A-AC1F-0CCB12972211}" name="Expected Result" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{DC82F03F-B715-406F-B0DE-D61DE98B3D49}" name="Actual Result" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{AE4CADFA-E0BD-4AEA-8322-C3CBB09140D9}" name="Status" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{36B04482-0528-4C73-AE34-4082ECC4D745}" name="Executed by" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{75B47AD3-20BD-43FB-B060-39CABA76AAC3}" name="Executed Date" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{36789A90-4167-4477-A969-ABB8212BBD61}" name="Comments (Any)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C31DD80F-756C-4177-BDB3-6D4F8DD72099}" name="Test Scenario ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{533B9560-B1D5-4D20-9000-392A140C7C1E}" name="Test Scenario Description" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{3860407E-E155-4A09-91CE-190A0F20369B}" name="Test Case ID" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{48A16583-BCC4-4F31-BCE0-E7AE733006F9}" name="Test Case Description" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{671A089D-3410-4E9A-8E3E-EC71871AEC97}" name="Test Steps" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{E00EF447-DC92-469B-A840-74344E24A09D}" name="Preconditions" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{1260BFA0-63A4-46F7-A460-DD1BD8BF23F7}" name="Test Data" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{FA3365D1-CF54-4DE9-9880-A45BC574C6F8}" name="Post conditions" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{1F65AB25-4AB4-4C5A-AC1F-0CCB12972211}" name="Expected Result" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{DC82F03F-B715-406F-B0DE-D61DE98B3D49}" name="Actual Result" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{AE4CADFA-E0BD-4AEA-8322-C3CBB09140D9}" name="Status" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{36B04482-0528-4C73-AE34-4082ECC4D745}" name="Executed by" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{75B47AD3-20BD-43FB-B060-39CABA76AAC3}" name="Executed Date" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{36789A90-4167-4477-A969-ABB8212BBD61}" name="Comments (Any)" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBAD7A3-B347-44E2-9B27-AD66B7491497}" name="Table58" displayName="Table58" ref="A129:N133" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="14">
+  <autoFilter ref="A129:N133" xr:uid="{AF06605C-3A8F-42B6-8000-848E95CF3CA7}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{899B6D11-A4A4-4D1E-A920-3C8360FF23B4}" name="Test Scenario ID"/>
+    <tableColumn id="2" xr3:uid="{22F80579-E3C2-408E-8D5B-69B43D1820AE}" name="Test Scenario Description" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{327B4D30-DC50-4881-85B7-FE0E95D1645D}" name="Test Case ID" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{C16AFB2D-696A-4057-B9E7-4AE3B66D0BCC}" name="Test Case Description" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{6394A458-9315-4B26-81CC-5B793F264CC9}" name="Test Steps" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{0A9E3BCA-17A3-49CD-B0EB-2FC2105B329C}" name="Preconditions" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{6841F312-2C04-4D4A-974A-2960637B3AF7}" name="Test Data" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{3900FEF4-2C67-4E7D-8C78-251AB4C1E247}" name="Post conditions" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{07C83640-211A-49C2-B8B7-4D777AE93C6F}" name="Expected Result" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{BFBD50E4-2E76-407A-8746-31C0704AF568}" name="Actual Result" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{22555ED7-718B-4E1C-9AFD-B42B50B7008E}" name="Status" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{FC333FD7-3AE0-4888-B1D8-0279072E2AFF}" name="Executed by" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{76838723-32E4-42B5-959A-E2C2FA2C6C2D}" name="Executed Date" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{066A28AE-B2B4-4DFE-963F-99A3000947CF}" name="Comments (Any)" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3823,7 +4177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -5912,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="B108" s="1">
-        <v>45299</v>
+        <v>45665</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
@@ -5928,7 +6282,7 @@
         <v>5</v>
       </c>
       <c r="B110" s="1">
-        <v>45300</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
@@ -6013,7 +6367,7 @@
         <v>32</v>
       </c>
       <c r="M113" s="36">
-        <v>45299</v>
+        <v>45665</v>
       </c>
       <c r="N113" s="31"/>
     </row>
@@ -6055,7 +6409,7 @@
         <v>32</v>
       </c>
       <c r="M114" s="36">
-        <v>45299</v>
+        <v>45665</v>
       </c>
       <c r="N114" s="31"/>
     </row>
@@ -6097,7 +6451,7 @@
         <v>32</v>
       </c>
       <c r="M115" s="36">
-        <v>45299</v>
+        <v>45665</v>
       </c>
       <c r="N115" s="31"/>
     </row>
@@ -6269,10 +6623,270 @@
       </c>
       <c r="N119" s="31"/>
     </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A122" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B122" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A123" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B123" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A124" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B124" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A125" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B125" s="1">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A126" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B126" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A127" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B127" s="1">
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A129" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B129" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F129" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="H129" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="I129" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="J129" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="K129" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="L129" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="M129" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="N129" s="43" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B130" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C130" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="D130" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="E130" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="F130" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G130" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="H130" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="I130" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="J130" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="K130" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L130" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M130" s="19">
+        <v>45667</v>
+      </c>
+      <c r="N130" s="14"/>
+    </row>
+    <row r="131" spans="1:14" ht="125.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B131" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="C131" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D131" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="E131" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="F131" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G131" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="H131" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="I131" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="J131" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="K131" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L131" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M131" s="19">
+        <v>45667</v>
+      </c>
+      <c r="N131" s="14"/>
+    </row>
+    <row r="132" spans="1:14" ht="136.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="C132" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="E132" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="F132" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G132" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="H132" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="I132" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="J132" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="K132" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L132" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M132" s="19">
+        <v>46010</v>
+      </c>
+      <c r="N132" s="14"/>
+    </row>
+    <row r="133" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A133" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B133" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D133" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="E133" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="F133" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G133" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="H133" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="I133" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="J133" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="K133" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L133" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M133" s="19">
+        <v>46011</v>
+      </c>
+      <c r="N133" s="14"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="8">
+  <tableParts count="9">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -6281,6 +6895,7 @@
     <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA35776-3DC1-4C76-B17D-6F48865DCDEA}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98271240-5ED2-4F87-843B-531B5F9988A3}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="342">
   <si>
     <t>Project Name</t>
   </si>
@@ -1320,24 +1320,64 @@
     <t>Verify applying filters</t>
   </si>
   <si>
-    <t>Apply filters like Location, Price Range, Condition Date listed.</t>
+    <t>Results update according to the selected filters</t>
+  </si>
+  <si>
+    <t>Results updating according to the selected filters</t>
+  </si>
+  <si>
+    <t>User should be able to applying filters</t>
+  </si>
+  <si>
+    <t>Apply filters like , Price Range, Condition Date listed.</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword -  Iphone 13
+Price Range - 30000 - 5000</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_5</t>
+  </si>
+  <si>
+    <t>Verify posting a new item</t>
   </si>
   <si>
     <t xml:space="preserve">01. Enter a valid username 
 02. Enter a valid password
 03. Click on Login Button
 04. click the Marketplace icon in the main navigation menu.
-05. nter a search keyword in the search bar.
+05. Enter a search keyword in the search bar.
 06. Apply filters </t>
   </si>
   <si>
-    <t>Results update according to the selected filters</t>
-  </si>
-  <si>
-    <t>Results updating according to the selected filters</t>
-  </si>
-  <si>
-    <t>User should be able to applying filters</t>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.
+05.Navigate to Create New Listing from the Marketplace menu
+06.Choose Listing type
+07. Enter valid details for the item 
+06. Upload a valid image file.
+08. Click on "Publish" button.</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Title: "This is a test listing by KAVISHKA"
+Price: "1000"
+Category: "Electronics"
+Location: "New York, NY"</t>
+  </si>
+  <si>
+    <t>The item is successfully listed in the Marketplace.</t>
+  </si>
+  <si>
+    <t>User should be able to  post a new item in the Marketplace.</t>
+  </si>
+  <si>
+    <t>post a new item in the Marketplace.</t>
   </si>
 </sst>
 </file>
@@ -1609,6 +1649,186 @@
   </cellStyles>
   <dxfs count="139">
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1632,186 +1852,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3858,23 +3898,23 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBAD7A3-B347-44E2-9B27-AD66B7491497}" name="Table58" displayName="Table58" ref="A129:N133" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="14">
-  <autoFilter ref="A129:N133" xr:uid="{AF06605C-3A8F-42B6-8000-848E95CF3CA7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBAD7A3-B347-44E2-9B27-AD66B7491497}" name="Table58" displayName="Table58" ref="A129:N134" totalsRowShown="0" headerRowDxfId="14" tableBorderDxfId="13">
+  <autoFilter ref="A129:N134" xr:uid="{AF06605C-3A8F-42B6-8000-848E95CF3CA7}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{899B6D11-A4A4-4D1E-A920-3C8360FF23B4}" name="Test Scenario ID"/>
-    <tableColumn id="2" xr3:uid="{22F80579-E3C2-408E-8D5B-69B43D1820AE}" name="Test Scenario Description" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{327B4D30-DC50-4881-85B7-FE0E95D1645D}" name="Test Case ID" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{C16AFB2D-696A-4057-B9E7-4AE3B66D0BCC}" name="Test Case Description" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{6394A458-9315-4B26-81CC-5B793F264CC9}" name="Test Steps" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{0A9E3BCA-17A3-49CD-B0EB-2FC2105B329C}" name="Preconditions" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{6841F312-2C04-4D4A-974A-2960637B3AF7}" name="Test Data" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{3900FEF4-2C67-4E7D-8C78-251AB4C1E247}" name="Post conditions" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{07C83640-211A-49C2-B8B7-4D777AE93C6F}" name="Expected Result" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{BFBD50E4-2E76-407A-8746-31C0704AF568}" name="Actual Result" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{22555ED7-718B-4E1C-9AFD-B42B50B7008E}" name="Status" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{FC333FD7-3AE0-4888-B1D8-0279072E2AFF}" name="Executed by" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{76838723-32E4-42B5-959A-E2C2FA2C6C2D}" name="Executed Date" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{066A28AE-B2B4-4DFE-963F-99A3000947CF}" name="Comments (Any)" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{22F80579-E3C2-408E-8D5B-69B43D1820AE}" name="Test Scenario Description" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{327B4D30-DC50-4881-85B7-FE0E95D1645D}" name="Test Case ID" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{C16AFB2D-696A-4057-B9E7-4AE3B66D0BCC}" name="Test Case Description" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{6394A458-9315-4B26-81CC-5B793F264CC9}" name="Test Steps" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{0A9E3BCA-17A3-49CD-B0EB-2FC2105B329C}" name="Preconditions" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{6841F312-2C04-4D4A-974A-2960637B3AF7}" name="Test Data" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{3900FEF4-2C67-4E7D-8C78-251AB4C1E247}" name="Post conditions" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{07C83640-211A-49C2-B8B7-4D777AE93C6F}" name="Expected Result" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{BFBD50E4-2E76-407A-8746-31C0704AF568}" name="Actual Result" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{22555ED7-718B-4E1C-9AFD-B42B50B7008E}" name="Status" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{FC333FD7-3AE0-4888-B1D8-0279072E2AFF}" name="Executed by" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{76838723-32E4-42B5-959A-E2C2FA2C6C2D}" name="Executed Date" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{066A28AE-B2B4-4DFE-963F-99A3000947CF}" name="Comments (Any)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4177,7 +4217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -6837,7 +6877,7 @@
         <v>32</v>
       </c>
       <c r="M132" s="19">
-        <v>46010</v>
+        <v>45667</v>
       </c>
       <c r="N132" s="14"/>
     </row>
@@ -6852,25 +6892,25 @@
         <v>309</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F133" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G133" s="14" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="H133" s="17" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K133" s="18" t="s">
         <v>96</v>
@@ -6879,9 +6919,51 @@
         <v>32</v>
       </c>
       <c r="M133" s="19">
-        <v>46011</v>
+        <v>45668</v>
       </c>
       <c r="N133" s="14"/>
+    </row>
+    <row r="134" spans="1:14" ht="177" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="C134" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="D134" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="E134" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="F134" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G134" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="H134" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="I134" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="J134" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="K134" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L134" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M134" s="19">
+        <v>45668</v>
+      </c>
+      <c r="N134" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98271240-5ED2-4F87-843B-531B5F9988A3}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC12FF2-1CB1-4E25-9854-93A4FE7B5F27}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="375">
   <si>
     <t>Project Name</t>
   </si>
@@ -1363,21 +1363,158 @@
 08. Click on "Publish" button.</t>
   </si>
   <si>
+    <t>The item is successfully listed in the Marketplace.</t>
+  </si>
+  <si>
+    <t>User should be able to  post a new item in the Marketplace.</t>
+  </si>
+  <si>
+    <t>post a new item in the Marketplace.</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_6</t>
+  </si>
+  <si>
+    <t>Verify posting with missing mandatory fields</t>
+  </si>
+  <si>
+    <t>post a new item in the Marketplace missing mandatory fields.</t>
+  </si>
+  <si>
+    <t>User should not be able to  post a new item in the Marketplace missing mandatory fields.</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Title: ""
+Price: ""
+Category: "Tools"
+Condition: "New"
+Location: "Colombo, Sri Lanka"</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.
+05.Navigate to Create New Listing from the Marketplace menu
+06.Choose Listing type
+07. Enter details for the item with missing mandatory fields
+06. Upload a valid image file.
+08. Click on "Publish" button.</t>
+  </si>
+  <si>
     <t>Username - jigiwi7156@jofuso.com
 Password - Celkon
 Title: "This is a test listing by KAVISHKA"
 Price: "1000"
-Category: "Electronics"
-Location: "New York, NY"</t>
-  </si>
-  <si>
-    <t>The item is successfully listed in the Marketplace.</t>
-  </si>
-  <si>
-    <t>User should be able to  post a new item in the Marketplace.</t>
-  </si>
-  <si>
-    <t>post a new item in the Marketplace.</t>
+Category: "Tools"
+Condition: "New"
+Location: "Colombo, Sri Lanka"
+Photo</t>
+  </si>
+  <si>
+    <t>An error message,  "Please enter a valid title", is displayed.
+An error message,  "Enter a price for your item", is displayed.</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_7</t>
+  </si>
+  <si>
+    <t>Verify detailed view of an item</t>
+  </si>
+  <si>
+    <t>View item detils</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.
+05. search for or locate an item in the Marketplace.
+06. click on the item's title or image.</t>
+  </si>
+  <si>
+    <t>A detailed view of the item is displayed, including title, description, price, seller details, and images</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword -  Iphone 13</t>
+  </si>
+  <si>
+    <t>User should be able to  view  detailed view of an item.</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_8</t>
+  </si>
+  <si>
+    <t>Verify saving an item to favorites</t>
+  </si>
+  <si>
+    <t>Saving and Favoriting Items</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_9</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.
+05. search for or locate an item in the Marketplace.
+06. click on the item's title or image.
+07. click on the "Save" icon on the item.</t>
+  </si>
+  <si>
+    <t>User should be able to  Saving and Favoriting Items</t>
+  </si>
+  <si>
+    <t>The item is added to the Saved Items section</t>
+  </si>
+  <si>
+    <t>Verify accessing saved items</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. click the Marketplace icon in the main navigation menu.
+05.Navigate to the Saved Items section in the Marketplace menu</t>
+  </si>
+  <si>
+    <t>Access saved items</t>
+  </si>
+  <si>
+    <t>All previously saved items are displayed</t>
+  </si>
+  <si>
+    <t>User should be able to Access and view saved itemss</t>
+  </si>
+  <si>
+    <t>TC_FB_Market_10</t>
+  </si>
+  <si>
+    <t>Verify unauthorized access to Marketplace</t>
+  </si>
+  <si>
+    <t>Navigate to the Marketplace without logging in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.Visit to Facebook
+02. click the Marketplace icon in the main navigation menu.
+</t>
+  </si>
+  <si>
+    <t>The user is redirected to the login page</t>
+  </si>
+  <si>
+    <t>User should not be able to interact with the Marketplace without logging in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+URL - https://web.facebook.com/marketplace/?_rdc=1&amp;_rdr
+</t>
   </si>
 </sst>
 </file>
@@ -3898,8 +4035,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBAD7A3-B347-44E2-9B27-AD66B7491497}" name="Table58" displayName="Table58" ref="A129:N134" totalsRowShown="0" headerRowDxfId="14" tableBorderDxfId="13">
-  <autoFilter ref="A129:N134" xr:uid="{AF06605C-3A8F-42B6-8000-848E95CF3CA7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{ECBAD7A3-B347-44E2-9B27-AD66B7491497}" name="Table58" displayName="Table58" ref="A129:N139" totalsRowShown="0" headerRowDxfId="14" tableBorderDxfId="13">
+  <autoFilter ref="A129:N139" xr:uid="{AF06605C-3A8F-42B6-8000-848E95CF3CA7}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{899B6D11-A4A4-4D1E-A920-3C8360FF23B4}" name="Test Scenario ID"/>
     <tableColumn id="2" xr3:uid="{22F80579-E3C2-408E-8D5B-69B43D1820AE}" name="Test Scenario Description" dataDxfId="12"/>
@@ -4217,7 +4354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N134"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -6708,7 +6845,7 @@
         <v>5</v>
       </c>
       <c r="B127" s="1">
-        <v>45666</v>
+        <v>45669</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
@@ -6923,7 +7060,7 @@
       </c>
       <c r="N133" s="14"/>
     </row>
-    <row r="134" spans="1:14" ht="177" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" ht="196.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>304</v>
       </c>
@@ -6934,7 +7071,7 @@
         <v>334</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E134" s="14" t="s">
         <v>337</v>
@@ -6943,16 +7080,16 @@
         <v>33</v>
       </c>
       <c r="G134" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="H134" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="I134" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="H134" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="I134" s="14" t="s">
-        <v>339</v>
-      </c>
       <c r="J134" s="14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K134" s="18" t="s">
         <v>96</v>
@@ -6964,6 +7101,216 @@
         <v>45668</v>
       </c>
       <c r="N134" s="14"/>
+    </row>
+    <row r="135" spans="1:14" ht="186" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="D135" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="E135" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="F135" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G135" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="H135" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="I135" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="J135" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="K135" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L135" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M135" s="19">
+        <v>45669</v>
+      </c>
+      <c r="N135" s="14"/>
+    </row>
+    <row r="136" spans="1:14" ht="174.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B136" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="C136" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="E136" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="F136" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G136" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="H136" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="I136" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J136" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="K136" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L136" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M136" s="19">
+        <v>45669</v>
+      </c>
+      <c r="N136" s="14"/>
+    </row>
+    <row r="137" spans="1:14" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B137" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="C137" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="D137" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="E137" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="F137" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G137" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="H137" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="I137" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="J137" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="K137" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L137" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M137" s="19">
+        <v>45669</v>
+      </c>
+      <c r="N137" s="14"/>
+    </row>
+    <row r="138" spans="1:14" ht="106.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B138" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="D138" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="E138" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="F138" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G138" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="H138" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="I138" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="J138" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="K138" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L138" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M138" s="19">
+        <v>45669</v>
+      </c>
+      <c r="N138" s="14"/>
+    </row>
+    <row r="139" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A139" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B139" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C139" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="D139" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="E139" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="F139" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G139" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="H139" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="I139" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="J139" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="K139" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L139" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M139" s="19">
+        <v>45669</v>
+      </c>
+      <c r="N139" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC12FF2-1CB1-4E25-9854-93A4FE7B5F27}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06CC7C3-6EED-4FA8-B3E6-7BA7A2B9D655}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="395">
   <si>
     <t>Project Name</t>
   </si>
@@ -1515,6 +1515,95 @@
     <t xml:space="preserve">
 URL - https://web.facebook.com/marketplace/?_rdc=1&amp;_rdr
 </t>
+  </si>
+  <si>
+    <t>TS_FB_10</t>
+  </si>
+  <si>
+    <t>FaceBook Groups</t>
+  </si>
+  <si>
+    <t>Verify that the user can search for a group.</t>
+  </si>
+  <si>
+    <t>TC_FB_Groups_1</t>
+  </si>
+  <si>
+    <t>Search for a Group</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Enter the group name in the search bar.
+05. Click the search icon.</t>
+  </si>
+  <si>
+    <t>The search results page is displayed,  specified group appears under the "Groups" filter.
+Clicking the group name navigates to the group page.</t>
+  </si>
+  <si>
+    <t>User should be able to search for a Group</t>
+  </si>
+  <si>
+    <t>TC_FB_Groups_2</t>
+  </si>
+  <si>
+    <t>TC_FB_Groups_3</t>
+  </si>
+  <si>
+    <t>Verify that the user can join a group successfully.</t>
+  </si>
+  <si>
+    <t>Join a Group</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword - Aliexpress coupon ඉක්මන්ට ගනිමු</t>
+  </si>
+  <si>
+    <t>User should be able to join a Group</t>
+  </si>
+  <si>
+    <t>Verify that the user can create a post in a group</t>
+  </si>
+  <si>
+    <t>Post in a Group</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Enter the group name in the search bar.
+05. Click the search icon.
+06. Press Enter.
+07. Navigate to the group page from the search results.
+08. Click on the "Join Group" button.</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Enter the group name in the search bar.
+05. Press Enter.
+06. Navigate to the group page from the search results.
+07.. Click on the "Join Group" button.
+08. Navigate to a group
+09. Locate the "Create Post" text box.
+10. Enter a message and attach media or files to the post.
+11. Click on the "Post" button.</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword - Aliexpress coupon ඉක්මන්ට ගනිමු
+Text - This is a Test Post by -KAVISHKA-
+Image</t>
+  </si>
+  <si>
+    <t>The post appears in the group feed with the entered text and media.
+The post is attributed to the user’s profile.</t>
   </si>
 </sst>
 </file>
@@ -1564,7 +1653,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1625,8 +1714,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF339933"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1663,11 +1758,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1780,6 +1886,22 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3836,6 +3958,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF339933"/>
       <color rgb="FFCCCC00"/>
       <color rgb="FFC72DC0"/>
     </mruColors>
@@ -4354,7 +4477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:N152"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -7312,11 +7435,229 @@
       </c>
       <c r="N139" s="14"/>
     </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A142" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B142" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A143" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A144" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A145" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="B145" s="1">
+        <v>45670</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A146" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A147" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B147" s="1">
+        <v>45669</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A149" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B149" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F149" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="H149" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="I149" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="J149" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="K149" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="L149" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="M149" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="N149" s="49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" ht="146.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B150" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="C150" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="D150" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="E150" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="F150" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G150" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="H150" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="I150" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="J150" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="K150" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L150" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M150" s="36">
+        <v>45670</v>
+      </c>
+      <c r="N150" s="45"/>
+    </row>
+    <row r="151" spans="1:14" ht="183.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B151" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="C151" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="D151" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="E151" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="F151" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G151" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="H151" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="I151" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="J151" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="K151" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L151" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M151" s="36">
+        <v>45670</v>
+      </c>
+      <c r="N151" s="45"/>
+    </row>
+    <row r="152" spans="1:14" ht="252" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B152" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="C152" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="D152" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="E152" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="F152" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G152" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="H152" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="I152" s="31" t="s">
+        <v>394</v>
+      </c>
+      <c r="J152" s="31" t="s">
+        <v>394</v>
+      </c>
+      <c r="K152" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L152" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M152" s="36">
+        <v>45670</v>
+      </c>
+      <c r="N152" s="45"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="9">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -7325,6 +7666,7 @@
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06CC7C3-6EED-4FA8-B3E6-7BA7A2B9D655}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB902252-74EF-4F27-ADBF-06A0A2CFE795}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="415">
   <si>
     <t>Project Name</t>
   </si>
@@ -1604,6 +1604,101 @@
   <si>
     <t>The post appears in the group feed with the entered text and media.
 The post is attributed to the user’s profile.</t>
+  </si>
+  <si>
+    <t>TC_FB_Groups_4</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Enter the group name in the search bar.
+05. Press Enter.
+06. Navigate to the group page from the search results.
+07.. Click on the "Join Group" button.
+08. Navigate to a group
+09. Locate a post in the feed.
+10. Click the "Like" button for the post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword - Aliexpress coupon ඉක්මන්ට ගනිමු
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The "Like" button changes state.
+The like count for the post increases by one.
+</t>
+  </si>
+  <si>
+    <t>Verify that the user can React a post in the group.</t>
+  </si>
+  <si>
+    <t>React a Post in a Group</t>
+  </si>
+  <si>
+    <t>User should be able to React a Post in a Group</t>
+  </si>
+  <si>
+    <t>TC_FB_Groups_5</t>
+  </si>
+  <si>
+    <t>Verify that the user can comment on a post in the group.</t>
+  </si>
+  <si>
+    <t>Comment on a Post in a Group</t>
+  </si>
+  <si>
+    <t>User should be able to Comment on a Post in a Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The comment appears under the post in the group feed.
+The comment is attributed to the user’s profile.
+The comment count for the post increases by one.
+</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword - Aliexpress coupon ඉක්මන්ට ගනිමු
+Comment - This is a test comment by -KAVISHKA-</t>
+  </si>
+  <si>
+    <t>TC_FB_Groups_6</t>
+  </si>
+  <si>
+    <t>Verify that the user can leave a group.</t>
+  </si>
+  <si>
+    <t>Leave a Group</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Enter the group name in the search bar.
+05. Press Enter.
+06. Navigate to the group page from the search results.
+07.. Click on the "Join Group" button.
+08. Navigate to a group
+09.Click on the "Joined" button.
+10. Select "Leave Group" from the dropdown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword - Aliexpress coupon ඉක්මන්ට ගනිමු
+</t>
+  </si>
+  <si>
+    <t>User should be able to Leave a Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The user is no longer a member of the group.
+The "Join Group" button is visible on the group page again.
+Posts and interactions in the group are no longer accessible.
+</t>
   </si>
 </sst>
 </file>
@@ -4477,7 +4572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:N155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -7480,7 +7575,7 @@
         <v>5</v>
       </c>
       <c r="B147" s="1">
-        <v>45669</v>
+        <v>45671</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
@@ -7652,6 +7747,132 @@
         <v>45670</v>
       </c>
       <c r="N152" s="45"/>
+    </row>
+    <row r="153" spans="1:14" ht="235.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B153" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="C153" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="D153" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="E153" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="F153" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G153" s="31" t="s">
+        <v>397</v>
+      </c>
+      <c r="H153" s="34" t="s">
+        <v>401</v>
+      </c>
+      <c r="I153" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="J153" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="K153" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L153" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M153" s="36">
+        <v>45671</v>
+      </c>
+      <c r="N153" s="45"/>
+    </row>
+    <row r="154" spans="1:14" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A154" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B154" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="C154" s="32" t="s">
+        <v>402</v>
+      </c>
+      <c r="D154" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="E154" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="F154" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G154" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="H154" s="34" t="s">
+        <v>405</v>
+      </c>
+      <c r="I154" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="J154" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="K154" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L154" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M154" s="36">
+        <v>45671</v>
+      </c>
+      <c r="N154" s="45"/>
+    </row>
+    <row r="155" spans="1:14" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="44" t="s">
+        <v>375</v>
+      </c>
+      <c r="B155" s="31" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="32" t="s">
+        <v>408</v>
+      </c>
+      <c r="D155" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="E155" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="F155" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G155" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="H155" s="34" t="s">
+        <v>413</v>
+      </c>
+      <c r="I155" s="31" t="s">
+        <v>414</v>
+      </c>
+      <c r="J155" s="31" t="s">
+        <v>414</v>
+      </c>
+      <c r="K155" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="L155" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="M155" s="36">
+        <v>45671</v>
+      </c>
+      <c r="N155" s="45"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB902252-74EF-4F27-ADBF-06A0A2CFE795}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8A4BF3-3107-4A5B-8D58-B62555A293F5}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="N153" s="45"/>
     </row>
-    <row r="154" spans="1:14" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" ht="219.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="44" t="s">
         <v>375</v>
       </c>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8A4BF3-3107-4A5B-8D58-B62555A293F5}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28016C93-2147-476C-B5BC-DB405A6907B1}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="503">
   <si>
     <t>Project Name</t>
   </si>
@@ -1700,12 +1700,374 @@
 Posts and interactions in the group are no longer accessible.
 </t>
   </si>
+  <si>
+    <t>FaceBook Notifications</t>
+  </si>
+  <si>
+    <t>TS_FB_11</t>
+  </si>
+  <si>
+    <t>Verify Notifications Icon is Clickable</t>
+  </si>
+  <si>
+    <t>TC_FB_Notify_1</t>
+  </si>
+  <si>
+    <t>TC_FB_Notify_2</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Locate the notifications icon (bell icon).
+05. Click on the notifications icon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Username - jigiwi7156@jofuso.com
+Password - Celkon
+</t>
+  </si>
+  <si>
+    <t>User should be able to view notifications</t>
+  </si>
+  <si>
+    <t>The notifications panel should open, displaying recent notifications.</t>
+  </si>
+  <si>
+    <t>Verify Notifications Content</t>
+  </si>
+  <si>
+    <t>The notification should no longer appear highlighted or as "unread."</t>
+  </si>
+  <si>
+    <t>User should be able to read an unreaded notification</t>
+  </si>
+  <si>
+    <t>Verify Notifications Icon Functionality</t>
+  </si>
+  <si>
+    <t>Verify Marking Notifications as Read</t>
+  </si>
+  <si>
+    <t>TC_FB_Notify_3</t>
+  </si>
+  <si>
+    <t>Verify Real-time Notifications</t>
+  </si>
+  <si>
+    <t>Check Real-time Notifications</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the notifications icon.
+05 .Click on an unread notification.
+06. Check if the notification's state changes to "read."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04.Send a friend request to another user (User B).
+05.Login to User B's Facebook account.
+06.  Click on the notifications icon. 
+07.Check if a real-time notification appears in Browser
+</t>
+  </si>
+  <si>
+    <t>User should be able to receive real time notification</t>
+  </si>
+  <si>
+    <t>A real-time notification should appears</t>
+  </si>
+  <si>
+    <t>TC_FB_Notify_4</t>
+  </si>
+  <si>
+    <t>Verify Notification Redirects to Correct Content</t>
+  </si>
+  <si>
+    <t>Verify Notification Redirection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04.  Click on the notifications icon. 
+05.Click on a notification from the list.
+06. Verify that it redirects to the appropriate post, profile, or content.
+</t>
+  </si>
+  <si>
+    <t>The user should be redirected to the correct section or content associated with the notification.</t>
+  </si>
+  <si>
+    <t>User should be able to redirected to the correct section or content associated with the notification.</t>
+  </si>
+  <si>
+    <t>TC_FB_Notify_5</t>
+  </si>
+  <si>
+    <t>Verify Load More Notifications</t>
+  </si>
+  <si>
+    <t>Load Additional Notifications</t>
+  </si>
+  <si>
+    <t>Additional notifications should load seamlessly.</t>
+  </si>
+  <si>
+    <t>User should be able to view more notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the notifications icon. 
+05.Click on "See All" or equivalent button.
+</t>
+  </si>
+  <si>
+    <t>TC_FB_Notify_6</t>
+  </si>
+  <si>
+    <t>Verify Delete Notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the notifications icon. 
+05.Select a notification
+06.Click on "more" button.
+07..Click on "Delete this notification" button.
+</t>
+  </si>
+  <si>
+    <t>User should be able to Delete notifications</t>
+  </si>
+  <si>
+    <t>Notifications should Deleted.</t>
+  </si>
+  <si>
+    <t>TS_FB_12</t>
+  </si>
+  <si>
+    <t>FaceBook Videos and Reels</t>
+  </si>
+  <si>
+    <t>Verify Facebok Videos and playback functinality Functionality</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_1</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_2</t>
+  </si>
+  <si>
+    <t>Verify Navigation to Videos Section</t>
+  </si>
+  <si>
+    <t>The "Videos" page should load successfully.
+The page title or header should confirm navigation to the Videos section.
+A list of video thumbnails should be visible.</t>
+  </si>
+  <si>
+    <t>User should be able to Visit Videos Section</t>
+  </si>
+  <si>
+    <t>Verify Navigation to Reels Section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" section in the navigation bar.
+</t>
+  </si>
+  <si>
+    <t>The "Reels" page should load successfully.
+The page displays a list/grid of short videos (Reels).</t>
+  </si>
+  <si>
+    <t>User should be able to Visit Facebook Reels Section</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_3</t>
+  </si>
+  <si>
+    <t>Verify Video Playback Functionality</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" or "Watch" section in the navigation bar.
+05. Click on the "Reels" section in the sidebar menu.</t>
+  </si>
+  <si>
+    <t>The video should start playing automatically or upon clicking the play button.
+Video playback controls should be functional.
+The video should play without errors</t>
+  </si>
+  <si>
+    <t>User should be able to play videos on Facebook</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_4</t>
+  </si>
+  <si>
+    <t>Verify Reel Playback Functionality</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" or "Watch" section in the navigation bar.
+05. Click on any video thumbnail to start playback
+06. Check for the presence of controls like play, pause, volume, fullscreen.</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" or "Watch" section in the navigation bar.
+05. Click on any reel thumbnail.
+06. Swipe to view the next reel.</t>
+  </si>
+  <si>
+    <t>The reel should play in a vertical format.
+swiping should load and play the next reel seamlessly.</t>
+  </si>
+  <si>
+    <t>User should be able to play Reels on Facebook</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_5</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" or "Watch" section in the navigation bar.
+05.Play a video.
+06. Locate and click on the "Like" button</t>
+  </si>
+  <si>
+    <t>User should be able to React on videos on Facebook</t>
+  </si>
+  <si>
+    <t>Verify React Functionality in Videos</t>
+  </si>
+  <si>
+    <t>Clicking the "Like" button should toggle its state to indicate a React.
+The like count should increase by 1</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_6</t>
+  </si>
+  <si>
+    <t>Verify Comment Functionality in Videos</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Comment - "This is a test comment, From KAVISHKA"  + Emoji</t>
+  </si>
+  <si>
+    <t>The comment should appear in the list below the video.
+No error message should appear during the process.</t>
+  </si>
+  <si>
+    <t>User should be able to comment on videos on Facebook</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_7</t>
+  </si>
+  <si>
+    <t>Verify Share Functionality in Videos</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" or "Watch" section in the navigation bar.
+05. Play a video.
+06.Locate and click on the "Comment" button
+07. Enter a comment</t>
+  </si>
+  <si>
+    <t>User should be able to share  videos on Facebook</t>
+  </si>
+  <si>
+    <t>The video should be shared to the feed.
+A confirmation message , "Shared successfully"should appear.</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_8</t>
+  </si>
+  <si>
+    <t>Verify Video Search Functionality</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" or "Watch" section in the navigation bar.
+05. Play a video.
+06. Click on Share
+07.Choose an option (share to a feed)</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" or "Watch" section in the navigation bar.
+05. Play a video.
+06.Locate the search bar  
+07. Enter a keyword related to a video.
+08. Click the search button or press Enter</t>
+  </si>
+  <si>
+    <t>Videos matching the keyword should appear in the search results.</t>
+  </si>
+  <si>
+    <t>User should be able to Search  videos on Facebook</t>
+  </si>
+  <si>
+    <t>TC_FB_Reels_9</t>
+  </si>
+  <si>
+    <t>Username - jigiwi7156@jofuso.com
+Password - Celkon
+Keyword - Iron man</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the "Videos" or "Watch" section in the navigation bar.
+05. Play a video.
+06. Click the fullscreen button on the video player.
+07. Exit fullscreen mode by pressing "Esc" or clicking the exit button</t>
+  </si>
+  <si>
+    <t>The video should switch to fullscreen mode.
+Exiting fullscreen mode should restore the original view..</t>
+  </si>
+  <si>
+    <t>User should be able to switch to fullscreen mode in videos on Facebook</t>
+  </si>
+  <si>
+    <t>Verify Full-Screen Mode in Videos</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1747,8 +2109,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1815,8 +2199,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1864,11 +2260,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1995,6 +2422,54 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4572,7 +5047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N155"/>
+  <dimension ref="A1:N190"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -6724,7 +7199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="192" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" ht="174.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="35" t="s">
         <v>256</v>
       </c>
@@ -6766,7 +7241,7 @@
       </c>
       <c r="N113" s="31"/>
     </row>
-    <row r="114" spans="1:14" ht="210.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" ht="279" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="35" t="s">
         <v>256</v>
       </c>
@@ -7873,6 +8348,820 @@
         <v>45671</v>
       </c>
       <c r="N155" s="45"/>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A158" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B158" s="57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A159" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="B159" s="57" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A160" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="B160" s="57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A161" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B161" s="59">
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A162" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="B162" s="57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A163" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" s="59">
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A165" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B165" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="F165" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="H165" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="I165" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="J165" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="K165" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="L165" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="M165" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="N165" s="63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" ht="122.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="B166" s="51" t="s">
+        <v>427</v>
+      </c>
+      <c r="C166" s="52" t="s">
+        <v>418</v>
+      </c>
+      <c r="D166" s="51" t="s">
+        <v>417</v>
+      </c>
+      <c r="E166" s="51" t="s">
+        <v>420</v>
+      </c>
+      <c r="F166" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G166" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H166" s="54" t="s">
+        <v>422</v>
+      </c>
+      <c r="I166" s="51" t="s">
+        <v>423</v>
+      </c>
+      <c r="J166" s="51" t="s">
+        <v>423</v>
+      </c>
+      <c r="K166" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L166" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M166" s="56">
+        <v>45672</v>
+      </c>
+      <c r="N166" s="58"/>
+    </row>
+    <row r="167" spans="1:14" ht="150.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="B167" s="51" t="s">
+        <v>428</v>
+      </c>
+      <c r="C167" s="52" t="s">
+        <v>419</v>
+      </c>
+      <c r="D167" s="51" t="s">
+        <v>424</v>
+      </c>
+      <c r="E167" s="51" t="s">
+        <v>432</v>
+      </c>
+      <c r="F167" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G167" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H167" s="54" t="s">
+        <v>426</v>
+      </c>
+      <c r="I167" s="51" t="s">
+        <v>425</v>
+      </c>
+      <c r="J167" s="51" t="s">
+        <v>425</v>
+      </c>
+      <c r="K167" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L167" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M167" s="56">
+        <v>45672</v>
+      </c>
+      <c r="N167" s="58"/>
+    </row>
+    <row r="168" spans="1:14" ht="183" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="B168" s="51" t="s">
+        <v>431</v>
+      </c>
+      <c r="C168" s="52" t="s">
+        <v>429</v>
+      </c>
+      <c r="D168" s="51" t="s">
+        <v>430</v>
+      </c>
+      <c r="E168" s="51" t="s">
+        <v>433</v>
+      </c>
+      <c r="F168" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G168" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H168" s="54" t="s">
+        <v>434</v>
+      </c>
+      <c r="I168" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="J168" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="K168" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L168" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M168" s="56">
+        <v>45672</v>
+      </c>
+      <c r="N168" s="58"/>
+    </row>
+    <row r="169" spans="1:14" ht="157.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="B169" s="51" t="s">
+        <v>438</v>
+      </c>
+      <c r="C169" s="52" t="s">
+        <v>436</v>
+      </c>
+      <c r="D169" s="51" t="s">
+        <v>437</v>
+      </c>
+      <c r="E169" s="51" t="s">
+        <v>439</v>
+      </c>
+      <c r="F169" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G169" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H169" s="54" t="s">
+        <v>441</v>
+      </c>
+      <c r="I169" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="J169" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="K169" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L169" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M169" s="56">
+        <v>45672</v>
+      </c>
+      <c r="N169" s="58"/>
+    </row>
+    <row r="170" spans="1:14" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="B170" s="51" t="s">
+        <v>444</v>
+      </c>
+      <c r="C170" s="52" t="s">
+        <v>442</v>
+      </c>
+      <c r="D170" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="E170" s="51" t="s">
+        <v>447</v>
+      </c>
+      <c r="F170" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G170" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H170" s="54" t="s">
+        <v>446</v>
+      </c>
+      <c r="I170" s="51" t="s">
+        <v>445</v>
+      </c>
+      <c r="J170" s="51" t="s">
+        <v>445</v>
+      </c>
+      <c r="K170" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L170" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M170" s="56">
+        <v>45672</v>
+      </c>
+      <c r="N170" s="58"/>
+    </row>
+    <row r="171" spans="1:14" ht="139.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="B171" s="51" t="s">
+        <v>444</v>
+      </c>
+      <c r="C171" s="52" t="s">
+        <v>448</v>
+      </c>
+      <c r="D171" s="51" t="s">
+        <v>449</v>
+      </c>
+      <c r="E171" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="F171" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G171" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H171" s="54" t="s">
+        <v>451</v>
+      </c>
+      <c r="I171" s="51" t="s">
+        <v>452</v>
+      </c>
+      <c r="J171" s="51" t="s">
+        <v>452</v>
+      </c>
+      <c r="K171" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L171" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M171" s="56">
+        <v>45672</v>
+      </c>
+      <c r="N171" s="58"/>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A174" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B174" s="57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A175" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="B175" s="57" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A176" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="B176" s="57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A177" s="64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B177" s="59">
+        <v>45673</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A178" s="64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B178" s="57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A179" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B179" s="59">
+        <v>45673</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A181" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="B181" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="F181" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="66" t="s">
+        <v>29</v>
+      </c>
+      <c r="H181" s="66" t="s">
+        <v>30</v>
+      </c>
+      <c r="I181" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="J181" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="K181" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="L181" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="M181" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="N181" s="67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" ht="193.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B182" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C182" s="52" t="s">
+        <v>456</v>
+      </c>
+      <c r="D182" s="51" t="s">
+        <v>458</v>
+      </c>
+      <c r="E182" s="51" t="s">
+        <v>462</v>
+      </c>
+      <c r="F182" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G182" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H182" s="54" t="s">
+        <v>460</v>
+      </c>
+      <c r="I182" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="J182" s="51" t="s">
+        <v>459</v>
+      </c>
+      <c r="K182" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L182" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M182" s="56">
+        <v>45673</v>
+      </c>
+      <c r="N182" s="58"/>
+    </row>
+    <row r="183" spans="1:14" ht="128.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B183" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C183" s="52" t="s">
+        <v>457</v>
+      </c>
+      <c r="D183" s="51" t="s">
+        <v>461</v>
+      </c>
+      <c r="E183" s="51" t="s">
+        <v>467</v>
+      </c>
+      <c r="F183" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G183" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H183" s="54" t="s">
+        <v>464</v>
+      </c>
+      <c r="I183" s="51" t="s">
+        <v>463</v>
+      </c>
+      <c r="J183" s="51" t="s">
+        <v>463</v>
+      </c>
+      <c r="K183" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L183" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M183" s="56">
+        <v>45673</v>
+      </c>
+      <c r="N183" s="58"/>
+    </row>
+    <row r="184" spans="1:14" ht="164.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B184" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C184" s="52" t="s">
+        <v>465</v>
+      </c>
+      <c r="D184" s="51" t="s">
+        <v>466</v>
+      </c>
+      <c r="E184" s="51" t="s">
+        <v>472</v>
+      </c>
+      <c r="F184" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G184" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H184" s="54" t="s">
+        <v>469</v>
+      </c>
+      <c r="I184" s="51" t="s">
+        <v>468</v>
+      </c>
+      <c r="J184" s="51" t="s">
+        <v>468</v>
+      </c>
+      <c r="K184" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L184" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M184" s="56">
+        <v>45673</v>
+      </c>
+      <c r="N184" s="58"/>
+    </row>
+    <row r="185" spans="1:14" ht="166.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B185" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C185" s="52" t="s">
+        <v>470</v>
+      </c>
+      <c r="D185" s="51" t="s">
+        <v>471</v>
+      </c>
+      <c r="E185" s="51" t="s">
+        <v>473</v>
+      </c>
+      <c r="F185" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G185" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H185" s="54" t="s">
+        <v>475</v>
+      </c>
+      <c r="I185" s="51" t="s">
+        <v>474</v>
+      </c>
+      <c r="J185" s="51" t="s">
+        <v>474</v>
+      </c>
+      <c r="K185" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L185" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M185" s="56">
+        <v>45673</v>
+      </c>
+      <c r="N185" s="58"/>
+    </row>
+    <row r="186" spans="1:14" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B186" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C186" s="52" t="s">
+        <v>476</v>
+      </c>
+      <c r="D186" s="51" t="s">
+        <v>479</v>
+      </c>
+      <c r="E186" s="51" t="s">
+        <v>477</v>
+      </c>
+      <c r="F186" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G186" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H186" s="54" t="s">
+        <v>478</v>
+      </c>
+      <c r="I186" s="51" t="s">
+        <v>480</v>
+      </c>
+      <c r="J186" s="51" t="s">
+        <v>480</v>
+      </c>
+      <c r="K186" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L186" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M186" s="56">
+        <v>45674</v>
+      </c>
+      <c r="N186" s="58"/>
+    </row>
+    <row r="187" spans="1:14" ht="161.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B187" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C187" s="52" t="s">
+        <v>481</v>
+      </c>
+      <c r="D187" s="51" t="s">
+        <v>482</v>
+      </c>
+      <c r="E187" s="51" t="s">
+        <v>488</v>
+      </c>
+      <c r="F187" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G187" s="51" t="s">
+        <v>483</v>
+      </c>
+      <c r="H187" s="54" t="s">
+        <v>485</v>
+      </c>
+      <c r="I187" s="51" t="s">
+        <v>484</v>
+      </c>
+      <c r="J187" s="51" t="s">
+        <v>484</v>
+      </c>
+      <c r="K187" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L187" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M187" s="56">
+        <v>45674</v>
+      </c>
+      <c r="N187" s="58"/>
+    </row>
+    <row r="188" spans="1:14" ht="170.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B188" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C188" s="52" t="s">
+        <v>486</v>
+      </c>
+      <c r="D188" s="51" t="s">
+        <v>487</v>
+      </c>
+      <c r="E188" s="51" t="s">
+        <v>493</v>
+      </c>
+      <c r="F188" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G188" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H188" s="54" t="s">
+        <v>489</v>
+      </c>
+      <c r="I188" s="51" t="s">
+        <v>490</v>
+      </c>
+      <c r="J188" s="51" t="s">
+        <v>490</v>
+      </c>
+      <c r="K188" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L188" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M188" s="56">
+        <v>45674</v>
+      </c>
+      <c r="N188" s="58"/>
+    </row>
+    <row r="189" spans="1:14" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B189" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C189" s="52" t="s">
+        <v>491</v>
+      </c>
+      <c r="D189" s="51" t="s">
+        <v>492</v>
+      </c>
+      <c r="E189" s="51" t="s">
+        <v>494</v>
+      </c>
+      <c r="F189" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G189" s="51" t="s">
+        <v>498</v>
+      </c>
+      <c r="H189" s="54" t="s">
+        <v>496</v>
+      </c>
+      <c r="I189" s="51" t="s">
+        <v>495</v>
+      </c>
+      <c r="J189" s="51" t="s">
+        <v>495</v>
+      </c>
+      <c r="K189" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L189" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M189" s="56">
+        <v>45674</v>
+      </c>
+      <c r="N189" s="58"/>
+    </row>
+    <row r="190" spans="1:14" ht="197.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B190" s="51" t="s">
+        <v>455</v>
+      </c>
+      <c r="C190" s="52" t="s">
+        <v>497</v>
+      </c>
+      <c r="D190" s="51" t="s">
+        <v>502</v>
+      </c>
+      <c r="E190" s="51" t="s">
+        <v>499</v>
+      </c>
+      <c r="F190" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G190" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H190" s="54" t="s">
+        <v>501</v>
+      </c>
+      <c r="I190" s="51" t="s">
+        <v>500</v>
+      </c>
+      <c r="J190" s="51" t="s">
+        <v>500</v>
+      </c>
+      <c r="K190" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L190" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M190" s="56">
+        <v>45674</v>
+      </c>
+      <c r="N190" s="58"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28016C93-2147-476C-B5BC-DB405A6907B1}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E31489-2C03-4B02-B2A8-CF8B09F3C801}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="515">
   <si>
     <t>Project Name</t>
   </si>
@@ -1857,9 +1857,6 @@
     <t>FaceBook Videos and Reels</t>
   </si>
   <si>
-    <t>Verify Facebok Videos and playback functinality Functionality</t>
-  </si>
-  <si>
     <t>TC_FB_Reels_1</t>
   </si>
   <si>
@@ -2061,6 +2058,58 @@
   </si>
   <si>
     <t>Verify Full-Screen Mode in Videos</t>
+  </si>
+  <si>
+    <t>TS_FB_13</t>
+  </si>
+  <si>
+    <t>Verify Facebok Videos and Reels playback Functionality</t>
+  </si>
+  <si>
+    <t>Verify Facebok Settings Functionality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can access the settings page.
+</t>
+  </si>
+  <si>
+    <t>User should be able to access the settings page.</t>
+  </si>
+  <si>
+    <t>TC_FB_Settings_1</t>
+  </si>
+  <si>
+    <t>The user redirected to the Facebook Settings page.</t>
+  </si>
+  <si>
+    <t>TC_FB_Settings_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can chaange the language of the Facebook webpage.
+</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the profile icon/menu.
+05. Select "Settings &amp; Privacy" from the dropdown menu.
+06. Click on "Settings".</t>
+  </si>
+  <si>
+    <t>01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the profile icon/menu.
+05. Select "Settings &amp; Privacy" from the dropdown menu.
+06. Click on "Language".
+07. Select a Language</t>
+  </si>
+  <si>
+    <t>The user changed language of the Facebook webpage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be able to change the language </t>
   </si>
 </sst>
 </file>
@@ -2132,7 +2181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2208,6 +2257,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -2295,7 +2350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2470,6 +2525,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -5047,7 +5112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N190"/>
+  <dimension ref="A1:N202"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -8738,7 +8803,7 @@
         <v>5</v>
       </c>
       <c r="B179" s="59">
-        <v>45673</v>
+        <v>45674</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
@@ -8790,16 +8855,16 @@
         <v>453</v>
       </c>
       <c r="B182" s="51" t="s">
+        <v>503</v>
+      </c>
+      <c r="C182" s="52" t="s">
         <v>455</v>
       </c>
-      <c r="C182" s="52" t="s">
-        <v>456</v>
-      </c>
       <c r="D182" s="51" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E182" s="51" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F182" s="53" t="s">
         <v>33</v>
@@ -8808,13 +8873,13 @@
         <v>421</v>
       </c>
       <c r="H182" s="54" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I182" s="51" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J182" s="51" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K182" s="55" t="s">
         <v>96</v>
@@ -8832,16 +8897,16 @@
         <v>453</v>
       </c>
       <c r="B183" s="51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C183" s="52" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D183" s="51" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E183" s="51" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F183" s="53" t="s">
         <v>33</v>
@@ -8850,13 +8915,13 @@
         <v>421</v>
       </c>
       <c r="H183" s="54" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I183" s="51" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J183" s="51" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K183" s="55" t="s">
         <v>96</v>
@@ -8874,16 +8939,16 @@
         <v>453</v>
       </c>
       <c r="B184" s="51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C184" s="52" t="s">
+        <v>464</v>
+      </c>
+      <c r="D184" s="51" t="s">
         <v>465</v>
       </c>
-      <c r="D184" s="51" t="s">
-        <v>466</v>
-      </c>
       <c r="E184" s="51" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F184" s="53" t="s">
         <v>33</v>
@@ -8892,13 +8957,13 @@
         <v>421</v>
       </c>
       <c r="H184" s="54" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I184" s="51" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J184" s="51" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K184" s="55" t="s">
         <v>96</v>
@@ -8916,16 +8981,16 @@
         <v>453</v>
       </c>
       <c r="B185" s="51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C185" s="52" t="s">
+        <v>469</v>
+      </c>
+      <c r="D185" s="51" t="s">
         <v>470</v>
       </c>
-      <c r="D185" s="51" t="s">
-        <v>471</v>
-      </c>
       <c r="E185" s="51" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F185" s="53" t="s">
         <v>33</v>
@@ -8934,13 +8999,13 @@
         <v>421</v>
       </c>
       <c r="H185" s="54" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I185" s="51" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J185" s="51" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K185" s="55" t="s">
         <v>96</v>
@@ -8958,16 +9023,16 @@
         <v>453</v>
       </c>
       <c r="B186" s="51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C186" s="52" t="s">
+        <v>475</v>
+      </c>
+      <c r="D186" s="51" t="s">
+        <v>478</v>
+      </c>
+      <c r="E186" s="51" t="s">
         <v>476</v>
-      </c>
-      <c r="D186" s="51" t="s">
-        <v>479</v>
-      </c>
-      <c r="E186" s="51" t="s">
-        <v>477</v>
       </c>
       <c r="F186" s="53" t="s">
         <v>33</v>
@@ -8976,13 +9041,13 @@
         <v>421</v>
       </c>
       <c r="H186" s="54" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I186" s="51" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J186" s="51" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K186" s="55" t="s">
         <v>96</v>
@@ -9000,31 +9065,31 @@
         <v>453</v>
       </c>
       <c r="B187" s="51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C187" s="52" t="s">
+        <v>480</v>
+      </c>
+      <c r="D187" s="51" t="s">
         <v>481</v>
       </c>
-      <c r="D187" s="51" t="s">
-        <v>482</v>
-      </c>
       <c r="E187" s="51" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F187" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G187" s="51" t="s">
+        <v>482</v>
+      </c>
+      <c r="H187" s="54" t="s">
+        <v>484</v>
+      </c>
+      <c r="I187" s="51" t="s">
         <v>483</v>
       </c>
-      <c r="H187" s="54" t="s">
-        <v>485</v>
-      </c>
-      <c r="I187" s="51" t="s">
-        <v>484</v>
-      </c>
       <c r="J187" s="51" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K187" s="55" t="s">
         <v>96</v>
@@ -9042,16 +9107,16 @@
         <v>453</v>
       </c>
       <c r="B188" s="51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C188" s="52" t="s">
+        <v>485</v>
+      </c>
+      <c r="D188" s="51" t="s">
         <v>486</v>
       </c>
-      <c r="D188" s="51" t="s">
-        <v>487</v>
-      </c>
       <c r="E188" s="51" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F188" s="53" t="s">
         <v>33</v>
@@ -9060,13 +9125,13 @@
         <v>421</v>
       </c>
       <c r="H188" s="54" t="s">
+        <v>488</v>
+      </c>
+      <c r="I188" s="51" t="s">
         <v>489</v>
       </c>
-      <c r="I188" s="51" t="s">
-        <v>490</v>
-      </c>
       <c r="J188" s="51" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K188" s="55" t="s">
         <v>96</v>
@@ -9084,31 +9149,31 @@
         <v>453</v>
       </c>
       <c r="B189" s="51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C189" s="52" t="s">
+        <v>490</v>
+      </c>
+      <c r="D189" s="51" t="s">
         <v>491</v>
       </c>
-      <c r="D189" s="51" t="s">
-        <v>492</v>
-      </c>
       <c r="E189" s="51" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F189" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G189" s="51" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H189" s="54" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I189" s="51" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J189" s="51" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K189" s="55" t="s">
         <v>96</v>
@@ -9126,16 +9191,16 @@
         <v>453</v>
       </c>
       <c r="B190" s="51" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="C190" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D190" s="51" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E190" s="51" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F190" s="53" t="s">
         <v>33</v>
@@ -9144,13 +9209,13 @@
         <v>421</v>
       </c>
       <c r="H190" s="54" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I190" s="51" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J190" s="51" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K190" s="55" t="s">
         <v>96</v>
@@ -9162,6 +9227,182 @@
         <v>45674</v>
       </c>
       <c r="N190" s="58"/>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A193" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B193" s="57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A194" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="B194" s="57" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A195" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B195" s="57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A196" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="B196" s="59">
+        <v>45675</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A197" s="68" t="s">
+        <v>4</v>
+      </c>
+      <c r="B197" s="57" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A198" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B198" s="59">
+        <v>45675</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A200" s="69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B200" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="F200" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" s="70" t="s">
+        <v>29</v>
+      </c>
+      <c r="H200" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="I200" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="J200" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="K200" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="L200" s="70" t="s">
+        <v>14</v>
+      </c>
+      <c r="M200" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N200" s="71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" ht="178.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="B201" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="C201" s="52" t="s">
+        <v>507</v>
+      </c>
+      <c r="D201" s="51" t="s">
+        <v>505</v>
+      </c>
+      <c r="E201" s="51" t="s">
+        <v>511</v>
+      </c>
+      <c r="F201" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G201" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H201" s="54" t="s">
+        <v>506</v>
+      </c>
+      <c r="I201" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="J201" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="K201" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L201" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M201" s="56">
+        <v>45675</v>
+      </c>
+      <c r="N201" s="58"/>
+    </row>
+    <row r="202" spans="1:14" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="B202" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="C202" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="D202" s="51" t="s">
+        <v>510</v>
+      </c>
+      <c r="E202" s="51" t="s">
+        <v>512</v>
+      </c>
+      <c r="F202" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G202" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H202" s="54" t="s">
+        <v>514</v>
+      </c>
+      <c r="I202" s="51" t="s">
+        <v>513</v>
+      </c>
+      <c r="J202" s="51" t="s">
+        <v>513</v>
+      </c>
+      <c r="K202" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L202" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M202" s="56">
+        <v>45675</v>
+      </c>
+      <c r="N202" s="58"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E31489-2C03-4B02-B2A8-CF8B09F3C801}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C01E64-6D05-4C9B-AB03-40137E579F3F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C01E64-6D05-4C9B-AB03-40137E579F3F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640AECC0-05E1-451F-9A00-6460AA83D194}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="546">
   <si>
     <t>Project Name</t>
   </si>
@@ -2085,10 +2085,6 @@
     <t>TC_FB_Settings_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify that the user can chaange the language of the Facebook webpage.
-</t>
-  </si>
-  <si>
     <t>01. Enter a valid username 
 02. Enter a valid password
 03. Click on Login Button
@@ -2110,6 +2106,144 @@
   </si>
   <si>
     <t xml:space="preserve">User should be able to change the language </t>
+  </si>
+  <si>
+    <t>FaceBook Settings</t>
+  </si>
+  <si>
+    <t>TC_FB_Settings_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can change the language of the Facebook webpage.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the profile icon/menu.
+05. Select "Settings &amp; Privacy" from the dropdown menu.
+06. Click on "privacy checkup".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can access the privacy checkup page.
+</t>
+  </si>
+  <si>
+    <t>User should be able to change the privacy checkup settings.</t>
+  </si>
+  <si>
+    <t>The user changed the privacy checkup settings.</t>
+  </si>
+  <si>
+    <t>TC_FB_Settings_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can access the privacy centre
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the profile icon/menu.
+05. Select "Settings &amp; Privacy" from the dropdown menu.
+06. Click on "privacy centre".
+</t>
+  </si>
+  <si>
+    <t>User should be able to access the Privacy Centre.</t>
+  </si>
+  <si>
+    <t>The user access the Privacy Centre.</t>
+  </si>
+  <si>
+    <t>TC_FB_Settings_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can access Activity Log
+</t>
+  </si>
+  <si>
+    <t>User should be able to view Activity Log</t>
+  </si>
+  <si>
+    <t>The user accessed the Activity Log.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the profile icon/menu.
+05. Select "Settings &amp; Privacy" from the dropdown menu.
+06. Click on "Activity Log".
+</t>
+  </si>
+  <si>
+    <t>TC_FB_Settings_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can switch to dark mode and light mode
+</t>
+  </si>
+  <si>
+    <t>User should be able to switch between dark and light theme.</t>
+  </si>
+  <si>
+    <t>The user  switched between dark and light theme</t>
+  </si>
+  <si>
+    <t>TC_FB_Settings_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can switch to compact mode
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the profile icon/menu.
+05. Select ""Display &amp; accessibility"" from the dopdown menu.
+06. Select and choose Dark mode (On/Off/Automatic)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the profile icon/menu.
+05. Select ""Display &amp; accessibility"" from the dopdown menu.
+06. click on "On"
+</t>
+  </si>
+  <si>
+    <t>User should be able to switch to compact mode</t>
+  </si>
+  <si>
+    <t>The user  switched to compact mode</t>
+  </si>
+  <si>
+    <t>TC_FB_Settings_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the user can logout from Facebook
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01. Enter a valid username 
+02. Enter a valid password
+03. Click on Login Button
+04. Click on the profile icon/menu.
+05. Click on "Log Out"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be able to logout from Facebook website </t>
+  </si>
+  <si>
+    <t>The user logged out from the facebook.</t>
   </si>
 </sst>
 </file>
@@ -5112,7 +5246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32799D75-E317-4EA9-991F-FF31DA4317A3}">
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:N208"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -9241,7 +9375,7 @@
         <v>1</v>
       </c>
       <c r="B194" s="57" t="s">
-        <v>454</v>
+        <v>514</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
@@ -9257,7 +9391,7 @@
         <v>3</v>
       </c>
       <c r="B196" s="59">
-        <v>45675</v>
+        <v>45687</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.3">
@@ -9273,7 +9407,7 @@
         <v>5</v>
       </c>
       <c r="B198" s="59">
-        <v>45675</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.3">
@@ -9320,7 +9454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:14" ht="178.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14" ht="148.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="50" t="s">
         <v>502</v>
       </c>
@@ -9334,7 +9468,7 @@
         <v>505</v>
       </c>
       <c r="E201" s="51" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F201" s="53" t="s">
         <v>33</v>
@@ -9358,7 +9492,7 @@
         <v>32</v>
       </c>
       <c r="M201" s="56">
-        <v>45675</v>
+        <v>45687</v>
       </c>
       <c r="N201" s="58"/>
     </row>
@@ -9373,10 +9507,10 @@
         <v>509</v>
       </c>
       <c r="D202" s="51" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E202" s="51" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F202" s="53" t="s">
         <v>33</v>
@@ -9385,13 +9519,13 @@
         <v>421</v>
       </c>
       <c r="H202" s="54" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I202" s="51" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J202" s="51" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K202" s="55" t="s">
         <v>96</v>
@@ -9400,9 +9534,261 @@
         <v>32</v>
       </c>
       <c r="M202" s="56">
-        <v>45675</v>
+        <v>45687</v>
       </c>
       <c r="N202" s="58"/>
+    </row>
+    <row r="203" spans="1:14" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="B203" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="C203" s="52" t="s">
+        <v>515</v>
+      </c>
+      <c r="D203" s="51" t="s">
+        <v>518</v>
+      </c>
+      <c r="E203" s="51" t="s">
+        <v>517</v>
+      </c>
+      <c r="F203" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G203" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H203" s="54" t="s">
+        <v>519</v>
+      </c>
+      <c r="I203" s="51" t="s">
+        <v>520</v>
+      </c>
+      <c r="J203" s="51" t="s">
+        <v>520</v>
+      </c>
+      <c r="K203" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L203" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M203" s="56">
+        <v>45687</v>
+      </c>
+      <c r="N203" s="58"/>
+    </row>
+    <row r="204" spans="1:14" ht="137.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="B204" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="C204" s="52" t="s">
+        <v>521</v>
+      </c>
+      <c r="D204" s="51" t="s">
+        <v>522</v>
+      </c>
+      <c r="E204" s="51" t="s">
+        <v>523</v>
+      </c>
+      <c r="F204" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G204" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H204" s="54" t="s">
+        <v>524</v>
+      </c>
+      <c r="I204" s="51" t="s">
+        <v>525</v>
+      </c>
+      <c r="J204" s="51" t="s">
+        <v>525</v>
+      </c>
+      <c r="K204" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L204" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M204" s="56">
+        <v>45687</v>
+      </c>
+      <c r="N204" s="58"/>
+    </row>
+    <row r="205" spans="1:14" ht="143.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="B205" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="C205" s="52" t="s">
+        <v>526</v>
+      </c>
+      <c r="D205" s="51" t="s">
+        <v>527</v>
+      </c>
+      <c r="E205" s="51" t="s">
+        <v>530</v>
+      </c>
+      <c r="F205" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G205" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H205" s="54" t="s">
+        <v>528</v>
+      </c>
+      <c r="I205" s="51" t="s">
+        <v>529</v>
+      </c>
+      <c r="J205" s="51" t="s">
+        <v>529</v>
+      </c>
+      <c r="K205" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L205" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M205" s="56">
+        <v>45687</v>
+      </c>
+      <c r="N205" s="58"/>
+    </row>
+    <row r="206" spans="1:14" ht="182.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="B206" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="C206" s="52" t="s">
+        <v>531</v>
+      </c>
+      <c r="D206" s="51" t="s">
+        <v>532</v>
+      </c>
+      <c r="E206" s="51" t="s">
+        <v>537</v>
+      </c>
+      <c r="F206" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G206" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H206" s="54" t="s">
+        <v>533</v>
+      </c>
+      <c r="I206" s="51" t="s">
+        <v>534</v>
+      </c>
+      <c r="J206" s="51" t="s">
+        <v>534</v>
+      </c>
+      <c r="K206" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L206" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M206" s="56">
+        <v>45688</v>
+      </c>
+      <c r="N206" s="58"/>
+    </row>
+    <row r="207" spans="1:14" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="B207" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="C207" s="52" t="s">
+        <v>535</v>
+      </c>
+      <c r="D207" s="51" t="s">
+        <v>536</v>
+      </c>
+      <c r="E207" s="51" t="s">
+        <v>538</v>
+      </c>
+      <c r="F207" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G207" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H207" s="54" t="s">
+        <v>539</v>
+      </c>
+      <c r="I207" s="51" t="s">
+        <v>540</v>
+      </c>
+      <c r="J207" s="51" t="s">
+        <v>540</v>
+      </c>
+      <c r="K207" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L207" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M207" s="56">
+        <v>45688</v>
+      </c>
+      <c r="N207" s="58"/>
+    </row>
+    <row r="208" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A208" s="50" t="s">
+        <v>502</v>
+      </c>
+      <c r="B208" s="51" t="s">
+        <v>504</v>
+      </c>
+      <c r="C208" s="52" t="s">
+        <v>541</v>
+      </c>
+      <c r="D208" s="51" t="s">
+        <v>542</v>
+      </c>
+      <c r="E208" s="51" t="s">
+        <v>543</v>
+      </c>
+      <c r="F208" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G208" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="H208" s="54" t="s">
+        <v>544</v>
+      </c>
+      <c r="I208" s="51" t="s">
+        <v>545</v>
+      </c>
+      <c r="J208" s="51" t="s">
+        <v>545</v>
+      </c>
+      <c r="K208" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="L208" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="M208" s="56">
+        <v>45688</v>
+      </c>
+      <c r="N208" s="58"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
+++ b/Facebook-Automation-Test/src/test/java/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA\My QA Projects\Facebook Automation Test\Facebook-Automation-Test\src\test\java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640AECC0-05E1-451F-9A00-6460AA83D194}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D40F67A-FDCF-4FF7-82D2-AEB7F89A7E99}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{560DE587-4291-4869-85E5-DA09B090168E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="517">
   <si>
     <t>Project Name</t>
   </si>
@@ -489,11 +489,6 @@
   <si>
     <t>Don't Enter a username 
 &amp; password</t>
-  </si>
-  <si>
-    <t>01. Don’t Enter a username 
-02. Don't Enter a password
-03. Click on Login Button</t>
   </si>
   <si>
     <t xml:space="preserve">Username - 
@@ -758,12 +753,6 @@
     <t>Reacting to post</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify Facebook Post create and edit Fucntionality </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify Facebook post reaction Fucntionality </t>
-  </si>
-  <si>
     <t>React on Facebook posts</t>
   </si>
   <si>
@@ -771,9 +760,6 @@
   </si>
   <si>
     <t>TC_FB_post_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify Facebook comment Fucntionality </t>
   </si>
   <si>
     <t>Write text comment on Facebook posts</t>
@@ -846,9 +832,6 @@
     <t>User should be able to react on posts</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify Facebook Post share Fucntionality </t>
-  </si>
-  <si>
     <t>Share a post on Facebook</t>
   </si>
   <si>
@@ -875,9 +858,6 @@
   </si>
   <si>
     <t>Verify that the user can send multiple messages in a conversation.</t>
-  </si>
-  <si>
-    <t>Verify that the user can send an image file via chat.</t>
   </si>
   <si>
     <t>Verify that the user can send audio messages.</t>
@@ -918,9 +898,6 @@
 06. Click on send button</t>
   </si>
   <si>
-    <t>send a sticker or emoji to a recipient.</t>
-  </si>
-  <si>
     <t>Username - jigiwi7156@jofuso.com
 Password - Celkon
 Message - "This is a test message from KAVISHKA"</t>
@@ -931,9 +908,6 @@
 Message - "This is a test message from KAVISHKA"
 Emoji
 Sticker</t>
-  </si>
-  <si>
-    <t>send multiple messages in a conversation.</t>
   </si>
   <si>
     <t>01. Enter a valid username 
@@ -969,9 +943,6 @@
   </si>
   <si>
     <t>sending an image file to a recipient.</t>
-  </si>
-  <si>
-    <t>send a audio message to a recipient.</t>
   </si>
   <si>
     <t>User should be able to send a audio message in a conversation</t>
@@ -1038,9 +1009,6 @@
     <t>TC_FB_Friends_1</t>
   </si>
   <si>
-    <t>Verify Send Friend Request</t>
-  </si>
-  <si>
     <t>01. Enter a valid username 
 02. Enter a valid password
 03. Click on Login Button
@@ -1068,9 +1036,6 @@
     <t>TC_FB_Friends_5</t>
   </si>
   <si>
-    <t>Verify Accept Friend Request</t>
-  </si>
-  <si>
     <t>User successfully accept the friend request, and the status should change to "Friends."</t>
   </si>
   <si>
@@ -1083,16 +1048,10 @@
     <t>Ensure that a user can accept a friend request from another user.</t>
   </si>
   <si>
-    <t>Verify Unfriend Functionality</t>
-  </si>
-  <si>
     <t>The user successfully unfriended and the button should change back to "Add Friend."</t>
   </si>
   <si>
     <t>User should be successfully unfriended.</t>
-  </si>
-  <si>
-    <t>Verify that the user can View Friend Suggestions</t>
   </si>
   <si>
     <t>Ensure that the friend suggestions section is visible and displays recommendations to user.</t>
@@ -1119,10 +1078,6 @@
 03. Click on Login Button
 04. Navigate to the "Friends" section.
 05.Click on the "All Friends" section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that the user can View Friends List
-</t>
   </si>
   <si>
     <t xml:space="preserve">User should be able to View Friends List
@@ -1152,9 +1107,6 @@
 </t>
   </si>
   <si>
-    <t>Verify Remove Friend Request</t>
-  </si>
-  <si>
     <t>Ensure that a user can Remove a pending friend request.</t>
   </si>
   <si>
@@ -1192,9 +1144,6 @@
     <t>TC_FB_Friends_7</t>
   </si>
   <si>
-    <t>Verify Unfollow Functionality</t>
-  </si>
-  <si>
     <t>Ensure that a user can unfollow an another user from their friend list.</t>
   </si>
   <si>
@@ -1231,9 +1180,6 @@
     <t>TS_FB_09</t>
   </si>
   <si>
-    <t>FaceBook Mrketplace</t>
-  </si>
-  <si>
     <t>TC_FB_Market_1</t>
   </si>
   <si>
@@ -1244,12 +1190,6 @@
   </si>
   <si>
     <t>TC_FB_Market_4</t>
-  </si>
-  <si>
-    <t>Verify searching for an item with valid keywords</t>
-  </si>
-  <si>
-    <t>Verify access to Marketplace after login</t>
   </si>
   <si>
     <t>Login to Access Marketplace</t>
@@ -1292,9 +1232,6 @@
     <t>searching for an item with valid keywords</t>
   </si>
   <si>
-    <t>Verify search with no matching keywords</t>
-  </si>
-  <si>
     <t>searching for an item no matching keywords</t>
   </si>
   <si>
@@ -1317,9 +1254,6 @@
     <t>A message like "No results found" is displaying</t>
   </si>
   <si>
-    <t>Verify applying filters</t>
-  </si>
-  <si>
     <t>Results update according to the selected filters</t>
   </si>
   <si>
@@ -1339,9 +1273,6 @@
   </si>
   <si>
     <t>TC_FB_Market_5</t>
-  </si>
-  <si>
-    <t>Verify posting a new item</t>
   </si>
   <si>
     <t xml:space="preserve">01. Enter a valid username 
@@ -1375,9 +1306,6 @@
     <t>TC_FB_Market_6</t>
   </si>
   <si>
-    <t>Verify posting with missing mandatory fields</t>
-  </si>
-  <si>
     <t>post a new item in the Marketplace missing mandatory fields.</t>
   </si>
   <si>
@@ -1421,9 +1349,6 @@
     <t>TC_FB_Market_7</t>
   </si>
   <si>
-    <t>Verify detailed view of an item</t>
-  </si>
-  <si>
     <t>View item detils</t>
   </si>
   <si>
@@ -1447,9 +1372,6 @@
   </si>
   <si>
     <t>TC_FB_Market_8</t>
-  </si>
-  <si>
-    <t>Verify saving an item to favorites</t>
   </si>
   <si>
     <t>Saving and Favoriting Items</t>
@@ -1473,9 +1395,6 @@
     <t>The item is added to the Saved Items section</t>
   </si>
   <si>
-    <t>Verify accessing saved items</t>
-  </si>
-  <si>
     <t>01. Enter a valid username 
 02. Enter a valid password
 03. Click on Login Button
@@ -1495,9 +1414,6 @@
     <t>TC_FB_Market_10</t>
   </si>
   <si>
-    <t>Verify unauthorized access to Marketplace</t>
-  </si>
-  <si>
     <t>Navigate to the Marketplace without logging in</t>
   </si>
   <si>
@@ -1527,9 +1443,6 @@
   </si>
   <si>
     <t>TC_FB_Groups_1</t>
-  </si>
-  <si>
-    <t>Search for a Group</t>
   </si>
   <si>
     <t>01. Enter a valid username 
@@ -1555,9 +1468,6 @@
     <t>Verify that the user can join a group successfully.</t>
   </si>
   <si>
-    <t>Join a Group</t>
-  </si>
-  <si>
     <t>Username - jigiwi7156@jofuso.com
 Password - Celkon
 Keyword - Aliexpress coupon ඉක්මන්ට ගනිමු</t>
@@ -1567,9 +1477,6 @@
   </si>
   <si>
     <t>Verify that the user can create a post in a group</t>
-  </si>
-  <si>
-    <t>Post in a Group</t>
   </si>
   <si>
     <t>01. Enter a valid username 
@@ -1632,9 +1539,6 @@
 </t>
   </si>
   <si>
-    <t>Verify that the user can React a post in the group.</t>
-  </si>
-  <si>
     <t>React a Post in a Group</t>
   </si>
   <si>
@@ -1645,9 +1549,6 @@
   </si>
   <si>
     <t>Verify that the user can comment on a post in the group.</t>
-  </si>
-  <si>
-    <t>Comment on a Post in a Group</t>
   </si>
   <si>
     <t>User should be able to Comment on a Post in a Group</t>
@@ -1669,9 +1570,6 @@
   </si>
   <si>
     <t>Verify that the user can leave a group.</t>
-  </si>
-  <si>
-    <t>Leave a Group</t>
   </si>
   <si>
     <t>01. Enter a valid username 
@@ -1743,19 +1641,10 @@
     <t>User should be able to read an unreaded notification</t>
   </si>
   <si>
-    <t>Verify Notifications Icon Functionality</t>
-  </si>
-  <si>
-    <t>Verify Marking Notifications as Read</t>
-  </si>
-  <si>
     <t>TC_FB_Notify_3</t>
   </si>
   <si>
     <t>Verify Real-time Notifications</t>
-  </si>
-  <si>
-    <t>Check Real-time Notifications</t>
   </si>
   <si>
     <t>01. Enter a valid username 
@@ -1788,9 +1677,6 @@
     <t>Verify Notification Redirects to Correct Content</t>
   </si>
   <si>
-    <t>Verify Notification Redirection</t>
-  </si>
-  <si>
     <t xml:space="preserve">01. Enter a valid username 
 02. Enter a valid password
 03. Click on Login Button
@@ -1810,9 +1696,6 @@
   </si>
   <si>
     <t>Verify Load More Notifications</t>
-  </si>
-  <si>
-    <t>Load Additional Notifications</t>
   </si>
   <si>
     <t>Additional notifications should load seamlessly.</t>
@@ -2244,6 +2127,35 @@
   </si>
   <si>
     <t>The user logged out from the facebook.</t>
+  </si>
+  <si>
+    <t>01. Empty username 
+02. Empty password
+03. Click on Login Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Facebook Post create edit,react, comment, share Fucntionality </t>
+  </si>
+  <si>
+    <t>Verify that the user can send multiple messages in a conversation..</t>
+  </si>
+  <si>
+    <t>Verify FaceBook Messaging Functionality</t>
+  </si>
+  <si>
+    <t>FaceBook Marketplace</t>
+  </si>
+  <si>
+    <t>Verify Send,Accept,Remove Friend Requests, Unfollow, unfreind Funtionslity  and veriy that the user can View Friend Suggestions and  View Friends List</t>
+  </si>
+  <si>
+    <t>Verify FaceBook Marketplace Functionality</t>
+  </si>
+  <si>
+    <t>Verify that search facebook group, pin, post, react, comment in a group an leave Facebook group functionality</t>
+  </si>
+  <si>
+    <t>Verify Facebook Notifications Functionality</t>
   </si>
 </sst>
 </file>
@@ -5546,22 +5458,22 @@
         <v>117</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>118</v>
+        <v>508</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>33</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>43</v>
       </c>
       <c r="I13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>96</v>
@@ -6017,7 +5929,7 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -6113,7 +6025,7 @@
         <v>105</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G43" s="14"/>
       <c r="H43" s="17" t="s">
@@ -6191,7 +6103,7 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -6272,34 +6184,34 @@
     </row>
     <row r="55" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="D55" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C55" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>129</v>
-      </c>
       <c r="E55" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F55" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I55" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="J55" s="14" t="s">
         <v>143</v>
-      </c>
-      <c r="J55" s="14" t="s">
-        <v>144</v>
       </c>
       <c r="K55" s="18" t="s">
         <v>96</v>
@@ -6311,39 +6223,39 @@
         <v>45643</v>
       </c>
       <c r="N55" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F56" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>70</v>
       </c>
       <c r="I56" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="J56" s="14" t="s">
         <v>132</v>
-      </c>
-      <c r="J56" s="14" t="s">
-        <v>133</v>
       </c>
       <c r="K56" s="18" t="s">
         <v>96</v>
@@ -6358,34 +6270,34 @@
     </row>
     <row r="57" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C57" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D57" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="E57" s="14" t="s">
         <v>138</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>139</v>
       </c>
       <c r="F57" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H57" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I57" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="I57" s="14" t="s">
+      <c r="J57" s="14" t="s">
         <v>143</v>
-      </c>
-      <c r="J57" s="14" t="s">
-        <v>144</v>
       </c>
       <c r="K57" s="18" t="s">
         <v>96</v>
@@ -6397,39 +6309,39 @@
         <v>45643</v>
       </c>
       <c r="N57" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D58" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="E58" s="14" t="s">
         <v>147</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="F58" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>70</v>
       </c>
       <c r="I58" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="J58" s="14" t="s">
         <v>132</v>
-      </c>
-      <c r="J58" s="14" t="s">
-        <v>133</v>
       </c>
       <c r="K58" s="18" t="s">
         <v>96</v>
@@ -6455,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
@@ -6536,34 +6448,34 @@
     </row>
     <row r="69" spans="1:14" ht="169.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C69" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="D69" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C69" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D69" s="14" t="s">
+      <c r="E69" s="14" t="s">
         <v>153</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>154</v>
       </c>
       <c r="F69" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G69" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="H69" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="I69" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="H69" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="I69" s="14" t="s">
+      <c r="J69" s="14" t="s">
         <v>156</v>
-      </c>
-      <c r="J69" s="14" t="s">
-        <v>157</v>
       </c>
       <c r="K69" s="18" t="s">
         <v>96</v>
@@ -6589,7 +6501,7 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -6670,34 +6582,34 @@
     </row>
     <row r="80" spans="1:14" ht="180.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>187</v>
+        <v>509</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H80" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="I80" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="I80" s="14" t="s">
-        <v>163</v>
-      </c>
       <c r="J80" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K80" s="18" t="s">
         <v>96</v>
@@ -6712,34 +6624,34 @@
     </row>
     <row r="81" spans="1:14" ht="173.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="C81" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B81" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="C81" s="15" t="s">
+      <c r="D81" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="D81" s="14" t="s">
-        <v>169</v>
-      </c>
       <c r="E81" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I81" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J81" s="14" t="s">
         <v>177</v>
-      </c>
-      <c r="J81" s="14" t="s">
-        <v>178</v>
       </c>
       <c r="K81" s="18" t="s">
         <v>96</v>
@@ -6754,34 +6666,34 @@
     </row>
     <row r="82" spans="1:14" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B82" s="14" t="s">
-        <v>187</v>
+        <v>509</v>
       </c>
       <c r="C82" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D82" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="D82" s="14" t="s">
-        <v>173</v>
-      </c>
       <c r="E82" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F82" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H82" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="I82" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="I82" s="14" t="s">
-        <v>175</v>
-      </c>
       <c r="J82" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K82" s="18" t="s">
         <v>96</v>
@@ -6796,34 +6708,34 @@
     </row>
     <row r="83" spans="1:14" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>188</v>
+        <v>509</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F83" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G83" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="I83" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="H83" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="I83" s="14" t="s">
+      <c r="J83" s="14" t="s">
         <v>185</v>
-      </c>
-      <c r="J83" s="14" t="s">
-        <v>186</v>
       </c>
       <c r="K83" s="18" t="s">
         <v>96</v>
@@ -6838,34 +6750,34 @@
     </row>
     <row r="84" spans="1:14" ht="111.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>192</v>
+        <v>509</v>
       </c>
       <c r="C84" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E84" s="14" t="s">
         <v>190</v>
-      </c>
-      <c r="D84" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>194</v>
       </c>
       <c r="F84" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H84" s="17" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K84" s="18" t="s">
         <v>96</v>
@@ -6880,34 +6792,34 @@
     </row>
     <row r="85" spans="1:14" ht="129" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>192</v>
+        <v>509</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F85" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G85" s="14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K85" s="18" t="s">
         <v>96</v>
@@ -6922,34 +6834,34 @@
     </row>
     <row r="86" spans="1:14" ht="124.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>192</v>
+        <v>509</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F86" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G86" s="14" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K86" s="18" t="s">
         <v>96</v>
@@ -6964,19 +6876,19 @@
     </row>
     <row r="87" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>210</v>
+        <v>509</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F87" s="16" t="s">
         <v>33</v>
@@ -6985,13 +6897,13 @@
         <v>38</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K87" s="18" t="s">
         <v>96</v>
@@ -7017,7 +6929,7 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
@@ -7098,34 +7010,34 @@
     </row>
     <row r="98" spans="1:14" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="35" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>227</v>
+        <v>511</v>
       </c>
       <c r="C98" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="D98" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="D98" s="31" t="s">
-        <v>226</v>
-      </c>
       <c r="E98" s="31" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F98" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G98" s="31" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="H98" s="34" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="I98" s="31" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J98" s="31" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K98" s="35" t="s">
         <v>96</v>
@@ -7140,34 +7052,34 @@
     </row>
     <row r="99" spans="1:14" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="35" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>229</v>
+        <v>511</v>
       </c>
       <c r="C99" s="32" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D99" s="31" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F99" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G99" s="31" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="H99" s="34" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I99" s="31" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J99" s="31" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="K99" s="35" t="s">
         <v>96</v>
@@ -7182,34 +7094,34 @@
     </row>
     <row r="100" spans="1:14" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B100" s="31" t="s">
+        <v>511</v>
+      </c>
+      <c r="C100" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="B100" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="C100" s="32" t="s">
-        <v>223</v>
-      </c>
       <c r="D100" s="31" t="s">
-        <v>234</v>
+        <v>510</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="F100" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G100" s="31" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="H100" s="34" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I100" s="31" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="J100" s="31" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="K100" s="35" t="s">
         <v>96</v>
@@ -7224,34 +7136,34 @@
     </row>
     <row r="101" spans="1:14" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="35" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>219</v>
+        <v>511</v>
       </c>
       <c r="C101" s="32" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D101" s="31" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="E101" s="31" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F101" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G101" s="31" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="H101" s="34" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="I101" s="31" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="J101" s="31" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="K101" s="35" t="s">
         <v>96</v>
@@ -7266,34 +7178,34 @@
     </row>
     <row r="102" spans="1:14" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="35" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>220</v>
+        <v>511</v>
       </c>
       <c r="C102" s="32" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D102" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="E102" s="31" t="s">
         <v>245</v>
-      </c>
-      <c r="E102" s="31" t="s">
-        <v>254</v>
       </c>
       <c r="F102" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G102" s="31" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="H102" s="34" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="I102" s="31" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="J102" s="31" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="K102" s="35" t="s">
         <v>96</v>
@@ -7319,7 +7231,7 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
@@ -7400,34 +7312,34 @@
     </row>
     <row r="113" spans="1:14" ht="174.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="35" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B113" s="31" t="s">
+        <v>513</v>
+      </c>
+      <c r="C113" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D113" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="D113" s="31" t="s">
-        <v>269</v>
-      </c>
       <c r="E113" s="31" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="F113" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G113" s="31" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="H113" s="34" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="I113" s="31" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="J113" s="31" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="K113" s="35" t="s">
         <v>96</v>
@@ -7442,34 +7354,34 @@
     </row>
     <row r="114" spans="1:14" ht="279" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="35" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>266</v>
+        <v>513</v>
       </c>
       <c r="C114" s="32" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D114" s="31" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E114" s="31" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="F114" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G114" s="31" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="H114" s="34" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="I114" s="31" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="J114" s="31" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="K114" s="35" t="s">
         <v>96</v>
@@ -7484,34 +7396,34 @@
     </row>
     <row r="115" spans="1:14" ht="223.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="35" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>286</v>
+        <v>513</v>
       </c>
       <c r="C115" s="32" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D115" s="31" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="F115" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G115" s="31" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="H115" s="34" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="I115" s="31" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="J115" s="31" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="K115" s="35" t="s">
         <v>96</v>
@@ -7526,34 +7438,34 @@
     </row>
     <row r="116" spans="1:14" ht="183" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="35" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>295</v>
+        <v>513</v>
       </c>
       <c r="C116" s="32" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D116" s="31" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="F116" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G116" s="31" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="H116" s="34" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="I116" s="31" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="J116" s="31" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="K116" s="35" t="s">
         <v>96</v>
@@ -7568,34 +7480,34 @@
     </row>
     <row r="117" spans="1:14" ht="196.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="35" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B117" s="31" t="s">
-        <v>271</v>
+        <v>513</v>
       </c>
       <c r="C117" s="32" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D117" s="31" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="E117" s="31" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="F117" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G117" s="31" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="H117" s="34" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="I117" s="31" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="J117" s="31" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="K117" s="35" t="s">
         <v>96</v>
@@ -7610,34 +7522,34 @@
     </row>
     <row r="118" spans="1:14" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="35" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>274</v>
+        <v>513</v>
       </c>
       <c r="C118" s="32" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="D118" s="31" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="E118" s="31" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="F118" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G118" s="31" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="H118" s="34" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="I118" s="31" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="J118" s="31" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="K118" s="35" t="s">
         <v>96</v>
@@ -7652,34 +7564,34 @@
     </row>
     <row r="119" spans="1:14" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="35" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B119" s="31" t="s">
-        <v>281</v>
+        <v>513</v>
       </c>
       <c r="C119" s="32" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="D119" s="31" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="E119" s="31" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="F119" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G119" s="31" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="H119" s="34" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="I119" s="31" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="J119" s="31" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="K119" s="35" t="s">
         <v>96</v>
@@ -7705,7 +7617,7 @@
         <v>1</v>
       </c>
       <c r="B123" t="s">
-        <v>305</v>
+        <v>512</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
@@ -7786,34 +7698,34 @@
     </row>
     <row r="130" spans="1:14" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="13" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B130" s="14" t="s">
-        <v>311</v>
+        <v>514</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="F130" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G130" s="14" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="H130" s="17" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="I130" s="14" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="J130" s="14" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="K130" s="18" t="s">
         <v>96</v>
@@ -7828,34 +7740,34 @@
     </row>
     <row r="131" spans="1:14" ht="125.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="13" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>310</v>
+        <v>514</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="F131" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G131" s="14" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H131" s="17" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="I131" s="14" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="K131" s="18" t="s">
         <v>96</v>
@@ -7870,34 +7782,34 @@
     </row>
     <row r="132" spans="1:14" ht="136.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="C132" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="E132" s="14" t="s">
         <v>304</v>
-      </c>
-      <c r="B132" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="C132" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="D132" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="E132" s="14" t="s">
-        <v>324</v>
       </c>
       <c r="F132" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="H132" s="17" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="J132" s="14" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="K132" s="18" t="s">
         <v>96</v>
@@ -7912,34 +7824,34 @@
     </row>
     <row r="133" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>328</v>
+        <v>514</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="E133" s="14" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="F133" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G133" s="14" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="H133" s="17" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="K133" s="18" t="s">
         <v>96</v>
@@ -7954,34 +7866,34 @@
     </row>
     <row r="134" spans="1:14" ht="196.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>335</v>
+        <v>514</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="F134" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G134" s="14" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="H134" s="17" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="J134" s="14" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="K134" s="18" t="s">
         <v>96</v>
@@ -7996,34 +7908,34 @@
     </row>
     <row r="135" spans="1:14" ht="186" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>342</v>
+        <v>514</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="E135" s="14" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="F135" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G135" s="14" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="H135" s="17" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="I135" s="14" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="K135" s="18" t="s">
         <v>96</v>
@@ -8038,34 +7950,34 @@
     </row>
     <row r="136" spans="1:14" ht="174.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>350</v>
+        <v>514</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="E136" s="14" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="F136" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G136" s="14" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="H136" s="17" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="K136" s="18" t="s">
         <v>96</v>
@@ -8080,34 +7992,34 @@
     </row>
     <row r="137" spans="1:14" ht="163.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B137" s="14" t="s">
-        <v>357</v>
+        <v>514</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="E137" s="14" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="F137" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G137" s="14" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="H137" s="17" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="J137" s="14" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="K137" s="18" t="s">
         <v>96</v>
@@ -8122,34 +8034,34 @@
     </row>
     <row r="138" spans="1:14" ht="106.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>363</v>
+        <v>514</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="F138" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="H138" s="17" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="K138" s="18" t="s">
         <v>96</v>
@@ -8164,34 +8076,34 @@
     </row>
     <row r="139" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>369</v>
+        <v>514</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="E139" s="14" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="F139" s="16" t="s">
         <v>33</v>
       </c>
       <c r="G139" s="14" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="H139" s="17" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="J139" s="14" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="K139" s="18" t="s">
         <v>96</v>
@@ -8217,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="B143" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
@@ -8298,34 +8210,34 @@
     </row>
     <row r="150" spans="1:14" ht="146.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="44" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B150" s="31" t="s">
-        <v>377</v>
+        <v>515</v>
       </c>
       <c r="C150" s="32" t="s">
-        <v>378</v>
+        <v>351</v>
       </c>
       <c r="D150" s="31" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="E150" s="31" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="F150" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G150" s="31" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="H150" s="34" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="I150" s="31" t="s">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="J150" s="31" t="s">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="K150" s="35" t="s">
         <v>96</v>
@@ -8340,34 +8252,34 @@
     </row>
     <row r="151" spans="1:14" ht="183.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="44" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>385</v>
+        <v>515</v>
       </c>
       <c r="C151" s="32" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="D151" s="31" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="E151" s="31" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="F151" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G151" s="31" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="H151" s="34" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="I151" s="31" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="J151" s="31" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="K151" s="35" t="s">
         <v>96</v>
@@ -8382,34 +8294,34 @@
     </row>
     <row r="152" spans="1:14" ht="252" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="44" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B152" s="31" t="s">
-        <v>389</v>
+        <v>515</v>
       </c>
       <c r="C152" s="32" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="D152" s="31" t="s">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="E152" s="31" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="F152" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G152" s="31" t="s">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="H152" s="34" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="I152" s="31" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="J152" s="31" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="K152" s="35" t="s">
         <v>96</v>
@@ -8424,34 +8336,34 @@
     </row>
     <row r="153" spans="1:14" ht="235.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="44" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B153" s="31" t="s">
-        <v>399</v>
+        <v>515</v>
       </c>
       <c r="C153" s="32" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D153" s="31" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="E153" s="31" t="s">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="F153" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G153" s="31" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="H153" s="34" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="I153" s="31" t="s">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="J153" s="31" t="s">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="K153" s="35" t="s">
         <v>96</v>
@@ -8466,34 +8378,34 @@
     </row>
     <row r="154" spans="1:14" ht="219.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="44" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B154" s="31" t="s">
-        <v>403</v>
+        <v>515</v>
       </c>
       <c r="C154" s="32" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="D154" s="31" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="E154" s="31" t="s">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="F154" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G154" s="31" t="s">
-        <v>407</v>
+        <v>375</v>
       </c>
       <c r="H154" s="34" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="I154" s="31" t="s">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="J154" s="31" t="s">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="K154" s="35" t="s">
         <v>96</v>
@@ -8508,34 +8420,34 @@
     </row>
     <row r="155" spans="1:14" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="44" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B155" s="31" t="s">
-        <v>409</v>
+        <v>515</v>
       </c>
       <c r="C155" s="32" t="s">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="D155" s="31" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="E155" s="31" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="F155" s="33" t="s">
         <v>33</v>
       </c>
       <c r="G155" s="31" t="s">
-        <v>412</v>
+        <v>379</v>
       </c>
       <c r="H155" s="34" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="I155" s="31" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="J155" s="31" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="K155" s="35" t="s">
         <v>96</v>
@@ -8561,7 +8473,7 @@
         <v>1</v>
       </c>
       <c r="B159" s="57" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
@@ -8642,34 +8554,34 @@
     </row>
     <row r="166" spans="1:14" ht="122.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="50" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B166" s="51" t="s">
-        <v>427</v>
+        <v>516</v>
       </c>
       <c r="C166" s="52" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="D166" s="51" t="s">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="E166" s="51" t="s">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="F166" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G166" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H166" s="54" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="I166" s="51" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="J166" s="51" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="K166" s="55" t="s">
         <v>96</v>
@@ -8684,34 +8596,34 @@
     </row>
     <row r="167" spans="1:14" ht="150.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="50" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B167" s="51" t="s">
-        <v>428</v>
+        <v>516</v>
       </c>
       <c r="C167" s="52" t="s">
-        <v>419</v>
+        <v>386</v>
       </c>
       <c r="D167" s="51" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="E167" s="51" t="s">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="F167" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G167" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H167" s="54" t="s">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="I167" s="51" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="J167" s="51" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="K167" s="55" t="s">
         <v>96</v>
@@ -8726,34 +8638,34 @@
     </row>
     <row r="168" spans="1:14" ht="183" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="50" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B168" s="51" t="s">
-        <v>431</v>
+        <v>516</v>
       </c>
       <c r="C168" s="52" t="s">
-        <v>429</v>
+        <v>394</v>
       </c>
       <c r="D168" s="51" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="E168" s="51" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="F168" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G168" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H168" s="54" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="I168" s="51" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="J168" s="51" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="K168" s="55" t="s">
         <v>96</v>
@@ -8768,34 +8680,34 @@
     </row>
     <row r="169" spans="1:14" ht="157.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="50" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B169" s="51" t="s">
-        <v>438</v>
+        <v>516</v>
       </c>
       <c r="C169" s="52" t="s">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="D169" s="51" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="E169" s="51" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="F169" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G169" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H169" s="54" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="I169" s="51" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="J169" s="51" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="K169" s="55" t="s">
         <v>96</v>
@@ -8810,34 +8722,34 @@
     </row>
     <row r="170" spans="1:14" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="50" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B170" s="51" t="s">
-        <v>444</v>
+        <v>516</v>
       </c>
       <c r="C170" s="52" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
       <c r="D170" s="51" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="E170" s="51" t="s">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="F170" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G170" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H170" s="54" t="s">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="I170" s="51" t="s">
-        <v>445</v>
+        <v>407</v>
       </c>
       <c r="J170" s="51" t="s">
-        <v>445</v>
+        <v>407</v>
       </c>
       <c r="K170" s="55" t="s">
         <v>96</v>
@@ -8852,34 +8764,34 @@
     </row>
     <row r="171" spans="1:14" ht="139.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="50" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B171" s="51" t="s">
-        <v>444</v>
+        <v>516</v>
       </c>
       <c r="C171" s="52" t="s">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="D171" s="51" t="s">
-        <v>449</v>
+        <v>411</v>
       </c>
       <c r="E171" s="51" t="s">
-        <v>450</v>
+        <v>412</v>
       </c>
       <c r="F171" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G171" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H171" s="54" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
       <c r="I171" s="51" t="s">
-        <v>452</v>
+        <v>414</v>
       </c>
       <c r="J171" s="51" t="s">
-        <v>452</v>
+        <v>414</v>
       </c>
       <c r="K171" s="55" t="s">
         <v>96</v>
@@ -8905,7 +8817,7 @@
         <v>1</v>
       </c>
       <c r="B175" s="57" t="s">
-        <v>454</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
@@ -8986,34 +8898,34 @@
     </row>
     <row r="182" spans="1:14" ht="193.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="50" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B182" s="51" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C182" s="52" t="s">
-        <v>455</v>
+        <v>417</v>
       </c>
       <c r="D182" s="51" t="s">
-        <v>457</v>
+        <v>419</v>
       </c>
       <c r="E182" s="51" t="s">
-        <v>461</v>
+        <v>423</v>
       </c>
       <c r="F182" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G182" s="51" t="s">
+        <v>388</v>
+      </c>
+      <c r="H182" s="54" t="s">
         <v>421</v>
       </c>
-      <c r="H182" s="54" t="s">
-        <v>459</v>
-      </c>
       <c r="I182" s="51" t="s">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="J182" s="51" t="s">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="K182" s="55" t="s">
         <v>96</v>
@@ -9028,34 +8940,34 @@
     </row>
     <row r="183" spans="1:14" ht="128.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="50" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B183" s="51" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C183" s="52" t="s">
-        <v>456</v>
+        <v>418</v>
       </c>
       <c r="D183" s="51" t="s">
-        <v>460</v>
+        <v>422</v>
       </c>
       <c r="E183" s="51" t="s">
-        <v>466</v>
+        <v>428</v>
       </c>
       <c r="F183" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G183" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H183" s="54" t="s">
-        <v>463</v>
+        <v>425</v>
       </c>
       <c r="I183" s="51" t="s">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="J183" s="51" t="s">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="K183" s="55" t="s">
         <v>96</v>
@@ -9070,34 +8982,34 @@
     </row>
     <row r="184" spans="1:14" ht="164.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="50" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B184" s="51" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C184" s="52" t="s">
-        <v>464</v>
+        <v>426</v>
       </c>
       <c r="D184" s="51" t="s">
-        <v>465</v>
+        <v>427</v>
       </c>
       <c r="E184" s="51" t="s">
-        <v>471</v>
+        <v>433</v>
       </c>
       <c r="F184" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G184" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H184" s="54" t="s">
-        <v>468</v>
+        <v>430</v>
       </c>
       <c r="I184" s="51" t="s">
-        <v>467</v>
+        <v>429</v>
       </c>
       <c r="J184" s="51" t="s">
-        <v>467</v>
+        <v>429</v>
       </c>
       <c r="K184" s="55" t="s">
         <v>96</v>
@@ -9112,34 +9024,34 @@
     </row>
     <row r="185" spans="1:14" ht="166.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="50" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B185" s="51" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C185" s="52" t="s">
-        <v>469</v>
+        <v>431</v>
       </c>
       <c r="D185" s="51" t="s">
-        <v>470</v>
+        <v>432</v>
       </c>
       <c r="E185" s="51" t="s">
-        <v>472</v>
+        <v>434</v>
       </c>
       <c r="F185" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G185" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H185" s="54" t="s">
-        <v>474</v>
+        <v>436</v>
       </c>
       <c r="I185" s="51" t="s">
-        <v>473</v>
+        <v>435</v>
       </c>
       <c r="J185" s="51" t="s">
-        <v>473</v>
+        <v>435</v>
       </c>
       <c r="K185" s="55" t="s">
         <v>96</v>
@@ -9154,34 +9066,34 @@
     </row>
     <row r="186" spans="1:14" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="50" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B186" s="51" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C186" s="52" t="s">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="D186" s="51" t="s">
-        <v>478</v>
+        <v>440</v>
       </c>
       <c r="E186" s="51" t="s">
-        <v>476</v>
+        <v>438</v>
       </c>
       <c r="F186" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G186" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H186" s="54" t="s">
-        <v>477</v>
+        <v>439</v>
       </c>
       <c r="I186" s="51" t="s">
-        <v>479</v>
+        <v>441</v>
       </c>
       <c r="J186" s="51" t="s">
-        <v>479</v>
+        <v>441</v>
       </c>
       <c r="K186" s="55" t="s">
         <v>96</v>
@@ -9196,34 +9108,34 @@
     </row>
     <row r="187" spans="1:14" ht="161.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="50" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B187" s="51" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C187" s="52" t="s">
-        <v>480</v>
+        <v>442</v>
       </c>
       <c r="D187" s="51" t="s">
-        <v>481</v>
+        <v>443</v>
       </c>
       <c r="E187" s="51" t="s">
-        <v>487</v>
+        <v>449</v>
       </c>
       <c r="F187" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G187" s="51" t="s">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="H187" s="54" t="s">
-        <v>484</v>
+        <v>446</v>
       </c>
       <c r="I187" s="51" t="s">
-        <v>483</v>
+        <v>445</v>
       </c>
       <c r="J187" s="51" t="s">
-        <v>483</v>
+        <v>445</v>
       </c>
       <c r="K187" s="55" t="s">
         <v>96</v>
@@ -9238,34 +9150,34 @@
     </row>
     <row r="188" spans="1:14" ht="170.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="50" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B188" s="51" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C188" s="52" t="s">
-        <v>485</v>
+        <v>447</v>
       </c>
       <c r="D188" s="51" t="s">
-        <v>486</v>
+        <v>448</v>
       </c>
       <c r="E188" s="51" t="s">
-        <v>492</v>
+        <v>454</v>
       </c>
       <c r="F188" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G188" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H188" s="54" t="s">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="I188" s="51" t="s">
-        <v>489</v>
+        <v>451</v>
       </c>
       <c r="J188" s="51" t="s">
-        <v>489</v>
+        <v>451</v>
       </c>
       <c r="K188" s="55" t="s">
         <v>96</v>
@@ -9280,34 +9192,34 @@
     </row>
     <row r="189" spans="1:14" ht="188.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="B189" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="C189" s="52" t="s">
+        <v>452</v>
+      </c>
+      <c r="D189" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="B189" s="51" t="s">
-        <v>503</v>
-      </c>
-      <c r="C189" s="52" t="s">
-        <v>490</v>
-      </c>
-      <c r="D189" s="51" t="s">
-        <v>491</v>
-      </c>
       <c r="E189" s="51" t="s">
-        <v>493</v>
+        <v>455</v>
       </c>
       <c r="F189" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G189" s="51" t="s">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="H189" s="54" t="s">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="I189" s="51" t="s">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="J189" s="51" t="s">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="K189" s="55" t="s">
         <v>96</v>
@@ -9322,34 +9234,34 @@
     </row>
     <row r="190" spans="1:14" ht="197.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="50" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B190" s="51" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="C190" s="52" t="s">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="D190" s="51" t="s">
-        <v>501</v>
+        <v>463</v>
       </c>
       <c r="E190" s="51" t="s">
-        <v>498</v>
+        <v>460</v>
       </c>
       <c r="F190" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G190" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H190" s="54" t="s">
-        <v>500</v>
+        <v>462</v>
       </c>
       <c r="I190" s="51" t="s">
-        <v>499</v>
+        <v>461</v>
       </c>
       <c r="J190" s="51" t="s">
-        <v>499</v>
+        <v>461</v>
       </c>
       <c r="K190" s="55" t="s">
         <v>96</v>
@@ -9375,7 +9287,7 @@
         <v>1</v>
       </c>
       <c r="B194" s="57" t="s">
-        <v>514</v>
+        <v>476</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
@@ -9456,34 +9368,34 @@
     </row>
     <row r="201" spans="1:14" ht="148.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="50" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="B201" s="51" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="C201" s="52" t="s">
-        <v>507</v>
+        <v>469</v>
       </c>
       <c r="D201" s="51" t="s">
-        <v>505</v>
+        <v>467</v>
       </c>
       <c r="E201" s="51" t="s">
-        <v>510</v>
+        <v>472</v>
       </c>
       <c r="F201" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G201" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H201" s="54" t="s">
-        <v>506</v>
+        <v>468</v>
       </c>
       <c r="I201" s="51" t="s">
-        <v>508</v>
+        <v>470</v>
       </c>
       <c r="J201" s="51" t="s">
-        <v>508</v>
+        <v>470</v>
       </c>
       <c r="K201" s="55" t="s">
         <v>96</v>
@@ -9498,34 +9410,34 @@
     </row>
     <row r="202" spans="1:14" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="50" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="B202" s="51" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="C202" s="52" t="s">
-        <v>509</v>
+        <v>471</v>
       </c>
       <c r="D202" s="51" t="s">
-        <v>516</v>
+        <v>478</v>
       </c>
       <c r="E202" s="51" t="s">
-        <v>511</v>
+        <v>473</v>
       </c>
       <c r="F202" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G202" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H202" s="54" t="s">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="I202" s="51" t="s">
-        <v>512</v>
+        <v>474</v>
       </c>
       <c r="J202" s="51" t="s">
-        <v>512</v>
+        <v>474</v>
       </c>
       <c r="K202" s="55" t="s">
         <v>96</v>
@@ -9540,34 +9452,34 @@
     </row>
     <row r="203" spans="1:14" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="50" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="B203" s="51" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="C203" s="52" t="s">
-        <v>515</v>
+        <v>477</v>
       </c>
       <c r="D203" s="51" t="s">
-        <v>518</v>
+        <v>480</v>
       </c>
       <c r="E203" s="51" t="s">
-        <v>517</v>
+        <v>479</v>
       </c>
       <c r="F203" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G203" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H203" s="54" t="s">
-        <v>519</v>
+        <v>481</v>
       </c>
       <c r="I203" s="51" t="s">
-        <v>520</v>
+        <v>482</v>
       </c>
       <c r="J203" s="51" t="s">
-        <v>520</v>
+        <v>482</v>
       </c>
       <c r="K203" s="55" t="s">
         <v>96</v>
@@ -9582,34 +9494,34 @@
     </row>
     <row r="204" spans="1:14" ht="137.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="50" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="B204" s="51" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="C204" s="52" t="s">
-        <v>521</v>
+        <v>483</v>
       </c>
       <c r="D204" s="51" t="s">
-        <v>522</v>
+        <v>484</v>
       </c>
       <c r="E204" s="51" t="s">
-        <v>523</v>
+        <v>485</v>
       </c>
       <c r="F204" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G204" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H204" s="54" t="s">
-        <v>524</v>
+        <v>486</v>
       </c>
       <c r="I204" s="51" t="s">
-        <v>525</v>
+        <v>487</v>
       </c>
       <c r="J204" s="51" t="s">
-        <v>525</v>
+        <v>487</v>
       </c>
       <c r="K204" s="55" t="s">
         <v>96</v>
@@ -9624,34 +9536,34 @@
     </row>
     <row r="205" spans="1:14" ht="143.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="50" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="B205" s="51" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="C205" s="52" t="s">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="D205" s="51" t="s">
-        <v>527</v>
+        <v>489</v>
       </c>
       <c r="E205" s="51" t="s">
-        <v>530</v>
+        <v>492</v>
       </c>
       <c r="F205" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G205" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H205" s="54" t="s">
-        <v>528</v>
+        <v>490</v>
       </c>
       <c r="I205" s="51" t="s">
-        <v>529</v>
+        <v>491</v>
       </c>
       <c r="J205" s="51" t="s">
-        <v>529</v>
+        <v>491</v>
       </c>
       <c r="K205" s="55" t="s">
         <v>96</v>
@@ -9666,34 +9578,34 @@
     </row>
     <row r="206" spans="1:14" ht="182.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="50" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="B206" s="51" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="C206" s="52" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="D206" s="51" t="s">
-        <v>532</v>
+        <v>494</v>
       </c>
       <c r="E206" s="51" t="s">
-        <v>537</v>
+        <v>499</v>
       </c>
       <c r="F206" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G206" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H206" s="54" t="s">
-        <v>533</v>
+        <v>495</v>
       </c>
       <c r="I206" s="51" t="s">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="J206" s="51" t="s">
-        <v>534</v>
+        <v>496</v>
       </c>
       <c r="K206" s="55" t="s">
         <v>96</v>
@@ -9708,34 +9620,34 @@
     </row>
     <row r="207" spans="1:14" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="50" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="B207" s="51" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="C207" s="52" t="s">
-        <v>535</v>
+        <v>497</v>
       </c>
       <c r="D207" s="51" t="s">
-        <v>536</v>
+        <v>498</v>
       </c>
       <c r="E207" s="51" t="s">
-        <v>538</v>
+        <v>500</v>
       </c>
       <c r="F207" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G207" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H207" s="54" t="s">
-        <v>539</v>
+        <v>501</v>
       </c>
       <c r="I207" s="51" t="s">
-        <v>540</v>
+        <v>502</v>
       </c>
       <c r="J207" s="51" t="s">
-        <v>540</v>
+        <v>502</v>
       </c>
       <c r="K207" s="55" t="s">
         <v>96</v>
@@ -9748,36 +9660,36 @@
       </c>
       <c r="N207" s="58"/>
     </row>
-    <row r="208" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="50" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="B208" s="51" t="s">
+        <v>466</v>
+      </c>
+      <c r="C208" s="52" t="s">
+        <v>503</v>
+      </c>
+      <c r="D208" s="51" t="s">
         <v>504</v>
       </c>
-      <c r="C208" s="52" t="s">
-        <v>541</v>
-      </c>
-      <c r="D208" s="51" t="s">
-        <v>542</v>
-      </c>
       <c r="E208" s="51" t="s">
-        <v>543</v>
+        <v>505</v>
       </c>
       <c r="F208" s="53" t="s">
         <v>33</v>
       </c>
       <c r="G208" s="51" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="H208" s="54" t="s">
-        <v>544</v>
+        <v>506</v>
       </c>
       <c r="I208" s="51" t="s">
-        <v>545</v>
+        <v>507</v>
       </c>
       <c r="J208" s="51" t="s">
-        <v>545</v>
+        <v>507</v>
       </c>
       <c r="K208" s="55" t="s">
         <v>96</v>
